--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\UserSpace\Games\Steam_Library\steamapps\common\BeamNG_Userdata\current\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AA2477-6E76-484F-B0B2-0B0FA72C70D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LSC Sweep" sheetId="1" r:id="rId1"/>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AA2477-6E76-484F-B0B2-0B0FA72C70D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16FF841-20CB-4218-B4EA-75B068F89C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LSC Sweep" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="LSR Sweep" sheetId="5" r:id="rId3"/>
     <sheet name="Full Sweep" sheetId="3" r:id="rId4"/>
     <sheet name="Parameters" sheetId="4" r:id="rId5"/>
+    <sheet name="Calculator" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="145">
   <si>
     <t>Astral · LSC sweep</t>
   </si>
@@ -306,9 +307,6 @@
     <t>HSC 越接近 0，第二膝点越晚、附加斜率越大；曲线交叉按公式保留。</t>
   </si>
   <si>
-    <t>来源：研究会话 v13；当前修订：k2 为 0.52～0.68，取消 HSC 中间段倍率（2026-09-20）。</t>
-  </si>
-  <si>
     <t>chatgpt-conversation://6a9ed043-7848-83e8-9d36-6e63c8202898</t>
   </si>
   <si>
@@ -350,16 +348,143 @@
   <si>
     <t>采样：0～1.00 m/s，每 0.05 m/s 一点，共 21 点；不另加膝点采样。</t>
   </si>
+  <si>
+    <t>当前 Type-A：k1 0.12/0.15/0.17；rL 0.78～0.90；k2 0.58～0.62（2026-09-28）。</t>
+  </si>
+  <si>
+    <t>Astral · Type-A 阻尼计算器</t>
+  </si>
+  <si>
+    <t>输入</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>范围 / 单位</t>
+  </si>
+  <si>
+    <t>阻尼力大小</t>
+  </si>
+  <si>
+    <t>结果</t>
+  </si>
+  <si>
+    <t>车型</t>
+  </si>
+  <si>
+    <t>Rally2</t>
+  </si>
+  <si>
+    <t>砂石 Type-A</t>
+  </si>
+  <si>
+    <t>压缩</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>LSC / c</t>
+  </si>
+  <si>
+    <t>回弹</t>
+  </si>
+  <si>
+    <t>HSC / C</t>
+  </si>
+  <si>
+    <t>−20～0 格</t>
+  </si>
+  <si>
+    <t>LSR / R</t>
+  </si>
+  <si>
+    <t>当前曲线系数</t>
+  </si>
+  <si>
+    <t>轴速大小</t>
+  </si>
+  <si>
+    <t>LS 压缩 cL</t>
+  </si>
+  <si>
+    <t>中间段 cM</t>
+  </si>
+  <si>
+    <t>HS 附加段 A</t>
+  </si>
+  <si>
+    <t>合计 HS 压缩 cH</t>
+  </si>
+  <si>
+    <t>格数与映射</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>LS 回弹</t>
+  </si>
+  <si>
+    <t>HS 回弹</t>
+  </si>
+  <si>
+    <t>c 总格数</t>
+  </si>
+  <si>
+    <t>−格数～0</t>
+  </si>
+  <si>
+    <t>R 总格数</t>
+  </si>
+  <si>
+    <t>c 标准位置</t>
+  </si>
+  <si>
+    <t>映射至 −20～0</t>
+  </si>
+  <si>
+    <t>C 标准位置</t>
+  </si>
+  <si>
+    <t>−20～0</t>
+  </si>
+  <si>
+    <t>R 标准位置</t>
+  </si>
+  <si>
+    <t>映射至 −40～0</t>
+  </si>
+  <si>
+    <t>c 插值区间</t>
+  </si>
+  <si>
+    <t>C 插值区间</t>
+  </si>
+  <si>
+    <t>R 插值区间</t>
+  </si>
+  <si>
+    <t>黄色格可输入；换车型后，请将 c／R 调整到该车型的有效范围。</t>
+  </si>
+  <si>
+    <t>0 为最硬端；两项输出均为同一轴速下的力大小，不使用回弹图的负号。</t>
+  </si>
+  <si>
+    <t>按连续分段接续模型计算，未计入 LRS／DSV、限位、弹簧与气体力。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.000"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -407,8 +532,46 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF24364B"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF24364B"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FF24364B"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF566578"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,8 +613,21 @@
         <fgColor rgb="FFE8EDF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30475E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -468,12 +644,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -545,10 +731,21 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="8" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="9" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔[0]" xfId="2" builtinId="6"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -697,61 +894,61 @@
                   <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126.36000000000001</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>173.16</c:v>
+                  <c:v>186.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.96</c:v>
+                  <c:v>237.12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>266.76</c:v>
+                  <c:v>287.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>313.56</c:v>
+                  <c:v>338.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>360.36</c:v>
+                  <c:v>389.21999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>407.16</c:v>
+                  <c:v>439.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>453.96</c:v>
+                  <c:v>490.62</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>500.76000000000005</c:v>
+                  <c:v>541.31999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>547.56000000000006</c:v>
+                  <c:v>592.02</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>594.36</c:v>
+                  <c:v>642.72</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>766.1600000000002</c:v>
+                  <c:v>818.42000000000019</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>937.96</c:v>
+                  <c:v>994.11999999999989</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1109.76</c:v>
+                  <c:v>1169.8200000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1281.5600000000002</c:v>
+                  <c:v>1345.5200000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1453.3600000000001</c:v>
+                  <c:v>1521.22</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1625.1600000000003</c:v>
+                  <c:v>1696.92</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1796.96</c:v>
+                  <c:v>1872.62</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1968.76</c:v>
+                  <c:v>2048.3200000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -868,58 +1065,58 @@
                   <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>264.48</c:v>
+                  <c:v>279.58499999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>336.68000000000006</c:v>
+                  <c:v>356.53499999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>408.88</c:v>
+                  <c:v>433.48500000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>481.08</c:v>
+                  <c:v>510.43499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>553.28</c:v>
+                  <c:v>587.38499999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>625.48</c:v>
+                  <c:v>664.33500000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>697.68000000000006</c:v>
+                  <c:v>741.28500000000008</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>769.88</c:v>
+                  <c:v>818.23500000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>842.08</c:v>
+                  <c:v>895.18500000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>914.28</c:v>
+                  <c:v>972.13499999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1111.48</c:v>
+                  <c:v>1174.085</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1308.6799999999998</c:v>
+                  <c:v>1376.0349999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1505.88</c:v>
+                  <c:v>1577.9850000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1703.0800000000002</c:v>
+                  <c:v>1779.9350000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1900.28</c:v>
+                  <c:v>1981.885</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2097.48</c:v>
+                  <c:v>2183.835</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2294.6800000000003</c:v>
+                  <c:v>2385.7849999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2491.88</c:v>
+                  <c:v>2587.7349999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1036,58 +1233,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1260</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1485</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1710</c:v>
+                  <c:v>1779.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1935</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2160</c:v>
+                  <c:v>2240</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2385</c:v>
+                  <c:v>2470</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2610</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2835</c:v>
+                  <c:v>2930</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3060</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1204,58 +1401,58 @@
                   <c:v>310</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>462.52</c:v>
+                  <c:v>465</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>592.72</c:v>
+                  <c:v>603.88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>722.92000000000007</c:v>
+                  <c:v>738.73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>853.12000000000012</c:v>
+                  <c:v>873.57999999999993</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>983.31999999999994</c:v>
+                  <c:v>1008.43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1113.5200000000002</c:v>
+                  <c:v>1143.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1243.7200000000003</c:v>
+                  <c:v>1278.1300000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1373.92</c:v>
+                  <c:v>1412.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1504.1200000000003</c:v>
+                  <c:v>1547.83</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1634.3200000000002</c:v>
+                  <c:v>1682.6799999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1889.5200000000004</c:v>
+                  <c:v>1942.5300000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2144.7199999999998</c:v>
+                  <c:v>2202.3799999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2399.9200000000005</c:v>
+                  <c:v>2462.23</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2655.1200000000003</c:v>
+                  <c:v>2722.08</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2910.32</c:v>
+                  <c:v>2981.93</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3165.5200000000004</c:v>
+                  <c:v>3241.7799999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3420.7200000000003</c:v>
+                  <c:v>3501.6299999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3675.9200000000005</c:v>
+                  <c:v>3761.48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1375,55 +1572,55 @@
                   <c:v>555</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>726.68</c:v>
+                  <c:v>728.9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>889.48</c:v>
+                  <c:v>895.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1052.28</c:v>
+                  <c:v>1061.8999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1215.08</c:v>
+                  <c:v>1228.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1377.88</c:v>
+                  <c:v>1394.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1540.68</c:v>
+                  <c:v>1561.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1703.4799999999998</c:v>
+                  <c:v>1727.8999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1866.28</c:v>
+                  <c:v>1894.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2029.0799999999997</c:v>
+                  <c:v>2060.8999999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2316.88</c:v>
+                  <c:v>2352.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2604.6799999999998</c:v>
+                  <c:v>2643.8999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2892.4799999999996</c:v>
+                  <c:v>2935.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3180.28</c:v>
+                  <c:v>3226.9</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3468.08</c:v>
+                  <c:v>3518.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3755.88</c:v>
+                  <c:v>3809.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4043.68</c:v>
+                  <c:v>4101.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4331.4799999999996</c:v>
+                  <c:v>4392.8999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1741,58 +1938,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1300</c:v>
+                  <c:v>1340</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1450</c:v>
+                  <c:v>1495</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1600</c:v>
+                  <c:v>1649.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1750</c:v>
+                  <c:v>1805</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1900</c:v>
+                  <c:v>1960</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2050</c:v>
+                  <c:v>2115</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2200</c:v>
+                  <c:v>2270</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2350</c:v>
+                  <c:v>2425</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2500</c:v>
+                  <c:v>2580</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1909,58 +2106,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1295</c:v>
+                  <c:v>1337.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1482.5</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1670</c:v>
+                  <c:v>1722.4999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1857.5</c:v>
+                  <c:v>1915</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2045.0000000000002</c:v>
+                  <c:v>2107.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2232.5</c:v>
+                  <c:v>2300</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2420</c:v>
+                  <c:v>2492.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2607.5</c:v>
+                  <c:v>2685</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2795</c:v>
+                  <c:v>2877.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2077,58 +2274,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1260</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1485</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1710</c:v>
+                  <c:v>1779.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1935</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2160</c:v>
+                  <c:v>2240</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2385</c:v>
+                  <c:v>2470</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2610</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2835</c:v>
+                  <c:v>2930</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3060</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2245,58 +2442,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1260</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1457.5</c:v>
+                  <c:v>1555</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1720</c:v>
+                  <c:v>1822.4999999999995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1982.5</c:v>
+                  <c:v>2090</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2245</c:v>
+                  <c:v>2357.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2507.5</c:v>
+                  <c:v>2625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2770</c:v>
+                  <c:v>2892.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3032.5</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3295</c:v>
+                  <c:v>3427.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2413,58 +2610,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1260</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1400</c:v>
+                  <c:v>1545</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1699.9999999999998</c:v>
+                  <c:v>1849.9999999999995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2000</c:v>
+                  <c:v>2155</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2300</c:v>
+                  <c:v>2460</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2600</c:v>
+                  <c:v>2765</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2900</c:v>
+                  <c:v>3070</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3200</c:v>
+                  <c:v>3375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3500</c:v>
+                  <c:v>3680</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3813,61 +4010,61 @@
                   <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126.36000000000001</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>173.16</c:v>
+                  <c:v>186.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.96</c:v>
+                  <c:v>237.12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>266.76</c:v>
+                  <c:v>287.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>313.56</c:v>
+                  <c:v>338.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>360.36</c:v>
+                  <c:v>389.21999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>407.16</c:v>
+                  <c:v>439.92</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>453.96</c:v>
+                  <c:v>490.62</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>500.76000000000005</c:v>
+                  <c:v>541.31999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>547.56000000000006</c:v>
+                  <c:v>592.02</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>634.3599999999999</c:v>
+                  <c:v>662.72</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>731.16000000000008</c:v>
+                  <c:v>763.42000000000007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>827.95999999999992</c:v>
+                  <c:v>864.12</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>924.76</c:v>
+                  <c:v>964.82</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1021.5600000000001</c:v>
+                  <c:v>1065.5200000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1118.3599999999999</c:v>
+                  <c:v>1166.22</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1215.1600000000001</c:v>
+                  <c:v>1266.92</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1311.96</c:v>
+                  <c:v>1367.62</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1408.76</c:v>
+                  <c:v>1468.3200000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3984,58 +4181,58 @@
                   <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>264.48</c:v>
+                  <c:v>279.58499999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>336.68000000000006</c:v>
+                  <c:v>356.53499999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>408.88</c:v>
+                  <c:v>433.48500000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>481.08</c:v>
+                  <c:v>510.43499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>553.28</c:v>
+                  <c:v>587.38499999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>625.48</c:v>
+                  <c:v>664.33500000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>697.68000000000006</c:v>
+                  <c:v>741.28500000000008</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>769.88</c:v>
+                  <c:v>818.23500000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>842.08</c:v>
+                  <c:v>895.18500000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>949.28</c:v>
+                  <c:v>989.63499999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1108.98</c:v>
+                  <c:v>1154.085</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1268.6799999999998</c:v>
+                  <c:v>1318.5349999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1428.38</c:v>
+                  <c:v>1482.9850000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1588.0800000000002</c:v>
+                  <c:v>1647.4349999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1747.78</c:v>
+                  <c:v>1811.885</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1907.48</c:v>
+                  <c:v>1976.335</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2067.1800000000003</c:v>
+                  <c:v>2140.7849999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2226.88</c:v>
+                  <c:v>2305.2349999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4152,58 +4349,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>460</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>560</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>660</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>760</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>860</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1060</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1160</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1260</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1485</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1710</c:v>
+                  <c:v>1779.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1935</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2160</c:v>
+                  <c:v>2240</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2385</c:v>
+                  <c:v>2470</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2610</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2835</c:v>
+                  <c:v>2930</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3060</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4320,58 +4517,58 @@
                   <c:v>310</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>462.52</c:v>
+                  <c:v>465</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>592.72</c:v>
+                  <c:v>603.88</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>722.92000000000007</c:v>
+                  <c:v>738.73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>853.12000000000012</c:v>
+                  <c:v>873.57999999999993</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>983.31999999999994</c:v>
+                  <c:v>1008.43</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1113.5200000000002</c:v>
+                  <c:v>1143.2800000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1243.7200000000003</c:v>
+                  <c:v>1278.1300000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1373.92</c:v>
+                  <c:v>1412.98</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1504.1200000000003</c:v>
+                  <c:v>1547.83</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1634.3200000000002</c:v>
+                  <c:v>1682.6799999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1862.0200000000002</c:v>
+                  <c:v>1947.5300000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2154.7199999999998</c:v>
+                  <c:v>2244.8799999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2447.42</c:v>
+                  <c:v>2542.23</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2740.1200000000003</c:v>
+                  <c:v>2839.58</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3032.82</c:v>
+                  <c:v>3136.93</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3325.5200000000004</c:v>
+                  <c:v>3434.2799999999997</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3618.2200000000003</c:v>
+                  <c:v>3731.6299999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3910.9200000000005</c:v>
+                  <c:v>4028.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4491,55 +4688,55 @@
                   <c:v>555</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>726.68</c:v>
+                  <c:v>728.9</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>889.48</c:v>
+                  <c:v>895.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1052.28</c:v>
+                  <c:v>1061.8999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1215.08</c:v>
+                  <c:v>1228.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1377.88</c:v>
+                  <c:v>1394.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1540.68</c:v>
+                  <c:v>1561.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1703.4799999999998</c:v>
+                  <c:v>1727.8999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1866.28</c:v>
+                  <c:v>1894.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2029.0799999999997</c:v>
+                  <c:v>2060.8999999999996</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2231.88</c:v>
+                  <c:v>2347.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2594.6799999999994</c:v>
+                  <c:v>2713.8999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2957.4799999999996</c:v>
+                  <c:v>3080.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3320.28</c:v>
+                  <c:v>3446.9000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3683.08</c:v>
+                  <c:v>3813.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4045.88</c:v>
+                  <c:v>4179.8999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4408.6799999999994</c:v>
+                  <c:v>4546.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4771.4799999999996</c:v>
+                  <c:v>4912.8999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6529,16 +6726,16 @@
       </c>
       <c r="F38" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G38" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14">
         <f>E38*G38</f>
-        <v>936</v>
+        <v>1014</v>
       </c>
       <c r="J38" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D38,Parameters!$C$6:$G$6,0))</f>
@@ -6550,7 +6747,7 @@
       </c>
       <c r="L38" s="14">
         <f>I38+J38</f>
-        <v>3436</v>
+        <v>3514</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -6573,16 +6770,16 @@
       </c>
       <c r="F39" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.105</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G39" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="14">
         <f>E39*G39</f>
-        <v>1444</v>
+        <v>1539</v>
       </c>
       <c r="J39" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D39,Parameters!$C$6:$G$6,0))</f>
@@ -6594,7 +6791,7 @@
       </c>
       <c r="L39" s="14">
         <f>I39+J39</f>
-        <v>3944</v>
+        <v>4039</v>
       </c>
       <c r="M39" s="1"/>
     </row>
@@ -6617,16 +6814,16 @@
       </c>
       <c r="F40" s="16">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G40" s="16">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="17">
         <f>E40*G40</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J40" s="17">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D40,Parameters!$C$6:$G$6,0))</f>
@@ -6638,7 +6835,7 @@
       </c>
       <c r="L40" s="17">
         <f>I40+J40</f>
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="M40" s="1"/>
     </row>
@@ -6661,16 +6858,16 @@
       </c>
       <c r="F41" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.14500000000000002</v>
+        <v>0.16</v>
       </c>
       <c r="G41" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.84000000000000008</v>
+        <v>0.87</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14">
         <f>E41*G41</f>
-        <v>2604.0000000000005</v>
+        <v>2697</v>
       </c>
       <c r="J41" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D41,Parameters!$C$6:$G$6,0))</f>
@@ -6682,7 +6879,7 @@
       </c>
       <c r="L41" s="14">
         <f>I41+J41</f>
-        <v>5104</v>
+        <v>5197</v>
       </c>
       <c r="M41" s="1"/>
     </row>
@@ -6709,12 +6906,12 @@
       </c>
       <c r="G42" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14">
         <f>E42*G42</f>
-        <v>3256</v>
+        <v>3330</v>
       </c>
       <c r="J42" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D42,Parameters!$C$6:$G$6,0))</f>
@@ -6726,7 +6923,7 @@
       </c>
       <c r="L42" s="14">
         <f>I42+J42</f>
-        <v>5756</v>
+        <v>5830</v>
       </c>
       <c r="M42" s="1"/>
     </row>
@@ -6892,7 +7089,7 @@
       </c>
       <c r="C51" s="14">
         <f t="shared" si="0"/>
-        <v>126.36000000000001</v>
+        <v>130</v>
       </c>
       <c r="D51" s="14">
         <f t="shared" si="1"/>
@@ -6919,19 +7116,19 @@
       </c>
       <c r="C52" s="14">
         <f t="shared" si="0"/>
-        <v>173.16</v>
+        <v>186.42</v>
       </c>
       <c r="D52" s="14">
         <f t="shared" si="1"/>
-        <v>264.48</v>
+        <v>279.58499999999998</v>
       </c>
       <c r="E52" s="14">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="F52" s="14">
         <f t="shared" si="3"/>
-        <v>462.52</v>
+        <v>465</v>
       </c>
       <c r="G52" s="14">
         <f t="shared" si="4"/>
@@ -6946,23 +7143,23 @@
       </c>
       <c r="C53" s="14">
         <f t="shared" si="0"/>
-        <v>219.96</v>
+        <v>237.12</v>
       </c>
       <c r="D53" s="14">
         <f t="shared" si="1"/>
-        <v>336.68000000000006</v>
+        <v>356.53499999999997</v>
       </c>
       <c r="E53" s="14">
         <f t="shared" si="2"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="F53" s="14">
         <f t="shared" si="3"/>
-        <v>592.72</v>
+        <v>603.88</v>
       </c>
       <c r="G53" s="14">
         <f t="shared" si="4"/>
-        <v>726.68</v>
+        <v>728.9</v>
       </c>
       <c r="M53" s="1"/>
     </row>
@@ -6973,23 +7170,23 @@
       </c>
       <c r="C54" s="14">
         <f t="shared" si="0"/>
-        <v>266.76</v>
+        <v>287.82</v>
       </c>
       <c r="D54" s="14">
         <f t="shared" si="1"/>
-        <v>408.88</v>
+        <v>433.48500000000001</v>
       </c>
       <c r="E54" s="14">
         <f t="shared" si="2"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F54" s="14">
         <f t="shared" si="3"/>
-        <v>722.92000000000007</v>
+        <v>738.73</v>
       </c>
       <c r="G54" s="14">
         <f t="shared" si="4"/>
-        <v>889.48</v>
+        <v>895.4</v>
       </c>
       <c r="M54" s="1"/>
     </row>
@@ -7000,23 +7197,23 @@
       </c>
       <c r="C55" s="14">
         <f t="shared" si="0"/>
-        <v>313.56</v>
+        <v>338.52</v>
       </c>
       <c r="D55" s="14">
         <f t="shared" si="1"/>
-        <v>481.08</v>
+        <v>510.43499999999995</v>
       </c>
       <c r="E55" s="14">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="F55" s="14">
         <f t="shared" si="3"/>
-        <v>853.12000000000012</v>
+        <v>873.57999999999993</v>
       </c>
       <c r="G55" s="14">
         <f t="shared" si="4"/>
-        <v>1052.28</v>
+        <v>1061.8999999999999</v>
       </c>
       <c r="M55" s="1"/>
     </row>
@@ -7027,23 +7224,23 @@
       </c>
       <c r="C56" s="14">
         <f t="shared" si="0"/>
-        <v>360.36</v>
+        <v>389.21999999999997</v>
       </c>
       <c r="D56" s="14">
         <f t="shared" si="1"/>
-        <v>553.28</v>
+        <v>587.38499999999999</v>
       </c>
       <c r="E56" s="14">
         <f t="shared" si="2"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="F56" s="14">
         <f t="shared" si="3"/>
-        <v>983.31999999999994</v>
+        <v>1008.43</v>
       </c>
       <c r="G56" s="14">
         <f t="shared" si="4"/>
-        <v>1215.08</v>
+        <v>1228.3999999999999</v>
       </c>
       <c r="M56" s="1"/>
     </row>
@@ -7054,23 +7251,23 @@
       </c>
       <c r="C57" s="14">
         <f t="shared" si="0"/>
-        <v>407.16</v>
+        <v>439.92</v>
       </c>
       <c r="D57" s="14">
         <f t="shared" si="1"/>
-        <v>625.48</v>
+        <v>664.33500000000004</v>
       </c>
       <c r="E57" s="14">
         <f t="shared" si="2"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="F57" s="14">
         <f t="shared" si="3"/>
-        <v>1113.5200000000002</v>
+        <v>1143.2800000000002</v>
       </c>
       <c r="G57" s="14">
         <f t="shared" si="4"/>
-        <v>1377.88</v>
+        <v>1394.9</v>
       </c>
       <c r="M57" s="1"/>
     </row>
@@ -7081,23 +7278,23 @@
       </c>
       <c r="C58" s="14">
         <f t="shared" si="0"/>
-        <v>453.96</v>
+        <v>490.62</v>
       </c>
       <c r="D58" s="14">
         <f t="shared" si="1"/>
-        <v>697.68000000000006</v>
+        <v>741.28500000000008</v>
       </c>
       <c r="E58" s="14">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="F58" s="14">
         <f t="shared" si="3"/>
-        <v>1243.7200000000003</v>
+        <v>1278.1300000000001</v>
       </c>
       <c r="G58" s="14">
         <f t="shared" si="4"/>
-        <v>1540.68</v>
+        <v>1561.4</v>
       </c>
       <c r="M58" s="1"/>
     </row>
@@ -7108,23 +7305,23 @@
       </c>
       <c r="C59" s="14">
         <f t="shared" si="0"/>
-        <v>500.76000000000005</v>
+        <v>541.31999999999994</v>
       </c>
       <c r="D59" s="14">
         <f t="shared" si="1"/>
-        <v>769.88</v>
+        <v>818.23500000000001</v>
       </c>
       <c r="E59" s="14">
         <f t="shared" si="2"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="F59" s="14">
         <f t="shared" si="3"/>
-        <v>1373.92</v>
+        <v>1412.98</v>
       </c>
       <c r="G59" s="14">
         <f t="shared" si="4"/>
-        <v>1703.4799999999998</v>
+        <v>1727.8999999999999</v>
       </c>
       <c r="M59" s="1"/>
     </row>
@@ -7135,23 +7332,23 @@
       </c>
       <c r="C60" s="14">
         <f t="shared" si="0"/>
-        <v>547.56000000000006</v>
+        <v>592.02</v>
       </c>
       <c r="D60" s="14">
         <f t="shared" si="1"/>
-        <v>842.08</v>
+        <v>895.18500000000006</v>
       </c>
       <c r="E60" s="14">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="F60" s="14">
         <f t="shared" si="3"/>
-        <v>1504.1200000000003</v>
+        <v>1547.83</v>
       </c>
       <c r="G60" s="14">
         <f t="shared" si="4"/>
-        <v>1866.28</v>
+        <v>1894.4</v>
       </c>
       <c r="M60" s="1"/>
     </row>
@@ -7162,23 +7359,23 @@
       </c>
       <c r="C61" s="14">
         <f t="shared" si="0"/>
-        <v>594.36</v>
+        <v>642.72</v>
       </c>
       <c r="D61" s="14">
         <f t="shared" si="1"/>
-        <v>914.28</v>
+        <v>972.13499999999999</v>
       </c>
       <c r="E61" s="14">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1320</v>
       </c>
       <c r="F61" s="14">
         <f t="shared" si="3"/>
-        <v>1634.3200000000002</v>
+        <v>1682.6799999999998</v>
       </c>
       <c r="G61" s="14">
         <f t="shared" si="4"/>
-        <v>2029.0799999999997</v>
+        <v>2060.8999999999996</v>
       </c>
       <c r="M61" s="1"/>
     </row>
@@ -7189,23 +7386,23 @@
       </c>
       <c r="C62" s="14">
         <f t="shared" si="0"/>
-        <v>766.1600000000002</v>
+        <v>818.42000000000019</v>
       </c>
       <c r="D62" s="14">
         <f t="shared" si="1"/>
-        <v>1111.48</v>
+        <v>1174.085</v>
       </c>
       <c r="E62" s="14">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1550</v>
       </c>
       <c r="F62" s="14">
         <f t="shared" si="3"/>
-        <v>1889.5200000000004</v>
+        <v>1942.5300000000002</v>
       </c>
       <c r="G62" s="14">
         <f t="shared" si="4"/>
-        <v>2316.88</v>
+        <v>2352.3999999999996</v>
       </c>
       <c r="M62" s="1"/>
     </row>
@@ -7216,23 +7413,23 @@
       </c>
       <c r="C63" s="14">
         <f t="shared" si="0"/>
-        <v>937.96</v>
+        <v>994.11999999999989</v>
       </c>
       <c r="D63" s="14">
         <f t="shared" si="1"/>
-        <v>1308.6799999999998</v>
+        <v>1376.0349999999999</v>
       </c>
       <c r="E63" s="14">
         <f t="shared" si="2"/>
-        <v>1710</v>
+        <v>1779.9999999999998</v>
       </c>
       <c r="F63" s="14">
         <f t="shared" si="3"/>
-        <v>2144.7199999999998</v>
+        <v>2202.3799999999997</v>
       </c>
       <c r="G63" s="14">
         <f t="shared" si="4"/>
-        <v>2604.6799999999998</v>
+        <v>2643.8999999999996</v>
       </c>
       <c r="M63" s="1"/>
     </row>
@@ -7243,23 +7440,23 @@
       </c>
       <c r="C64" s="14">
         <f t="shared" si="0"/>
-        <v>1109.76</v>
+        <v>1169.8200000000002</v>
       </c>
       <c r="D64" s="14">
         <f t="shared" si="1"/>
-        <v>1505.88</v>
+        <v>1577.9850000000001</v>
       </c>
       <c r="E64" s="14">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2010</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="3"/>
-        <v>2399.9200000000005</v>
+        <v>2462.23</v>
       </c>
       <c r="G64" s="14">
         <f t="shared" si="4"/>
-        <v>2892.4799999999996</v>
+        <v>2935.3999999999996</v>
       </c>
       <c r="M64" s="1"/>
     </row>
@@ -7270,23 +7467,23 @@
       </c>
       <c r="C65" s="14">
         <f t="shared" si="0"/>
-        <v>1281.5600000000002</v>
+        <v>1345.5200000000002</v>
       </c>
       <c r="D65" s="14">
         <f t="shared" si="1"/>
-        <v>1703.0800000000002</v>
+        <v>1779.9350000000002</v>
       </c>
       <c r="E65" s="14">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2240</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" si="3"/>
-        <v>2655.1200000000003</v>
+        <v>2722.08</v>
       </c>
       <c r="G65" s="14">
         <f t="shared" si="4"/>
-        <v>3180.28</v>
+        <v>3226.9</v>
       </c>
       <c r="M65" s="1"/>
     </row>
@@ -7297,23 +7494,23 @@
       </c>
       <c r="C66" s="14">
         <f t="shared" si="0"/>
-        <v>1453.3600000000001</v>
+        <v>1521.22</v>
       </c>
       <c r="D66" s="14">
         <f t="shared" si="1"/>
-        <v>1900.28</v>
+        <v>1981.885</v>
       </c>
       <c r="E66" s="14">
         <f t="shared" si="2"/>
-        <v>2385</v>
+        <v>2470</v>
       </c>
       <c r="F66" s="14">
         <f t="shared" si="3"/>
-        <v>2910.32</v>
+        <v>2981.93</v>
       </c>
       <c r="G66" s="14">
         <f t="shared" si="4"/>
-        <v>3468.08</v>
+        <v>3518.3999999999996</v>
       </c>
       <c r="M66" s="1"/>
     </row>
@@ -7324,23 +7521,23 @@
       </c>
       <c r="C67" s="14">
         <f t="shared" si="0"/>
-        <v>1625.1600000000003</v>
+        <v>1696.92</v>
       </c>
       <c r="D67" s="14">
         <f t="shared" si="1"/>
-        <v>2097.48</v>
+        <v>2183.835</v>
       </c>
       <c r="E67" s="14">
         <f t="shared" si="2"/>
-        <v>2610</v>
+        <v>2700</v>
       </c>
       <c r="F67" s="14">
         <f t="shared" si="3"/>
-        <v>3165.5200000000004</v>
+        <v>3241.7799999999997</v>
       </c>
       <c r="G67" s="14">
         <f t="shared" si="4"/>
-        <v>3755.88</v>
+        <v>3809.9</v>
       </c>
       <c r="M67" s="1"/>
     </row>
@@ -7351,23 +7548,23 @@
       </c>
       <c r="C68" s="14">
         <f t="shared" si="0"/>
-        <v>1796.96</v>
+        <v>1872.62</v>
       </c>
       <c r="D68" s="14">
         <f t="shared" si="1"/>
-        <v>2294.6800000000003</v>
+        <v>2385.7849999999999</v>
       </c>
       <c r="E68" s="14">
         <f t="shared" si="2"/>
-        <v>2835</v>
+        <v>2930</v>
       </c>
       <c r="F68" s="14">
         <f t="shared" si="3"/>
-        <v>3420.7200000000003</v>
+        <v>3501.6299999999997</v>
       </c>
       <c r="G68" s="14">
         <f t="shared" si="4"/>
-        <v>4043.68</v>
+        <v>4101.3999999999996</v>
       </c>
       <c r="M68" s="1"/>
     </row>
@@ -7378,23 +7575,23 @@
       </c>
       <c r="C69" s="14">
         <f t="shared" si="0"/>
-        <v>1968.76</v>
+        <v>2048.3200000000002</v>
       </c>
       <c r="D69" s="14">
         <f t="shared" si="1"/>
-        <v>2491.88</v>
+        <v>2587.7349999999997</v>
       </c>
       <c r="E69" s="14">
         <f t="shared" si="2"/>
-        <v>3060</v>
+        <v>3160</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="3"/>
-        <v>3675.9200000000005</v>
+        <v>3761.48</v>
       </c>
       <c r="G69" s="14">
         <f t="shared" si="4"/>
-        <v>4331.4799999999996</v>
+        <v>4392.8999999999996</v>
       </c>
       <c r="M69" s="1"/>
     </row>
@@ -7402,19 +7599,19 @@
       <c r="A70" s="1"/>
       <c r="C70">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E70">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G70">
         <f t="shared" si="4"/>
@@ -7426,19 +7623,19 @@
       <c r="A71" s="1"/>
       <c r="C71">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D71">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E71">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F71">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G71">
         <f t="shared" si="4"/>
@@ -7450,19 +7647,19 @@
       <c r="A72" s="1"/>
       <c r="C72">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D72">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E72">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F72">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G72">
         <f t="shared" si="4"/>
@@ -7474,19 +7671,19 @@
       <c r="A73" s="1"/>
       <c r="C73">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D73">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E73">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F73">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G73">
         <f t="shared" si="4"/>
@@ -8128,16 +8325,16 @@
       </c>
       <c r="F38" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G38" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14">
         <f>E38*G38</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J38" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D38,Parameters!$C$6:$G$6,0))</f>
@@ -8145,11 +8342,11 @@
       </c>
       <c r="K38" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L38" s="14">
         <f>I38+J38</f>
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -8172,16 +8369,16 @@
       </c>
       <c r="F39" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G39" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="14">
         <f>E39*G39</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J39" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D39,Parameters!$C$6:$G$6,0))</f>
@@ -8189,11 +8386,11 @@
       </c>
       <c r="K39" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="L39" s="14">
         <f>I39+J39</f>
-        <v>3750</v>
+        <v>3850</v>
       </c>
       <c r="M39" s="1"/>
     </row>
@@ -8216,16 +8413,16 @@
       </c>
       <c r="F40" s="16">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G40" s="16">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="17">
         <f>E40*G40</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J40" s="17">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D40,Parameters!$C$6:$G$6,0))</f>
@@ -8237,7 +8434,7 @@
       </c>
       <c r="L40" s="17">
         <f>I40+J40</f>
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="M40" s="1"/>
     </row>
@@ -8260,16 +8457,16 @@
       </c>
       <c r="F41" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G41" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14">
         <f>E41*G41</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J41" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D41,Parameters!$C$6:$G$6,0))</f>
@@ -8277,11 +8474,11 @@
       </c>
       <c r="K41" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="L41" s="14">
         <f>I41+J41</f>
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="M41" s="1"/>
     </row>
@@ -8304,16 +8501,16 @@
       </c>
       <c r="F42" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G42" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14">
         <f>E42*G42</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J42" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D42,Parameters!$C$6:$G$6,0))</f>
@@ -8321,11 +8518,11 @@
       </c>
       <c r="K42" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="L42" s="14">
         <f>I42+J42</f>
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="M42" s="1"/>
     </row>
@@ -8518,23 +8715,23 @@
       </c>
       <c r="C52" s="14">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="D52" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="E52" s="14">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="F52" s="14">
         <f t="shared" si="3"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="G52" s="14">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="M52" s="1"/>
     </row>
@@ -8545,23 +8742,23 @@
       </c>
       <c r="C53" s="14">
         <f t="shared" si="0"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="D53" s="14">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="E53" s="14">
         <f t="shared" si="2"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="F53" s="14">
         <f t="shared" si="3"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G53" s="14">
         <f t="shared" si="4"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="M53" s="1"/>
     </row>
@@ -8572,23 +8769,23 @@
       </c>
       <c r="C54" s="14">
         <f t="shared" si="0"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="D54" s="14">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="E54" s="14">
         <f t="shared" si="2"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F54" s="14">
         <f t="shared" si="3"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="G54" s="14">
         <f t="shared" si="4"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="M54" s="1"/>
     </row>
@@ -8599,23 +8796,23 @@
       </c>
       <c r="C55" s="14">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="D55" s="14">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="E55" s="14">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="F55" s="14">
         <f t="shared" si="3"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="G55" s="14">
         <f t="shared" si="4"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="M55" s="1"/>
     </row>
@@ -8626,23 +8823,23 @@
       </c>
       <c r="C56" s="14">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="D56" s="14">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="E56" s="14">
         <f t="shared" si="2"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="F56" s="14">
         <f t="shared" si="3"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="G56" s="14">
         <f t="shared" si="4"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="M56" s="1"/>
     </row>
@@ -8653,23 +8850,23 @@
       </c>
       <c r="C57" s="14">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="D57" s="14">
         <f t="shared" si="1"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="E57" s="14">
         <f t="shared" si="2"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="F57" s="14">
         <f t="shared" si="3"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="G57" s="14">
         <f t="shared" si="4"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="M57" s="1"/>
     </row>
@@ -8680,23 +8877,23 @@
       </c>
       <c r="C58" s="14">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="D58" s="14">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="E58" s="14">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="F58" s="14">
         <f t="shared" si="3"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="G58" s="14">
         <f t="shared" si="4"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="M58" s="1"/>
     </row>
@@ -8707,23 +8904,23 @@
       </c>
       <c r="C59" s="14">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="D59" s="14">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="E59" s="14">
         <f t="shared" si="2"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="F59" s="14">
         <f t="shared" si="3"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="G59" s="14">
         <f t="shared" si="4"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="M59" s="1"/>
     </row>
@@ -8734,23 +8931,23 @@
       </c>
       <c r="C60" s="14">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="D60" s="14">
         <f t="shared" si="1"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="E60" s="14">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="F60" s="14">
         <f t="shared" si="3"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="G60" s="14">
         <f t="shared" si="4"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="M60" s="1"/>
     </row>
@@ -8761,23 +8958,23 @@
       </c>
       <c r="C61" s="14">
         <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1340</v>
       </c>
       <c r="D61" s="14">
         <f t="shared" si="1"/>
-        <v>1295</v>
+        <v>1337.5</v>
       </c>
       <c r="E61" s="14">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1320</v>
       </c>
       <c r="F61" s="14">
         <f t="shared" si="3"/>
-        <v>1260</v>
+        <v>1320</v>
       </c>
       <c r="G61" s="14">
         <f t="shared" si="4"/>
-        <v>1260</v>
+        <v>1320</v>
       </c>
       <c r="M61" s="1"/>
     </row>
@@ -8788,23 +8985,23 @@
       </c>
       <c r="C62" s="14">
         <f t="shared" si="0"/>
-        <v>1450</v>
+        <v>1495</v>
       </c>
       <c r="D62" s="14">
         <f t="shared" si="1"/>
-        <v>1482.5</v>
+        <v>1530</v>
       </c>
       <c r="E62" s="14">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1550</v>
       </c>
       <c r="F62" s="14">
         <f t="shared" si="3"/>
-        <v>1457.5</v>
+        <v>1555</v>
       </c>
       <c r="G62" s="14">
         <f t="shared" si="4"/>
-        <v>1400</v>
+        <v>1545</v>
       </c>
       <c r="M62" s="1"/>
     </row>
@@ -8815,23 +9012,23 @@
       </c>
       <c r="C63" s="14">
         <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>1649.9999999999998</v>
       </c>
       <c r="D63" s="14">
         <f t="shared" si="1"/>
-        <v>1670</v>
+        <v>1722.4999999999998</v>
       </c>
       <c r="E63" s="14">
         <f t="shared" si="2"/>
-        <v>1710</v>
+        <v>1779.9999999999998</v>
       </c>
       <c r="F63" s="14">
         <f t="shared" si="3"/>
-        <v>1720</v>
+        <v>1822.4999999999995</v>
       </c>
       <c r="G63" s="14">
         <f t="shared" si="4"/>
-        <v>1699.9999999999998</v>
+        <v>1849.9999999999995</v>
       </c>
       <c r="M63" s="1"/>
     </row>
@@ -8842,23 +9039,23 @@
       </c>
       <c r="C64" s="14">
         <f t="shared" si="0"/>
-        <v>1750</v>
+        <v>1805</v>
       </c>
       <c r="D64" s="14">
         <f t="shared" si="1"/>
-        <v>1857.5</v>
+        <v>1915</v>
       </c>
       <c r="E64" s="14">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2010</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="3"/>
-        <v>1982.5</v>
+        <v>2090</v>
       </c>
       <c r="G64" s="14">
         <f t="shared" si="4"/>
-        <v>2000</v>
+        <v>2155</v>
       </c>
       <c r="M64" s="1"/>
     </row>
@@ -8869,23 +9066,23 @@
       </c>
       <c r="C65" s="14">
         <f t="shared" si="0"/>
-        <v>1900</v>
+        <v>1960</v>
       </c>
       <c r="D65" s="14">
         <f t="shared" si="1"/>
-        <v>2045.0000000000002</v>
+        <v>2107.5</v>
       </c>
       <c r="E65" s="14">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2240</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" si="3"/>
-        <v>2245</v>
+        <v>2357.5</v>
       </c>
       <c r="G65" s="14">
         <f t="shared" si="4"/>
-        <v>2300</v>
+        <v>2460</v>
       </c>
       <c r="M65" s="1"/>
     </row>
@@ -8896,23 +9093,23 @@
       </c>
       <c r="C66" s="14">
         <f t="shared" si="0"/>
-        <v>2050</v>
+        <v>2115</v>
       </c>
       <c r="D66" s="14">
         <f t="shared" si="1"/>
-        <v>2232.5</v>
+        <v>2300</v>
       </c>
       <c r="E66" s="14">
         <f t="shared" si="2"/>
-        <v>2385</v>
+        <v>2470</v>
       </c>
       <c r="F66" s="14">
         <f t="shared" si="3"/>
-        <v>2507.5</v>
+        <v>2625</v>
       </c>
       <c r="G66" s="14">
         <f t="shared" si="4"/>
-        <v>2600</v>
+        <v>2765</v>
       </c>
       <c r="M66" s="1"/>
     </row>
@@ -8923,23 +9120,23 @@
       </c>
       <c r="C67" s="14">
         <f t="shared" si="0"/>
-        <v>2200</v>
+        <v>2270</v>
       </c>
       <c r="D67" s="14">
         <f t="shared" si="1"/>
-        <v>2420</v>
+        <v>2492.5</v>
       </c>
       <c r="E67" s="14">
         <f t="shared" si="2"/>
-        <v>2610</v>
+        <v>2700</v>
       </c>
       <c r="F67" s="14">
         <f t="shared" si="3"/>
-        <v>2770</v>
+        <v>2892.5</v>
       </c>
       <c r="G67" s="14">
         <f t="shared" si="4"/>
-        <v>2900</v>
+        <v>3070</v>
       </c>
       <c r="M67" s="1"/>
     </row>
@@ -8950,23 +9147,23 @@
       </c>
       <c r="C68" s="14">
         <f t="shared" si="0"/>
-        <v>2350</v>
+        <v>2425</v>
       </c>
       <c r="D68" s="14">
         <f t="shared" si="1"/>
-        <v>2607.5</v>
+        <v>2685</v>
       </c>
       <c r="E68" s="14">
         <f t="shared" si="2"/>
-        <v>2835</v>
+        <v>2930</v>
       </c>
       <c r="F68" s="14">
         <f t="shared" si="3"/>
-        <v>3032.5</v>
+        <v>3160</v>
       </c>
       <c r="G68" s="14">
         <f t="shared" si="4"/>
-        <v>3200</v>
+        <v>3375</v>
       </c>
       <c r="M68" s="1"/>
     </row>
@@ -8977,23 +9174,23 @@
       </c>
       <c r="C69" s="14">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>2580</v>
       </c>
       <c r="D69" s="14">
         <f t="shared" si="1"/>
-        <v>2795</v>
+        <v>2877.5</v>
       </c>
       <c r="E69" s="14">
         <f t="shared" si="2"/>
-        <v>3060</v>
+        <v>3160</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="3"/>
-        <v>3295</v>
+        <v>3427.5</v>
       </c>
       <c r="G69" s="14">
         <f t="shared" si="4"/>
-        <v>3500</v>
+        <v>3680</v>
       </c>
       <c r="M69" s="1"/>
     </row>
@@ -9001,23 +9198,23 @@
       <c r="A70" s="1"/>
       <c r="C70">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E70">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="G70">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="M70" s="1"/>
     </row>
@@ -9025,23 +9222,23 @@
       <c r="A71" s="1"/>
       <c r="C71">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D71">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E71">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F71">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="G71">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="M71" s="1"/>
     </row>
@@ -9049,23 +9246,23 @@
       <c r="A72" s="1"/>
       <c r="C72">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D72">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E72">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F72">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="G72">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="M72" s="1"/>
     </row>
@@ -9073,23 +9270,23 @@
       <c r="A73" s="1"/>
       <c r="C73">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="D73">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="E73">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F73">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="G73">
         <f t="shared" si="4"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="M73" s="1"/>
     </row>
@@ -9163,7 +9360,7 @@
       <c r="A3" s="20"/>
       <c r="B3" s="28" t="str">
         <f>"Rally2 Gravel · "&amp;Parameters!E35&amp;"；单一回弹旋钮，LSR：−40 / −30 / −20 / −10 / 0"</f>
-        <v>Rally2 Gravel · Type-B；单一回弹旋钮，LSR：−40 / −30 / −20 / −10 / 0</v>
+        <v>Rally2 Gravel · Type-A；单一回弹旋钮，LSR：−40 / −30 / −20 / −10 / 0</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -11389,16 +11586,16 @@
       </c>
       <c r="F38" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="G38" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14">
         <f>E38*G38</f>
-        <v>936</v>
+        <v>1014</v>
       </c>
       <c r="J38" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D38,Parameters!$C$6:$G$6,0))</f>
@@ -11406,11 +11603,11 @@
       </c>
       <c r="K38" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D38,Parameters!$C$6:$G$6,0))</f>
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L38" s="14">
         <f>I38+J38</f>
-        <v>1936</v>
+        <v>2014</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -11433,16 +11630,16 @@
       </c>
       <c r="F39" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.105</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G39" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="14">
         <f>E39*G39</f>
-        <v>1444</v>
+        <v>1539</v>
       </c>
       <c r="J39" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D39,Parameters!$C$6:$G$6,0))</f>
@@ -11450,11 +11647,11 @@
       </c>
       <c r="K39" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D39,Parameters!$C$6:$G$6,0))</f>
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="L39" s="14">
         <f>I39+J39</f>
-        <v>3194</v>
+        <v>3289</v>
       </c>
       <c r="M39" s="1"/>
     </row>
@@ -11477,16 +11674,16 @@
       </c>
       <c r="F40" s="16">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G40" s="16">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C40,Parameters!$C$6:$G$6,0))</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="H40" s="16"/>
       <c r="I40" s="17">
         <f>E40*G40</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J40" s="17">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D40,Parameters!$C$6:$G$6,0))</f>
@@ -11498,7 +11695,7 @@
       </c>
       <c r="L40" s="17">
         <f>I40+J40</f>
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="M40" s="1"/>
     </row>
@@ -11521,16 +11718,16 @@
       </c>
       <c r="F41" s="13">
         <f>INDEX(Parameters!$C$8:$G$8,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.14500000000000002</v>
+        <v>0.16</v>
       </c>
       <c r="G41" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.84000000000000008</v>
+        <v>0.87</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14">
         <f>E41*G41</f>
-        <v>2604.0000000000005</v>
+        <v>2697</v>
       </c>
       <c r="J41" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D41,Parameters!$C$6:$G$6,0))</f>
@@ -11538,11 +11735,11 @@
       </c>
       <c r="K41" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D41,Parameters!$C$6:$G$6,0))</f>
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="L41" s="14">
         <f>I41+J41</f>
-        <v>5854</v>
+        <v>5947</v>
       </c>
       <c r="M41" s="1"/>
     </row>
@@ -11569,12 +11766,12 @@
       </c>
       <c r="G42" s="13">
         <f>INDEX(Parameters!$C$9:$G$9,1,MATCH($C42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14">
         <f>E42*G42</f>
-        <v>3256</v>
+        <v>3330</v>
       </c>
       <c r="J42" s="14">
         <f>INDEX(Parameters!$C$10:$G$10,1,MATCH($D42,Parameters!$C$6:$G$6,0))</f>
@@ -11582,11 +11779,11 @@
       </c>
       <c r="K42" s="13">
         <f>INDEX(Parameters!$C$11:$G$11,1,MATCH($D42,Parameters!$C$6:$G$6,0))</f>
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="L42" s="14">
         <f>I42+J42</f>
-        <v>7256</v>
+        <v>7330</v>
       </c>
       <c r="M42" s="1"/>
     </row>
@@ -11812,7 +12009,7 @@
       </c>
       <c r="C51" s="14">
         <f t="shared" si="0"/>
-        <v>126.36000000000001</v>
+        <v>130</v>
       </c>
       <c r="D51" s="14">
         <f t="shared" si="1"/>
@@ -11859,19 +12056,19 @@
       </c>
       <c r="C52" s="14">
         <f t="shared" si="0"/>
-        <v>173.16</v>
+        <v>186.42</v>
       </c>
       <c r="D52" s="14">
         <f t="shared" si="1"/>
-        <v>264.48</v>
+        <v>279.58499999999998</v>
       </c>
       <c r="E52" s="14">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="F52" s="14">
         <f t="shared" si="3"/>
-        <v>462.52</v>
+        <v>465</v>
       </c>
       <c r="G52" s="14">
         <f t="shared" si="4"/>
@@ -11906,23 +12103,23 @@
       </c>
       <c r="C53" s="14">
         <f t="shared" si="0"/>
-        <v>219.96</v>
+        <v>237.12</v>
       </c>
       <c r="D53" s="14">
         <f t="shared" si="1"/>
-        <v>336.68000000000006</v>
+        <v>356.53499999999997</v>
       </c>
       <c r="E53" s="14">
         <f t="shared" si="2"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="F53" s="14">
         <f t="shared" si="3"/>
-        <v>592.72</v>
+        <v>603.88</v>
       </c>
       <c r="G53" s="14">
         <f t="shared" si="4"/>
-        <v>726.68</v>
+        <v>728.9</v>
       </c>
       <c r="H53" s="1">
         <f>-'LSR Sweep'!C53</f>
@@ -11953,23 +12150,23 @@
       </c>
       <c r="C54" s="14">
         <f t="shared" si="0"/>
-        <v>266.76</v>
+        <v>287.82</v>
       </c>
       <c r="D54" s="14">
         <f t="shared" si="1"/>
-        <v>408.88</v>
+        <v>433.48500000000001</v>
       </c>
       <c r="E54" s="14">
         <f t="shared" si="2"/>
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F54" s="14">
         <f t="shared" si="3"/>
-        <v>722.92000000000007</v>
+        <v>738.73</v>
       </c>
       <c r="G54" s="14">
         <f t="shared" si="4"/>
-        <v>889.48</v>
+        <v>895.4</v>
       </c>
       <c r="H54" s="1">
         <f>-'LSR Sweep'!C54</f>
@@ -12000,23 +12197,23 @@
       </c>
       <c r="C55" s="14">
         <f t="shared" si="0"/>
-        <v>313.56</v>
+        <v>338.52</v>
       </c>
       <c r="D55" s="14">
         <f t="shared" si="1"/>
-        <v>481.08</v>
+        <v>510.43499999999995</v>
       </c>
       <c r="E55" s="14">
         <f t="shared" si="2"/>
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="F55" s="14">
         <f t="shared" si="3"/>
-        <v>853.12000000000012</v>
+        <v>873.57999999999993</v>
       </c>
       <c r="G55" s="14">
         <f t="shared" si="4"/>
-        <v>1052.28</v>
+        <v>1061.8999999999999</v>
       </c>
       <c r="H55" s="1">
         <f>-'LSR Sweep'!C55</f>
@@ -12047,23 +12244,23 @@
       </c>
       <c r="C56" s="14">
         <f t="shared" si="0"/>
-        <v>360.36</v>
+        <v>389.21999999999997</v>
       </c>
       <c r="D56" s="14">
         <f t="shared" si="1"/>
-        <v>553.28</v>
+        <v>587.38499999999999</v>
       </c>
       <c r="E56" s="14">
         <f t="shared" si="2"/>
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="F56" s="14">
         <f t="shared" si="3"/>
-        <v>983.31999999999994</v>
+        <v>1008.43</v>
       </c>
       <c r="G56" s="14">
         <f t="shared" si="4"/>
-        <v>1215.08</v>
+        <v>1228.3999999999999</v>
       </c>
       <c r="H56" s="1">
         <f>-'LSR Sweep'!C56</f>
@@ -12094,23 +12291,23 @@
       </c>
       <c r="C57" s="14">
         <f t="shared" si="0"/>
-        <v>407.16</v>
+        <v>439.92</v>
       </c>
       <c r="D57" s="14">
         <f t="shared" si="1"/>
-        <v>625.48</v>
+        <v>664.33500000000004</v>
       </c>
       <c r="E57" s="14">
         <f t="shared" si="2"/>
-        <v>860</v>
+        <v>900</v>
       </c>
       <c r="F57" s="14">
         <f t="shared" si="3"/>
-        <v>1113.5200000000002</v>
+        <v>1143.2800000000002</v>
       </c>
       <c r="G57" s="14">
         <f t="shared" si="4"/>
-        <v>1377.88</v>
+        <v>1394.9</v>
       </c>
       <c r="H57" s="1">
         <f>-'LSR Sweep'!C57</f>
@@ -12141,23 +12338,23 @@
       </c>
       <c r="C58" s="14">
         <f t="shared" si="0"/>
-        <v>453.96</v>
+        <v>490.62</v>
       </c>
       <c r="D58" s="14">
         <f t="shared" si="1"/>
-        <v>697.68000000000006</v>
+        <v>741.28500000000008</v>
       </c>
       <c r="E58" s="14">
         <f t="shared" si="2"/>
-        <v>960</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="F58" s="14">
         <f t="shared" si="3"/>
-        <v>1243.7200000000003</v>
+        <v>1278.1300000000001</v>
       </c>
       <c r="G58" s="14">
         <f t="shared" si="4"/>
-        <v>1540.68</v>
+        <v>1561.4</v>
       </c>
       <c r="H58" s="1">
         <f>-'LSR Sweep'!C58</f>
@@ -12188,23 +12385,23 @@
       </c>
       <c r="C59" s="14">
         <f t="shared" si="0"/>
-        <v>500.76000000000005</v>
+        <v>541.31999999999994</v>
       </c>
       <c r="D59" s="14">
         <f t="shared" si="1"/>
-        <v>769.88</v>
+        <v>818.23500000000001</v>
       </c>
       <c r="E59" s="14">
         <f t="shared" si="2"/>
-        <v>1060</v>
+        <v>1110</v>
       </c>
       <c r="F59" s="14">
         <f t="shared" si="3"/>
-        <v>1373.92</v>
+        <v>1412.98</v>
       </c>
       <c r="G59" s="14">
         <f t="shared" si="4"/>
-        <v>1703.4799999999998</v>
+        <v>1727.8999999999999</v>
       </c>
       <c r="H59" s="1">
         <f>-'LSR Sweep'!C59</f>
@@ -12235,23 +12432,23 @@
       </c>
       <c r="C60" s="14">
         <f t="shared" si="0"/>
-        <v>547.56000000000006</v>
+        <v>592.02</v>
       </c>
       <c r="D60" s="14">
         <f t="shared" si="1"/>
-        <v>842.08</v>
+        <v>895.18500000000006</v>
       </c>
       <c r="E60" s="14">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1215</v>
       </c>
       <c r="F60" s="14">
         <f t="shared" si="3"/>
-        <v>1504.1200000000003</v>
+        <v>1547.83</v>
       </c>
       <c r="G60" s="14">
         <f t="shared" si="4"/>
-        <v>1866.28</v>
+        <v>1894.4</v>
       </c>
       <c r="H60" s="1">
         <f>-'LSR Sweep'!C60</f>
@@ -12282,23 +12479,23 @@
       </c>
       <c r="C61" s="14">
         <f t="shared" si="0"/>
-        <v>634.3599999999999</v>
+        <v>662.72</v>
       </c>
       <c r="D61" s="14">
         <f t="shared" si="1"/>
-        <v>949.28</v>
+        <v>989.63499999999999</v>
       </c>
       <c r="E61" s="14">
         <f t="shared" si="2"/>
-        <v>1260</v>
+        <v>1320</v>
       </c>
       <c r="F61" s="14">
         <f t="shared" si="3"/>
-        <v>1634.3200000000002</v>
+        <v>1682.6799999999998</v>
       </c>
       <c r="G61" s="14">
         <f t="shared" si="4"/>
-        <v>2029.0799999999997</v>
+        <v>2060.8999999999996</v>
       </c>
       <c r="H61" s="1">
         <f>-'LSR Sweep'!C61</f>
@@ -12329,23 +12526,23 @@
       </c>
       <c r="C62" s="14">
         <f t="shared" si="0"/>
-        <v>731.16000000000008</v>
+        <v>763.42000000000007</v>
       </c>
       <c r="D62" s="14">
         <f t="shared" si="1"/>
-        <v>1108.98</v>
+        <v>1154.085</v>
       </c>
       <c r="E62" s="14">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1550</v>
       </c>
       <c r="F62" s="14">
         <f t="shared" si="3"/>
-        <v>1862.0200000000002</v>
+        <v>1947.5300000000002</v>
       </c>
       <c r="G62" s="14">
         <f t="shared" si="4"/>
-        <v>2231.88</v>
+        <v>2347.3999999999996</v>
       </c>
       <c r="H62" s="1">
         <f>-'LSR Sweep'!C62</f>
@@ -12376,23 +12573,23 @@
       </c>
       <c r="C63" s="14">
         <f t="shared" si="0"/>
-        <v>827.95999999999992</v>
+        <v>864.12</v>
       </c>
       <c r="D63" s="14">
         <f t="shared" si="1"/>
-        <v>1268.6799999999998</v>
+        <v>1318.5349999999999</v>
       </c>
       <c r="E63" s="14">
         <f t="shared" si="2"/>
-        <v>1710</v>
+        <v>1779.9999999999998</v>
       </c>
       <c r="F63" s="14">
         <f t="shared" si="3"/>
-        <v>2154.7199999999998</v>
+        <v>2244.8799999999997</v>
       </c>
       <c r="G63" s="14">
         <f t="shared" si="4"/>
-        <v>2594.6799999999994</v>
+        <v>2713.8999999999996</v>
       </c>
       <c r="H63" s="1">
         <f>-'LSR Sweep'!C63</f>
@@ -12423,23 +12620,23 @@
       </c>
       <c r="C64" s="14">
         <f t="shared" si="0"/>
-        <v>924.76</v>
+        <v>964.82</v>
       </c>
       <c r="D64" s="14">
         <f t="shared" si="1"/>
-        <v>1428.38</v>
+        <v>1482.9850000000001</v>
       </c>
       <c r="E64" s="14">
         <f t="shared" si="2"/>
-        <v>1935</v>
+        <v>2010</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="3"/>
-        <v>2447.42</v>
+        <v>2542.23</v>
       </c>
       <c r="G64" s="14">
         <f t="shared" si="4"/>
-        <v>2957.4799999999996</v>
+        <v>3080.3999999999996</v>
       </c>
       <c r="H64" s="1">
         <f>-'LSR Sweep'!C64</f>
@@ -12470,23 +12667,23 @@
       </c>
       <c r="C65" s="14">
         <f t="shared" si="0"/>
-        <v>1021.5600000000001</v>
+        <v>1065.5200000000002</v>
       </c>
       <c r="D65" s="14">
         <f t="shared" si="1"/>
-        <v>1588.0800000000002</v>
+        <v>1647.4349999999999</v>
       </c>
       <c r="E65" s="14">
         <f t="shared" si="2"/>
-        <v>2160</v>
+        <v>2240</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" si="3"/>
-        <v>2740.1200000000003</v>
+        <v>2839.58</v>
       </c>
       <c r="G65" s="14">
         <f t="shared" si="4"/>
-        <v>3320.28</v>
+        <v>3446.9000000000005</v>
       </c>
       <c r="H65" s="1">
         <f>-'LSR Sweep'!C65</f>
@@ -12517,23 +12714,23 @@
       </c>
       <c r="C66" s="14">
         <f t="shared" si="0"/>
-        <v>1118.3599999999999</v>
+        <v>1166.22</v>
       </c>
       <c r="D66" s="14">
         <f t="shared" si="1"/>
-        <v>1747.78</v>
+        <v>1811.885</v>
       </c>
       <c r="E66" s="14">
         <f t="shared" si="2"/>
-        <v>2385</v>
+        <v>2470</v>
       </c>
       <c r="F66" s="14">
         <f t="shared" si="3"/>
-        <v>3032.82</v>
+        <v>3136.93</v>
       </c>
       <c r="G66" s="14">
         <f t="shared" si="4"/>
-        <v>3683.08</v>
+        <v>3813.3999999999996</v>
       </c>
       <c r="H66" s="1">
         <f>-'LSR Sweep'!C66</f>
@@ -12564,23 +12761,23 @@
       </c>
       <c r="C67" s="14">
         <f t="shared" si="0"/>
-        <v>1215.1600000000001</v>
+        <v>1266.92</v>
       </c>
       <c r="D67" s="14">
         <f t="shared" si="1"/>
-        <v>1907.48</v>
+        <v>1976.335</v>
       </c>
       <c r="E67" s="14">
         <f t="shared" si="2"/>
-        <v>2610</v>
+        <v>2700</v>
       </c>
       <c r="F67" s="14">
         <f t="shared" si="3"/>
-        <v>3325.5200000000004</v>
+        <v>3434.2799999999997</v>
       </c>
       <c r="G67" s="14">
         <f t="shared" si="4"/>
-        <v>4045.88</v>
+        <v>4179.8999999999996</v>
       </c>
       <c r="H67" s="1">
         <f>-'LSR Sweep'!C67</f>
@@ -12611,23 +12808,23 @@
       </c>
       <c r="C68" s="14">
         <f t="shared" si="0"/>
-        <v>1311.96</v>
+        <v>1367.62</v>
       </c>
       <c r="D68" s="14">
         <f t="shared" si="1"/>
-        <v>2067.1800000000003</v>
+        <v>2140.7849999999999</v>
       </c>
       <c r="E68" s="14">
         <f t="shared" si="2"/>
-        <v>2835</v>
+        <v>2930</v>
       </c>
       <c r="F68" s="14">
         <f t="shared" si="3"/>
-        <v>3618.2200000000003</v>
+        <v>3731.6299999999997</v>
       </c>
       <c r="G68" s="14">
         <f t="shared" si="4"/>
-        <v>4408.6799999999994</v>
+        <v>4546.3999999999996</v>
       </c>
       <c r="H68" s="1">
         <f>-'LSR Sweep'!C68</f>
@@ -12658,23 +12855,23 @@
       </c>
       <c r="C69" s="14">
         <f t="shared" si="0"/>
-        <v>1408.76</v>
+        <v>1468.3200000000002</v>
       </c>
       <c r="D69" s="14">
         <f t="shared" si="1"/>
-        <v>2226.88</v>
+        <v>2305.2349999999997</v>
       </c>
       <c r="E69" s="14">
         <f t="shared" si="2"/>
-        <v>3060</v>
+        <v>3160</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="3"/>
-        <v>3910.9200000000005</v>
+        <v>4028.98</v>
       </c>
       <c r="G69" s="14">
         <f t="shared" si="4"/>
-        <v>4771.4799999999996</v>
+        <v>4912.8999999999996</v>
       </c>
       <c r="H69" s="1">
         <f>-'LSR Sweep'!C69</f>
@@ -12702,19 +12899,19 @@
       <c r="A70" s="1"/>
       <c r="C70">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D70">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E70">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F70">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G70">
         <f t="shared" si="4"/>
@@ -12726,19 +12923,19 @@
       <c r="A71" s="1"/>
       <c r="C71">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D71">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E71">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F71">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G71">
         <f t="shared" si="4"/>
@@ -12750,19 +12947,19 @@
       <c r="A72" s="1"/>
       <c r="C72">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D72">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E72">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F72">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G72">
         <f t="shared" si="4"/>
@@ -12774,19 +12971,19 @@
       <c r="A73" s="1"/>
       <c r="C73">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="D73">
         <f t="shared" si="1"/>
-        <v>199.5</v>
+        <v>256.5</v>
       </c>
       <c r="E73">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F73">
         <f t="shared" si="3"/>
-        <v>449.50000000000006</v>
+        <v>496</v>
       </c>
       <c r="G73">
         <f t="shared" si="4"/>
@@ -12980,18 +13177,18 @@
         <v>73</v>
       </c>
       <c r="C8" s="9">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="D8" s="8">
         <f t="shared" si="0"/>
-        <v>0.105</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="E8" s="9">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="F8" s="8">
         <f t="shared" si="1"/>
-        <v>0.14500000000000002</v>
+        <v>0.16</v>
       </c>
       <c r="G8" s="9">
         <v>0.17</v>
@@ -13013,21 +13210,21 @@
         <v>76</v>
       </c>
       <c r="C9" s="9">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="D9" s="8">
         <f t="shared" si="0"/>
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="E9" s="9">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="F9" s="8">
         <f t="shared" si="1"/>
-        <v>0.84000000000000008</v>
+        <v>0.87</v>
       </c>
       <c r="G9" s="9">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>77</v>
@@ -13079,19 +13276,19 @@
         <v>80</v>
       </c>
       <c r="C11" s="9">
-        <v>0.56000000000000005</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D11" s="8">
-        <v>0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="E11" s="9">
         <v>0.6</v>
       </c>
       <c r="F11" s="8">
+        <v>0.61</v>
+      </c>
+      <c r="G11" s="9">
         <v>0.62</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0.64</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>74</v>
@@ -13243,7 +13440,7 @@
     <row r="20" spans="1:13" ht="24" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -13311,7 +13508,7 @@
     <row r="24" spans="1:13" ht="24" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -13328,7 +13525,7 @@
     <row r="25" spans="1:13" ht="24" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -13437,7 +13634,7 @@
     <row r="30" spans="1:13" ht="27" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30" s="22">
         <f t="shared" si="2"/>
@@ -13470,7 +13667,7 @@
     <row r="31" spans="1:13" ht="27" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="26">
         <v>0.3</v>
@@ -13501,7 +13698,7 @@
     <row r="32" spans="1:13" ht="27" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="26">
         <v>0.74</v>
@@ -13547,7 +13744,7 @@
     <row r="34" spans="1:13" ht="27" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -13568,19 +13765,19 @@
     <row r="35" spans="1:13" ht="27" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
       <c r="E35" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
       <c r="J35" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -13619,7 +13816,7 @@
     <row r="38" spans="1:13" ht="27" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
@@ -13636,7 +13833,7 @@
     <row r="39" spans="1:13" ht="27" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20"/>
@@ -13653,7 +13850,7 @@
     <row r="40" spans="1:13" ht="27" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="20"/>
@@ -13670,7 +13867,7 @@
     <row r="41" spans="1:13" ht="27" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
@@ -13687,7 +13884,7 @@
     <row r="42" spans="1:13" ht="27" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
@@ -14185,4 +14382,595 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="10" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="25" customHeight="1">
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+    </row>
+    <row r="2" spans="1:10" ht="25" customHeight="1">
+      <c r="A2" s="39"/>
+      <c r="B2" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+    </row>
+    <row r="3" spans="1:10" ht="25" customHeight="1">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10" ht="28" customHeight="1">
+      <c r="A4" s="39"/>
+      <c r="B4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="39"/>
+      <c r="F4" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10" ht="25" customHeight="1">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="45">
+        <f>IF(AND(OR(C5="Rally2",C5="WRC17",C5="Rally1"),COUNT(C6:C9)=4,C6+C16&gt;=0,C6&lt;=0,C7+20&gt;=0,C7&lt;=0,C8+C17&gt;=0,C8&lt;=0,C9&gt;=0,C6=INT(C6),C7=INT(C7),C8=INT(C8)),G9*MIN(C9,G17)+G10*MAX(0,C9-G17)+G11*MAX(0,C9-G18),"检查输入")</f>
+        <v>3160</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10" ht="25" customHeight="1">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="42">
+        <v>-12</v>
+      </c>
+      <c r="D6" s="39" t="str">
+        <f>"−"&amp;C16&amp;"～0 格"</f>
+        <v>−24～0 格</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="45">
+        <f>IF(AND(OR(C5="Rally2",C5="WRC17",C5="Rally1"),COUNT(C6:C9)=4,C6+C16&gt;=0,C6&lt;=0,C7+20&gt;=0,C7&lt;=0,C8+C17&gt;=0,C8&lt;=0,C9&gt;=0,C6=INT(C6),C7=INT(C7),C8=INT(C8)),G14*MIN(C9,G19)+G15*MAX(0,C9-G19),"检查输入")</f>
+        <v>1867.5450000000001</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+    </row>
+    <row r="7" spans="1:10" ht="25" customHeight="1">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="42">
+        <v>-10</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+    </row>
+    <row r="8" spans="1:10" ht="28" customHeight="1">
+      <c r="A8" s="39"/>
+      <c r="B8" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="42">
+        <v>-20</v>
+      </c>
+      <c r="D8" s="39" t="str">
+        <f>"−"&amp;C17&amp;"～0 格"</f>
+        <v>−40～0 格</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+    </row>
+    <row r="9" spans="1:10" ht="25" customHeight="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="43">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G9" s="44">
+        <f>INDEX(Parameters!$C$7:$G$7,1,C21)+(C18-INDEX(Parameters!$C$6:$G$6,1,C21))*(INDEX(Parameters!$C$7:$G$7,1,C21+1)-INDEX(Parameters!$C$7:$G$7,1,C21))/(INDEX(Parameters!$C$6:$G$6,1,C21+1)-INDEX(Parameters!$C$6:$G$6,1,C21))</f>
+        <v>2500</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+    </row>
+    <row r="10" spans="1:10" ht="25" customHeight="1">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="44">
+        <f>G9*(INDEX(Parameters!$C$9:$G$9,1,C21)+(C18-INDEX(Parameters!$C$6:$G$6,1,C21))*(INDEX(Parameters!$C$9:$G$9,1,C21+1)-INDEX(Parameters!$C$9:$G$9,1,C21))/(INDEX(Parameters!$C$6:$G$6,1,C21+1)-INDEX(Parameters!$C$6:$G$6,1,C21)))</f>
+        <v>2100</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+    </row>
+    <row r="11" spans="1:10" ht="25" customHeight="1">
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="44">
+        <f>INDEX(Parameters!$C$10:$G$10,1,C22)+(C19-INDEX(Parameters!$C$6:$G$6,1,C22))*(INDEX(Parameters!$C$10:$G$10,1,C22+1)-INDEX(Parameters!$C$10:$G$10,1,C22))/(INDEX(Parameters!$C$6:$G$6,1,C22+1)-INDEX(Parameters!$C$6:$G$6,1,C22))</f>
+        <v>2500</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+    </row>
+    <row r="12" spans="1:10" ht="25" customHeight="1">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="44">
+        <f>G10+G11</f>
+        <v>4600</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+    </row>
+    <row r="13" spans="1:10" ht="25" customHeight="1">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+    </row>
+    <row r="14" spans="1:10" ht="28" customHeight="1">
+      <c r="A14" s="39"/>
+      <c r="B14" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="44">
+        <f>INDEX(Parameters!$C$30:$G$30,1,C23)+(C20-INDEX(Parameters!$C$28:$G$28,1,C23))*(INDEX(Parameters!$C$30:$G$30,1,C23+1)-INDEX(Parameters!$C$30:$G$30,1,C23))/(INDEX(Parameters!$C$28:$G$28,1,C23+1)-INDEX(Parameters!$C$28:$G$28,1,C23))</f>
+        <v>2115</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+    </row>
+    <row r="15" spans="1:10" ht="25" customHeight="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="44">
+        <f>G14*(INDEX(Parameters!$C$32:$G$32,1,C23)+(C20-INDEX(Parameters!$C$28:$G$28,1,C23))*(INDEX(Parameters!$C$32:$G$32,1,C23+1)-INDEX(Parameters!$C$32:$G$32,1,C23))/(INDEX(Parameters!$C$28:$G$28,1,C23+1)-INDEX(Parameters!$C$28:$G$28,1,C23)))</f>
+        <v>1734.3</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+    </row>
+    <row r="16" spans="1:10" ht="25" customHeight="1">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="39">
+        <v>24</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+    </row>
+    <row r="17" spans="1:10" ht="25" customHeight="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="39">
+        <f>IF(C5="WRC17",60,40)</f>
+        <v>40</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="46">
+        <f>INDEX(Parameters!$C$8:$G$8,1,C21)+(C18-INDEX(Parameters!$C$6:$G$6,1,C21))*(INDEX(Parameters!$C$8:$G$8,1,C21+1)-INDEX(Parameters!$C$8:$G$8,1,C21))/(INDEX(Parameters!$C$6:$G$6,1,C21+1)-INDEX(Parameters!$C$6:$G$6,1,C21))</f>
+        <v>0.15</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+    </row>
+    <row r="18" spans="1:10" ht="25" customHeight="1">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="44">
+        <f>C6*20/C16</f>
+        <v>-10</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="46">
+        <f>INDEX(Parameters!$C$11:$G$11,1,C22)+(C19-INDEX(Parameters!$C$6:$G$6,1,C22))*(INDEX(Parameters!$C$11:$G$11,1,C22+1)-INDEX(Parameters!$C$11:$G$11,1,C22))/(INDEX(Parameters!$C$6:$G$6,1,C22+1)-INDEX(Parameters!$C$6:$G$6,1,C22))</f>
+        <v>0.6</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+    </row>
+    <row r="19" spans="1:10" ht="25" customHeight="1">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="44">
+        <f>C7</f>
+        <v>-10</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="46">
+        <f>INDEX(Parameters!$C$31:$G$31,1,C23)+(C20-INDEX(Parameters!$C$28:$G$28,1,C23))*(INDEX(Parameters!$C$31:$G$31,1,C23+1)-INDEX(Parameters!$C$31:$G$31,1,C23))/(INDEX(Parameters!$C$28:$G$28,1,C23+1)-INDEX(Parameters!$C$28:$G$28,1,C23))</f>
+        <v>0.35</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+    </row>
+    <row r="20" spans="1:10" ht="25" customHeight="1">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="44">
+        <f>C8*40/C17</f>
+        <v>-20</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+    </row>
+    <row r="21" spans="1:10" ht="25" customHeight="1">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="39">
+        <f>MIN(4,MATCH(C18,Parameters!$C$6:$G$6,1))</f>
+        <v>3</v>
+      </c>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+    </row>
+    <row r="22" spans="1:10" ht="25" customHeight="1">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="39">
+        <f>MIN(4,MATCH(C19,Parameters!$C$6:$G$6,1))</f>
+        <v>3</v>
+      </c>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+    </row>
+    <row r="23" spans="1:10" ht="25" customHeight="1">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="39">
+        <f>MIN(4,MATCH(C20,Parameters!$C$28:$G$28,1))</f>
+        <v>3</v>
+      </c>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+    </row>
+    <row r="24" spans="1:10" ht="25" customHeight="1">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+    </row>
+    <row r="25" spans="1:10" ht="25" customHeight="1">
+      <c r="A25" s="39"/>
+      <c r="B25" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+    </row>
+    <row r="26" spans="1:10" ht="25" customHeight="1">
+      <c r="A26" s="39"/>
+      <c r="B26" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+    </row>
+    <row r="27" spans="1:10" ht="25" customHeight="1">
+      <c r="A27" s="39"/>
+      <c r="B27" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+    </row>
+    <row r="28" spans="1:10" ht="25" customHeight="1">
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+    </row>
+    <row r="29" spans="1:10" ht="25" customHeight="1">
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+    </row>
+    <row r="30" spans="1:10" ht="25" customHeight="1">
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C5" xr:uid="{00000000-0002-0000-0500-000000000000}">
+      <formula1>"Rally2,WRC17,Rally1"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" sqref="C6" xr:uid="{00000000-0002-0000-0500-000001000000}">
+      <formula1>-C16</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="whole" sqref="C7" xr:uid="{00000000-0002-0000-0500-000002000000}">
+      <formula1>-20</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="whole" sqref="C8" xr:uid="{00000000-0002-0000-0500-000003000000}">
+      <formula1>-C17</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" sqref="C9" xr:uid="{00000000-0002-0000-0500-000004000000}">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087D4E63-93A6-4867-A663-16EA3214C4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A50490-75B4-4926-9251-292E108C01E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>轴速 0～1 m/s · 每 0.05 m/s 一点 · 直线连接 · 详细计算与采样位于 Samples</t>
-  </si>
-  <si>
-    <t>Astral · HSC Sweep</t>
   </si>
   <si>
     <t>固定 LSC</t>
@@ -301,13 +298,17 @@
   <si>
     <t>Type-B：第一 knee 由 HSC 控制；第二 knee 固定，统一在 L14 调整。Type-A 调节关系保持原样。</t>
   </si>
+  <si>
+    <t>Astral · HSC Sweep</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -443,10 +444,10 @@
     <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -482,26 +483,26 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -681,64 +682,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>143.4</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>182.4</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>221.4</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>260.39999999999998</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>299.39999999999998</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>338.40000000000003</c:v>
+                  <c:v>666</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>377.40000000000003</c:v>
+                  <c:v>702</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>416.4</c:v>
+                  <c:v>738</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>455.40000000000003</c:v>
+                  <c:v>774</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>494.4</c:v>
+                  <c:v>810</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>658.4000000000002</c:v>
+                  <c:v>871</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>822.39999999999986</c:v>
+                  <c:v>932</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>986.40000000000009</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1150.4000000000003</c:v>
+                  <c:v>1054</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1314.4</c:v>
+                  <c:v>1115</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1478.4</c:v>
+                  <c:v>1176</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1642.4</c:v>
+                  <c:v>1237</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1806.4</c:v>
+                  <c:v>1298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -857,64 +858,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>257.51249999999999</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>328.38750000000005</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>399.26250000000005</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>470.13749999999999</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>541.01249999999993</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>611.88750000000005</c:v>
+                  <c:v>894</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>682.76250000000005</c:v>
+                  <c:v>948</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>753.63749999999993</c:v>
+                  <c:v>1002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>824.51250000000005</c:v>
+                  <c:v>1056</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>895.38749999999993</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1091.2625000000003</c:v>
+                  <c:v>1189</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1287.1375</c:v>
+                  <c:v>1268</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1483.0125</c:v>
+                  <c:v>1347</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1678.8875000000003</c:v>
+                  <c:v>1426</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1874.7625</c:v>
+                  <c:v>1505</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2070.6375000000003</c:v>
+                  <c:v>1584</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2266.5124999999998</c:v>
+                  <c:v>1663</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2462.3874999999998</c:v>
+                  <c:v>1742</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1033,64 +1034,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>1125</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1320</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1550</c:v>
+                  <c:v>1525</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1779.9999999999998</c:v>
+                  <c:v>1625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2010</c:v>
+                  <c:v>1725</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2240</c:v>
+                  <c:v>1825</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2470</c:v>
+                  <c:v>1925</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2700</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2930</c:v>
+                  <c:v>2125</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3160</c:v>
+                  <c:v>2225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1209,64 +1210,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>487.5</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>633.1</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>774.47500000000002</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>915.84999999999991</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1057.2249999999999</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1198.5999999999999</c:v>
+                  <c:v>1359</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1339.9750000000001</c:v>
+                  <c:v>1458</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1481.35</c:v>
+                  <c:v>1557</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1622.7250000000001</c:v>
+                  <c:v>1656.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1764.1</c:v>
+                  <c:v>1755</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2030.4749999999999</c:v>
+                  <c:v>1879</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2296.8499999999995</c:v>
+                  <c:v>2003</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2563.2249999999999</c:v>
+                  <c:v>2127</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2829.6000000000004</c:v>
+                  <c:v>2251</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3095.9749999999999</c:v>
+                  <c:v>2375</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3362.35</c:v>
+                  <c:v>2499</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3628.7249999999999</c:v>
+                  <c:v>2623</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3895.1</c:v>
+                  <c:v>2747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1385,64 +1386,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>600</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>788</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>968</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1148</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1328</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1508</c:v>
+                  <c:v>1596</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1688</c:v>
+                  <c:v>1722</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1867.9999999999998</c:v>
+                  <c:v>1848</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2048</c:v>
+                  <c:v>1974.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2228</c:v>
+                  <c:v>2100</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2533</c:v>
+                  <c:v>2251</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2838</c:v>
+                  <c:v>2402</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3143</c:v>
+                  <c:v>2553</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3448</c:v>
+                  <c:v>2704</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3753</c:v>
+                  <c:v>2855</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4058</c:v>
+                  <c:v>3006</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4363</c:v>
+                  <c:v>3157</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4668</c:v>
+                  <c:v>3308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1761,64 +1762,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>825</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>975</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1050</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1125</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1200</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1275</c:v>
+                  <c:v>1340</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1375</c:v>
+                  <c:v>1495</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1475</c:v>
+                  <c:v>1649.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1575</c:v>
+                  <c:v>1805</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1675</c:v>
+                  <c:v>1960</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1775</c:v>
+                  <c:v>2115</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1875</c:v>
+                  <c:v>2270</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1975</c:v>
+                  <c:v>2425</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2075</c:v>
+                  <c:v>2580</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1937,64 +1938,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>975</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1050</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1125</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1200</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1275</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1350</c:v>
+                  <c:v>1337.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1450</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1550</c:v>
+                  <c:v>1722.4999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1650</c:v>
+                  <c:v>1915</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1750</c:v>
+                  <c:v>2107.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1850</c:v>
+                  <c:v>2300</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1950</c:v>
+                  <c:v>2492.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2050</c:v>
+                  <c:v>2685</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2150</c:v>
+                  <c:v>2877.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2113,64 +2114,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>1050</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1125</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1200</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1275</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1350</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1425</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1525</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1625</c:v>
+                  <c:v>1779.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1725</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1825</c:v>
+                  <c:v>2240</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1925</c:v>
+                  <c:v>2470</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2125</c:v>
+                  <c:v>2930</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2225</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2289,64 +2290,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>1050</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1200</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1275</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1350</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1425</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1500</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1600</c:v>
+                  <c:v>1555</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1700</c:v>
+                  <c:v>1822.4999999999995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1800</c:v>
+                  <c:v>2090</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1900</c:v>
+                  <c:v>2357.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2000</c:v>
+                  <c:v>2625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2100</c:v>
+                  <c:v>2892.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2200</c:v>
+                  <c:v>3160</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2300</c:v>
+                  <c:v>3427.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2465,64 +2466,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>900</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>1050</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1200</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1350</c:v>
+                  <c:v>1005.0000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1425</c:v>
+                  <c:v>1110</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1500</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1575</c:v>
+                  <c:v>1320</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1675</c:v>
+                  <c:v>1545</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1775</c:v>
+                  <c:v>1849.9999999999995</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1875</c:v>
+                  <c:v>2155</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1975</c:v>
+                  <c:v>2460</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2075</c:v>
+                  <c:v>2765</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2175</c:v>
+                  <c:v>3070</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2275</c:v>
+                  <c:v>3375</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2375</c:v>
+                  <c:v>3680</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2841,64 +2842,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>80</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>160</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>240</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>320</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>400</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>440</c:v>
+                  <c:v>412.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>480</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>520</c:v>
+                  <c:v>487.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>560</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>562.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>600</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>640</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>680</c:v>
+                  <c:v>637.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>720</c:v>
+                  <c:v>675</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>760</c:v>
+                  <c:v>712.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>800</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>840</c:v>
+                  <c:v>787.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>880</c:v>
+                  <c:v>825</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>920</c:v>
+                  <c:v>862.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>960</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1000</c:v>
+                  <c:v>937.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3017,64 +3018,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>110</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>220</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>330</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>440</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>550</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>634.69999999999993</c:v>
+                  <c:v>577</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>694.09999999999991</c:v>
+                  <c:v>631</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>753.5</c:v>
+                  <c:v>685</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>812.9</c:v>
+                  <c:v>739</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>872.3</c:v>
+                  <c:v>793</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>931.7</c:v>
+                  <c:v>847</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>991.09999999999991</c:v>
+                  <c:v>901</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1050.5</c:v>
+                  <c:v>955</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1109.8999999999999</c:v>
+                  <c:v>1009</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1169.3</c:v>
+                  <c:v>1063</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1228.7</c:v>
+                  <c:v>1117</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1288.0999999999999</c:v>
+                  <c:v>1171</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1347.5</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1406.9</c:v>
+                  <c:v>1279</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1466.3</c:v>
+                  <c:v>1333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3193,64 +3194,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>140</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>280</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>420</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>560</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>700</c:v>
+                  <c:v>625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>840</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>921.2</c:v>
+                  <c:v>822.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1002.4000000000001</c:v>
+                  <c:v>895</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1083.5999999999999</c:v>
+                  <c:v>967.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1164.8</c:v>
+                  <c:v>1040</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1246</c:v>
+                  <c:v>1112.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1327.2</c:v>
+                  <c:v>1185</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1408.4</c:v>
+                  <c:v>1257.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1489.6</c:v>
+                  <c:v>1330</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1570.8000000000002</c:v>
+                  <c:v>1402.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1652</c:v>
+                  <c:v>1475</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1733.2</c:v>
+                  <c:v>1547.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1814.4</c:v>
+                  <c:v>1620</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1895.6</c:v>
+                  <c:v>1692.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1976.8</c:v>
+                  <c:v>1765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3369,64 +3370,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>170</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>340</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>510</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>680</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>850</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1020</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1157.6999999999998</c:v>
+                  <c:v>1021.4999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1263.0999999999999</c:v>
+                  <c:v>1114.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1368.5</c:v>
+                  <c:v>1207.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1473.8999999999999</c:v>
+                  <c:v>1300.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1579.3</c:v>
+                  <c:v>1393.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1684.6999999999998</c:v>
+                  <c:v>1486.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1790.1</c:v>
+                  <c:v>1579.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1895.4999999999998</c:v>
+                  <c:v>1672.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2000.8999999999999</c:v>
+                  <c:v>1765.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2106.3000000000002</c:v>
+                  <c:v>1858.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2211.6999999999998</c:v>
+                  <c:v>1951.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2317.1</c:v>
+                  <c:v>2044.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2422.5</c:v>
+                  <c:v>2137.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2527.8999999999996</c:v>
+                  <c:v>2230.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3545,64 +3546,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>600</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>800</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000</c:v>
+                  <c:v>875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1200</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1400</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1532</c:v>
+                  <c:v>1340.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1664</c:v>
+                  <c:v>1456</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1796</c:v>
+                  <c:v>1571.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1928.0000000000002</c:v>
+                  <c:v>1687.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2060</c:v>
+                  <c:v>1802.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2192</c:v>
+                  <c:v>1918</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2324</c:v>
+                  <c:v>2033.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2456</c:v>
+                  <c:v>2149</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2588</c:v>
+                  <c:v>2264.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2720</c:v>
+                  <c:v>2380</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2852</c:v>
+                  <c:v>2495.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2984</c:v>
+                  <c:v>2611</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3116</c:v>
+                  <c:v>2726.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4970,64 +4971,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-80</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-160</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-240</c:v>
+                  <c:v>-225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-320</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-400</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-480</c:v>
+                  <c:v>-450</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-551.19999999999993</c:v>
+                  <c:v>-516.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-613.59999999999991</c:v>
+                  <c:v>-575.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-676</c:v>
+                  <c:v>-633.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-738.4</c:v>
+                  <c:v>-692.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-800.8</c:v>
+                  <c:v>-750.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-863.19999999999993</c:v>
+                  <c:v>-809.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-925.59999999999991</c:v>
+                  <c:v>-867.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-987.99999999999989</c:v>
+                  <c:v>-926.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1050.4000000000001</c:v>
+                  <c:v>-984.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1112.8</c:v>
+                  <c:v>-1043.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1175.1999999999998</c:v>
+                  <c:v>-1101.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1237.5999999999999</c:v>
+                  <c:v>-1160.25</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1300</c:v>
+                  <c:v>-1218.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1362.4</c:v>
+                  <c:v>-1277.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5146,64 +5147,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-110</c:v>
+                  <c:v>-100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-220</c:v>
+                  <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-330</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-440</c:v>
+                  <c:v>-400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-550</c:v>
+                  <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-660</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-770</c:v>
+                  <c:v>-700</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-860.2</c:v>
+                  <c:v>-782.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-950.40000000000009</c:v>
+                  <c:v>-864</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1040.5999999999999</c:v>
+                  <c:v>-946</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1130.8000000000002</c:v>
+                  <c:v>-1028</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1221</c:v>
+                  <c:v>-1110</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1311.2</c:v>
+                  <c:v>-1192</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1401.4</c:v>
+                  <c:v>-1274</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1491.6</c:v>
+                  <c:v>-1356</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1581.8000000000002</c:v>
+                  <c:v>-1438</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1672</c:v>
+                  <c:v>-1520</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1762.2</c:v>
+                  <c:v>-1602</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1852.3999999999999</c:v>
+                  <c:v>-1684</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1942.6000000000001</c:v>
+                  <c:v>-1766</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5322,64 +5323,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-140</c:v>
+                  <c:v>-125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-280</c:v>
+                  <c:v>-250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-420</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-560</c:v>
+                  <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-700</c:v>
+                  <c:v>-625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-840</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-979.99999999999989</c:v>
+                  <c:v>-875</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1110.2</c:v>
+                  <c:v>-991.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1230.5999999999999</c:v>
+                  <c:v>-1098.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1351</c:v>
+                  <c:v>-1206.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1471.4</c:v>
+                  <c:v>-1313.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1591.8</c:v>
+                  <c:v>-1421.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1712.2</c:v>
+                  <c:v>-1528.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1832.6</c:v>
+                  <c:v>-1636.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1953</c:v>
+                  <c:v>-1743.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2073.4</c:v>
+                  <c:v>-1851.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2193.8000000000002</c:v>
+                  <c:v>-1958.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2314.1999999999998</c:v>
+                  <c:v>-2066.25</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2434.6</c:v>
+                  <c:v>-2173.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2555</c:v>
+                  <c:v>-2281.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5498,64 +5499,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-170</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-340</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-510</c:v>
+                  <c:v>-450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-680</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-850</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1020</c:v>
+                  <c:v>-900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1190</c:v>
+                  <c:v>-1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1360</c:v>
+                  <c:v>-1200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1513</c:v>
+                  <c:v>-1335</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1666</c:v>
+                  <c:v>-1470</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1819</c:v>
+                  <c:v>-1605</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1972</c:v>
+                  <c:v>-1740</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-2125</c:v>
+                  <c:v>-1875</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2278</c:v>
+                  <c:v>-2009.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2431</c:v>
+                  <c:v>-2145</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2584</c:v>
+                  <c:v>-2280</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2737</c:v>
+                  <c:v>-2415</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2890</c:v>
+                  <c:v>-2550</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-3043</c:v>
+                  <c:v>-2685</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-3196</c:v>
+                  <c:v>-2820</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6125,20 +6126,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="B2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6168,17 +6169,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="E4" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6202,20 +6203,20 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>48</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
+      <c r="F6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6225,7 +6226,7 @@
     <row r="7" spans="1:15" ht="23" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3">
         <v>-12</v>
@@ -6246,18 +6247,18 @@
     <row r="8" spans="1:15" ht="23" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <v>-10</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="F8" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
       <c r="I8" s="27">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>2240</v>
@@ -6272,7 +6273,7 @@
     <row r="9" spans="1:15" ht="23" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="3">
         <v>-20</v>
@@ -6293,21 +6294,21 @@
     <row r="10" spans="1:15" ht="23" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="16">
         <v>0.8</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
+      <c r="F10" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="27">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1581.8000000000002</v>
+        <v>1438</v>
       </c>
       <c r="J10" s="27"/>
       <c r="K10" s="1"/>
@@ -6353,7 +6354,7 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1">
         <f>Parameters!D23</f>
@@ -6361,13 +6362,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
+      <c r="F13" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6377,7 +6378,7 @@
     <row r="14" spans="1:15" ht="23" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1">
         <f>Parameters!D24</f>
@@ -6385,17 +6386,17 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="F14" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
         <v>2500</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -6406,7 +6407,7 @@
     <row r="15" spans="1:15" ht="23" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1">
         <f>IF(C6="WRC17",Parameters!D26,Parameters!D25)</f>
@@ -6414,17 +6415,17 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
+      <c r="F15" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
         <v>2100</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -6438,17 +6439,17 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="F16" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
         <v>2500</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -6462,17 +6463,17 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="F17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
         <v>4600</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -6483,7 +6484,7 @@
     <row r="18" spans="1:15" ht="23" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="1" t="str">
         <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="Rally2",C6="WRC17",C6="Rally1"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
@@ -6508,17 +6509,17 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="F19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -6532,17 +6533,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="F20" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
-        <v>1804</v>
+        <v>1640</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -6573,17 +6574,17 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
+      <c r="F22" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
         <v>0.15</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -6597,17 +6598,17 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="F23" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -6621,17 +6622,17 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="F24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
         <v>0.35</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -6676,7 +6677,7 @@
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26"/>
@@ -6949,17 +6950,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -6967,6 +6957,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -7027,20 +7028,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7067,20 +7068,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7110,17 +7111,17 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7791,20 +7792,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="B2" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7831,20 +7832,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7868,23 +7869,23 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3">
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="E6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8555,20 +8556,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="B2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8595,20 +8596,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8631,20 +8632,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="B6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9311,20 +9312,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="B2" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9354,17 +9355,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9387,20 +9388,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="B6" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10071,40 +10072,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
+      <c r="B2" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="B3" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10128,30 +10129,30 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
+      <c r="J5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -10194,10 +10195,10 @@
     <row r="7" spans="1:15" ht="23" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D7" s="1">
         <f>(D$6-1)*$D$23</f>
@@ -10245,10 +10246,10 @@
     <row r="8" spans="1:15" ht="23" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <f>(D$6-1)*$D$24</f>
@@ -10313,10 +10314,10 @@
     <row r="10" spans="1:15" ht="23" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D10" s="3">
         <v>1000</v>
@@ -10358,10 +10359,10 @@
     <row r="11" spans="1:15" ht="23" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4">
         <v>0.12</v>
@@ -10403,10 +10404,10 @@
     <row r="12" spans="1:15" ht="23" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D12" s="4">
         <v>0.78</v>
@@ -10448,10 +10449,10 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3">
         <v>1000</v>
@@ -10493,10 +10494,10 @@
     <row r="14" spans="1:15" ht="23" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>0.57999999999999996</v>
@@ -10555,10 +10556,10 @@
     <row r="16" spans="1:15" ht="23" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1">
         <f>(D$6-1)*$D$25</f>
@@ -10606,55 +10607,55 @@
     <row r="17" spans="1:15" ht="23" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3">
         <v>1000</v>
       </c>
       <c r="E17" s="6">
         <f>(D17+F17)/2</f>
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F17" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="G17" s="6">
         <f>(F17+H17)/2</f>
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="H17" s="3">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="K17" s="6">
         <f>(J17+L17)/2</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="L17" s="3">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="M17" s="6">
         <f>(L17+N17)/2</f>
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="N17" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" ht="23" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" s="4">
         <v>0.3</v>
@@ -10696,10 +10697,10 @@
     <row r="19" spans="1:15" ht="23" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4">
         <v>0.74</v>
@@ -10774,35 +10775,35 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
+      <c r="B22" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="20"/>
+      <c r="B23" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="22"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -10816,10 +10817,10 @@
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="20"/>
+      <c r="B24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="22"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
@@ -10837,10 +10838,10 @@
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="20"/>
+      <c r="B25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="22"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10858,25 +10859,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="20"/>
+      <c r="B26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="22"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
+      <c r="F26" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -10898,154 +10899,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="B28" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
+      <c r="B29" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
+      <c r="B30" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
+      <c r="B31" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
+      <c r="B32" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
+      <c r="B33" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
+      <c r="B34" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
+      <c r="B35" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11152,6 +11153,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -11160,17 +11172,6 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11193,7 +11194,7 @@
     <row r="1" spans="1:22" ht="22" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
@@ -11267,67 +11268,67 @@
     <row r="4" spans="1:22" ht="35" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="12" t="s">
+      <c r="I4" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" s="12" t="s">
+      <c r="M4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="P4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q4" s="13" t="s">
+      <c r="R4" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="S4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="T4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="U4" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="V4" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="V4" s="13" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1">
@@ -11350,23 +11351,23 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>780</v>
+        <v>720</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11374,23 +11375,23 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>3280</v>
+        <v>1220</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11437,23 +11438,23 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.13500000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.81</v>
+        <v>0.45</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>1417.5</v>
+        <v>1080</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11461,23 +11462,23 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>3917.5</v>
+        <v>1580</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.32499999999999996</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1248</v>
+        <v>1080</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11524,23 +11525,23 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11548,23 +11549,23 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>4600</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.82</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>1804</v>
+        <v>1450</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -11611,23 +11612,23 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.87</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>2827.5</v>
+        <v>1980.0000000000002</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11635,23 +11636,23 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>5327.5</v>
+        <v>2480</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.375</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>2408</v>
+        <v>1860</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11698,23 +11699,23 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>3600</v>
+        <v>2520</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11722,23 +11723,23 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>6100</v>
+        <v>3020</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>3060</v>
+        <v>2310</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11840,7 +11841,7 @@
     <row r="13" spans="1:22" ht="22" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="10" t="str">
         <f>B5</f>
@@ -11926,23 +11927,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>162.5</v>
+        <v>180</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -11967,23 +11968,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -12008,23 +12009,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>143.4</v>
+        <v>270</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>257.51249999999999</v>
+        <v>360</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>487.5</v>
+        <v>540</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12049,23 +12050,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>182.4</v>
+        <v>360</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>328.38750000000005</v>
+        <v>480</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>633.1</v>
+        <v>720</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>788</v>
+        <v>840</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -12090,23 +12091,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>221.4</v>
+        <v>450</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>399.26250000000005</v>
+        <v>600</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>774.47500000000002</v>
+        <v>900</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>968</v>
+        <v>1050</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -12131,23 +12132,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>260.39999999999998</v>
+        <v>540</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>470.13749999999999</v>
+        <v>720</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>915.84999999999991</v>
+        <v>1080</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1148</v>
+        <v>1260</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -12172,23 +12173,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>299.39999999999998</v>
+        <v>630</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>541.01249999999993</v>
+        <v>840</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>795</v>
+        <v>1050</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1057.2249999999999</v>
+        <v>1260</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1328</v>
+        <v>1470</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -12213,23 +12214,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>338.40000000000003</v>
+        <v>666</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>611.88750000000005</v>
+        <v>894</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1198.5999999999999</v>
+        <v>1359</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>1508</v>
+        <v>1596</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -12254,23 +12255,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>377.40000000000003</v>
+        <v>702</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>682.76250000000005</v>
+        <v>948</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1005.0000000000001</v>
+        <v>1200</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>1339.9750000000001</v>
+        <v>1458</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>1688</v>
+        <v>1722</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -12295,23 +12296,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>416.4</v>
+        <v>738</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>753.63749999999993</v>
+        <v>1002</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1275</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>1481.35</v>
+        <v>1557</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>1867.9999999999998</v>
+        <v>1848</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -12336,23 +12337,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>455.40000000000003</v>
+        <v>774</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>824.51250000000005</v>
+        <v>1056</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>1215</v>
+        <v>1350</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>1622.7250000000001</v>
+        <v>1656.0000000000002</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>2048</v>
+        <v>1974.0000000000002</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -12377,23 +12378,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>494.4</v>
+        <v>810</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>895.38749999999993</v>
+        <v>1110</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>1320</v>
+        <v>1425</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>1764.1</v>
+        <v>1755</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>2228</v>
+        <v>2100</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -12418,23 +12419,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>658.4000000000002</v>
+        <v>871</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1091.2625000000003</v>
+        <v>1189</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>2030.4749999999999</v>
+        <v>1879</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2533</v>
+        <v>2251</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12459,23 +12460,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>822.39999999999986</v>
+        <v>932</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1287.1375</v>
+        <v>1268</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1779.9999999999998</v>
+        <v>1625</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>2296.8499999999995</v>
+        <v>2003</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2838</v>
+        <v>2402</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12500,23 +12501,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>986.40000000000009</v>
+        <v>993</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1483.0125</v>
+        <v>1347</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>2010</v>
+        <v>1725</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2563.2249999999999</v>
+        <v>2127</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>3143</v>
+        <v>2553</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12541,23 +12542,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1150.4000000000003</v>
+        <v>1054</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1678.8875000000003</v>
+        <v>1426</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>2240</v>
+        <v>1825</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2829.6000000000004</v>
+        <v>2251</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>3448</v>
+        <v>2704</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12582,23 +12583,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1314.4</v>
+        <v>1115</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>1874.7625</v>
+        <v>1505</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>2470</v>
+        <v>1925</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>3095.9749999999999</v>
+        <v>2375</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>3753</v>
+        <v>2855</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12623,23 +12624,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1478.4</v>
+        <v>1176</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>2070.6375000000003</v>
+        <v>1584</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2700</v>
+        <v>2025</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>3362.35</v>
+        <v>2499</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>4058</v>
+        <v>3006</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12664,23 +12665,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1642.4</v>
+        <v>1237</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>2266.5124999999998</v>
+        <v>1663</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>2930</v>
+        <v>2125</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>3628.7249999999999</v>
+        <v>2623</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>4363</v>
+        <v>3157</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12705,23 +12706,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1806.4</v>
+        <v>1298</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>2462.3874999999998</v>
+        <v>1742</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>3160</v>
+        <v>2225</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>3895.1</v>
+        <v>2747</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>4668</v>
+        <v>3308</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -12886,7 +12887,7 @@
     <row r="41" spans="1:22" ht="22" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
@@ -12958,67 +12959,67 @@
     </row>
     <row r="44" spans="1:22" ht="35" customHeight="1">
       <c r="B44" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="D44" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="E44" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="F44" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H44" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F44" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" s="13" t="s">
+      <c r="I44" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K44" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H44" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J44" s="13" t="s">
+      <c r="L44" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K44" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="L44" s="13" t="s">
+      <c r="M44" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="O44" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="M44" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O44" s="13" t="s">
+      <c r="P44" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q44" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="P44" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q44" s="13" t="s">
+      <c r="R44" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R44" s="13" t="s">
+      <c r="S44" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="S44" s="13" t="s">
+      <c r="T44" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T44" s="13" t="s">
+      <c r="U44" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="U44" s="13" t="s">
+      <c r="V44" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="V44" s="13" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="22" customHeight="1">
@@ -13040,47 +13041,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>1600</v>
+        <v>1000</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -13126,47 +13127,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>2000</v>
+        <v>3850</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>2200</v>
+        <v>1500</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.27500000000000002</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.54</v>
+        <v>0.78</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>1188</v>
+        <v>1170</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -13212,23 +13213,23 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13236,23 +13237,23 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.57999999999999996</v>
+        <v>0.82</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>1624</v>
+        <v>1640</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -13298,47 +13299,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>500</v>
+        <v>3250</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>2000</v>
+        <v>5350</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.32499999999999996</v>
+        <v>0.375</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>2108</v>
+        <v>2150</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -13384,47 +13385,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>2000</v>
+        <v>6100</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>2640</v>
+        <v>2700</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -13522,7 +13523,7 @@
     </row>
     <row r="53" spans="2:22" ht="22" customHeight="1">
       <c r="B53" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C53" s="11" t="str">
         <f>B45</f>
@@ -13606,23 +13607,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -13646,23 +13647,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -13686,23 +13687,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -13726,23 +13727,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -13766,23 +13767,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>750</v>
+        <v>585</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -13806,23 +13807,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>825</v>
+        <v>690</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>690</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>690</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>900</v>
+        <v>690</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>900</v>
+        <v>690</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -13846,23 +13847,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>900</v>
+        <v>795</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>975</v>
+        <v>795</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>1050</v>
+        <v>795</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>1050</v>
+        <v>795</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>1050</v>
+        <v>795</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -13886,23 +13887,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>975</v>
+        <v>900</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>1125</v>
+        <v>900</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -13926,23 +13927,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1050</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1125</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1200</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1275</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>1005.0000000000001</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -13966,23 +13967,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1125</v>
+        <v>1110</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1200</v>
+        <v>1110</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1275</v>
+        <v>1110</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>1350</v>
+        <v>1110</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>1425</v>
+        <v>1110</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -14006,23 +14007,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1200</v>
+        <v>1215</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>1275</v>
+        <v>1215</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>1350</v>
+        <v>1215</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>1425</v>
+        <v>1215</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>1500</v>
+        <v>1215</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -14046,23 +14047,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1275</v>
+        <v>1340</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1350</v>
+        <v>1337.5</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>1425</v>
+        <v>1320</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>1500</v>
+        <v>1320</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>1575</v>
+        <v>1320</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -14086,23 +14087,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1375</v>
+        <v>1495</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1450</v>
+        <v>1530</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1600</v>
+        <v>1555</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1675</v>
+        <v>1545</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14126,23 +14127,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1475</v>
+        <v>1649.9999999999998</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1550</v>
+        <v>1722.4999999999998</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1625</v>
+        <v>1779.9999999999998</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1700</v>
+        <v>1822.4999999999995</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1775</v>
+        <v>1849.9999999999995</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14166,23 +14167,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1575</v>
+        <v>1805</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1650</v>
+        <v>1915</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>1725</v>
+        <v>2010</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>1800</v>
+        <v>2090</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>1875</v>
+        <v>2155</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14206,23 +14207,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>1675</v>
+        <v>1960</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>1750</v>
+        <v>2107.5</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>1825</v>
+        <v>2240</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>1900</v>
+        <v>2357.5</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>1975</v>
+        <v>2460</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14246,23 +14247,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>1775</v>
+        <v>2115</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>1850</v>
+        <v>2300</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>1925</v>
+        <v>2470</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2000</v>
+        <v>2625</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2075</v>
+        <v>2765</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14286,23 +14287,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>1875</v>
+        <v>2270</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>1950</v>
+        <v>2492.5</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2025</v>
+        <v>2700</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2100</v>
+        <v>2892.5</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>2175</v>
+        <v>3070</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14326,23 +14327,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>1975</v>
+        <v>2425</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2050</v>
+        <v>2685</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>2125</v>
+        <v>2930</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>2200</v>
+        <v>3160</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>2275</v>
+        <v>3375</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14366,23 +14367,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2075</v>
+        <v>2580</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2150</v>
+        <v>2877.5</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>2225</v>
+        <v>3160</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>2300</v>
+        <v>3427.5</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>2375</v>
+        <v>3680</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14540,7 +14541,7 @@
     </row>
     <row r="81" spans="2:22" ht="22" customHeight="1">
       <c r="B81" s="29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
@@ -14611,67 +14612,67 @@
     </row>
     <row r="84" spans="2:22" ht="35" customHeight="1">
       <c r="B84" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="D84" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="E84" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="F84" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H84" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F84" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G84" s="13" t="s">
+      <c r="I84" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K84" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H84" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I84" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J84" s="13" t="s">
+      <c r="L84" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K84" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="L84" s="13" t="s">
+      <c r="M84" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N84" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="O84" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="M84" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N84" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O84" s="13" t="s">
+      <c r="P84" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q84" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="P84" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q84" s="13" t="s">
+      <c r="R84" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R84" s="13" t="s">
+      <c r="S84" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="S84" s="13" t="s">
+      <c r="T84" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T84" s="13" t="s">
+      <c r="U84" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="U84" s="13" t="s">
+      <c r="V84" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="V84" s="13" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="85" spans="2:22" ht="22" customHeight="1">
@@ -14721,7 +14722,7 @@
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
@@ -14733,7 +14734,7 @@
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -14807,7 +14808,7 @@
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
@@ -14819,7 +14820,7 @@
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>1188</v>
+        <v>1080</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -14893,7 +14894,7 @@
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
@@ -14905,7 +14906,7 @@
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>1624</v>
+        <v>1450</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -14979,7 +14980,7 @@
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
@@ -14991,7 +14992,7 @@
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>2108</v>
+        <v>1860</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -15065,7 +15066,7 @@
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
@@ -15077,7 +15078,7 @@
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>2640</v>
+        <v>2310</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -15175,7 +15176,7 @@
     </row>
     <row r="93" spans="2:22" ht="22" customHeight="1">
       <c r="B93" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C93" s="11" t="str">
         <f>B85</f>
@@ -15259,23 +15260,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -15299,23 +15300,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -15339,23 +15340,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>600</v>
+        <v>525</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -15379,23 +15380,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -15419,23 +15420,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>700</v>
+        <v>625</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>850</v>
+        <v>750</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>1000</v>
+        <v>875</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -15459,23 +15460,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>440</v>
+        <v>412.5</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>634.69999999999993</v>
+        <v>577</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>840</v>
+        <v>750</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>1020</v>
+        <v>900</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -15499,23 +15500,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>694.09999999999991</v>
+        <v>631</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>921.2</v>
+        <v>822.5</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>1157.6999999999998</v>
+        <v>1021.4999999999999</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1400</v>
+        <v>1225</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -15539,23 +15540,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>520</v>
+        <v>487.5</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>753.5</v>
+        <v>685</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>1002.4000000000001</v>
+        <v>895</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>1263.0999999999999</v>
+        <v>1114.5</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>1532</v>
+        <v>1340.5</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -15579,23 +15580,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>812.9</v>
+        <v>739</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>1083.5999999999999</v>
+        <v>967.5</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1368.5</v>
+        <v>1207.5</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>1664</v>
+        <v>1456</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -15619,23 +15620,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>600</v>
+        <v>562.5</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>872.3</v>
+        <v>793</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>1164.8</v>
+        <v>1040</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>1473.8999999999999</v>
+        <v>1300.5</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>1796</v>
+        <v>1571.5</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -15659,23 +15660,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>931.7</v>
+        <v>847</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>1246</v>
+        <v>1112.5</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>1579.3</v>
+        <v>1393.5</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>1928.0000000000002</v>
+        <v>1687.0000000000002</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -15699,23 +15700,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>680</v>
+        <v>637.5</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>991.09999999999991</v>
+        <v>901</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>1327.2</v>
+        <v>1185</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>1684.6999999999998</v>
+        <v>1486.5</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>2060</v>
+        <v>1802.5</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -15739,23 +15740,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>720</v>
+        <v>675</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>1050.5</v>
+        <v>955</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>1408.4</v>
+        <v>1257.5</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>1790.1</v>
+        <v>1579.5</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>2192</v>
+        <v>1918</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -15779,23 +15780,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>760</v>
+        <v>712.5</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>1109.8999999999999</v>
+        <v>1009</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>1489.6</v>
+        <v>1330</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>1895.4999999999998</v>
+        <v>1672.5</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>2324</v>
+        <v>2033.5</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -15819,23 +15820,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>1169.3</v>
+        <v>1063</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>1570.8000000000002</v>
+        <v>1402.5</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>2000.8999999999999</v>
+        <v>1765.5</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>2456</v>
+        <v>2149</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -15859,23 +15860,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>840</v>
+        <v>787.5</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>1228.7</v>
+        <v>1117</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>1652</v>
+        <v>1475</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>2106.3000000000002</v>
+        <v>1858.5</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>2588</v>
+        <v>2264.5</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -15899,23 +15900,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>880</v>
+        <v>825</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>1288.0999999999999</v>
+        <v>1171</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>1733.2</v>
+        <v>1547.5</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>2211.6999999999998</v>
+        <v>1951.5</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>2720</v>
+        <v>2380</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -15939,23 +15940,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>920</v>
+        <v>862.5</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>1347.5</v>
+        <v>1225</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>1814.4</v>
+        <v>1620</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>2317.1</v>
+        <v>2044.5</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>2852</v>
+        <v>2495.5</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -15979,23 +15980,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>960</v>
+        <v>900</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>1406.9</v>
+        <v>1279</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>1895.6</v>
+        <v>1692.5</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>2422.5</v>
+        <v>2137.5</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>2984</v>
+        <v>2611</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -16019,23 +16020,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>1000</v>
+        <v>937.5</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>1466.3</v>
+        <v>1333</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>1976.8</v>
+        <v>1765</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>2527.8999999999996</v>
+        <v>2230.5</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>3116</v>
+        <v>2726.5</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -16193,7 +16194,7 @@
     </row>
     <row r="121" spans="2:22" ht="22" customHeight="1">
       <c r="B121" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>
@@ -16264,67 +16265,67 @@
     </row>
     <row r="124" spans="2:22" ht="35" customHeight="1">
       <c r="B124" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C124" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="D124" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="E124" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E124" s="13" t="s">
+      <c r="F124" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G124" s="13" t="s">
+      <c r="I124" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J124" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K124" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H124" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J124" s="13" t="s">
+      <c r="L124" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K124" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="L124" s="13" t="s">
+      <c r="M124" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="N124" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="O124" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="M124" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N124" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O124" s="13" t="s">
+      <c r="P124" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q124" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="P124" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q124" s="13" t="s">
+      <c r="R124" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="R124" s="13" t="s">
+      <c r="S124" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="S124" s="13" t="s">
+      <c r="T124" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="T124" s="13" t="s">
+      <c r="U124" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="U124" s="13" t="s">
+      <c r="V124" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="V124" s="13" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="125" spans="2:22" ht="22" customHeight="1">
@@ -16460,7 +16461,7 @@
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
@@ -16472,7 +16473,7 @@
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>1248</v>
+        <v>1170</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -16546,7 +16547,7 @@
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
@@ -16558,7 +16559,7 @@
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>1804</v>
+        <v>1640</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -16632,7 +16633,7 @@
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
@@ -16644,7 +16645,7 @@
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>2408</v>
+        <v>2150</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -16718,7 +16719,7 @@
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
@@ -16730,7 +16731,7 @@
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>3060</v>
+        <v>2700</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -16828,7 +16829,7 @@
     </row>
     <row r="133" spans="2:22" ht="22" customHeight="1">
       <c r="B133" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C133" s="11" t="str">
         <f>B125</f>
@@ -16966,19 +16967,19 @@
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
-        <v>-110</v>
+        <v>-100</v>
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-140</v>
+        <v>-125</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -17021,19 +17022,19 @@
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-160</v>
+        <v>-150</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
-        <v>-220</v>
+        <v>-200</v>
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-280</v>
+        <v>-250</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-340</v>
+        <v>-300</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -17076,19 +17077,19 @@
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-240</v>
+        <v>-225</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
-        <v>-330</v>
+        <v>-300</v>
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-420</v>
+        <v>-375</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-510</v>
+        <v>-450</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -17131,19 +17132,19 @@
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-320</v>
+        <v>-300</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
-        <v>-440</v>
+        <v>-400</v>
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-560</v>
+        <v>-500</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-680</v>
+        <v>-600</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -17186,19 +17187,19 @@
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-400</v>
+        <v>-375</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
-        <v>-550</v>
+        <v>-500</v>
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-700</v>
+        <v>-625</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-850</v>
+        <v>-750</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -17241,19 +17242,19 @@
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-480</v>
+        <v>-450</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-660</v>
+        <v>-600</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-840</v>
+        <v>-750</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-1020</v>
+        <v>-900</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -17296,19 +17297,19 @@
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-551.19999999999993</v>
+        <v>-516.75</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-770</v>
+        <v>-700</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-979.99999999999989</v>
+        <v>-875</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1190</v>
+        <v>-1050</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -17351,19 +17352,19 @@
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-613.59999999999991</v>
+        <v>-575.25</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-860.2</v>
+        <v>-782.00000000000011</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-1110.2</v>
+        <v>-991.25</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1360</v>
+        <v>-1200</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -17406,19 +17407,19 @@
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-676</v>
+        <v>-633.75</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-950.40000000000009</v>
+        <v>-864</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1230.5999999999999</v>
+        <v>-1098.75</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-1513</v>
+        <v>-1335</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -17461,19 +17462,19 @@
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-738.4</v>
+        <v>-692.25</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-1040.5999999999999</v>
+        <v>-946</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-1351</v>
+        <v>-1206.25</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-1666</v>
+        <v>-1470</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -17516,19 +17517,19 @@
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-800.8</v>
+        <v>-750.75</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-1130.8000000000002</v>
+        <v>-1028</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-1471.4</v>
+        <v>-1313.75</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-1819</v>
+        <v>-1605</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -17571,19 +17572,19 @@
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-863.19999999999993</v>
+        <v>-809.25</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-1221</v>
+        <v>-1110</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-1591.8</v>
+        <v>-1421.25</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-1972</v>
+        <v>-1740</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -17626,19 +17627,19 @@
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-925.59999999999991</v>
+        <v>-867.75</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-1311.2</v>
+        <v>-1192</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-1712.2</v>
+        <v>-1528.75</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-2125</v>
+        <v>-1875</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -17681,19 +17682,19 @@
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-987.99999999999989</v>
+        <v>-926.25</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-1401.4</v>
+        <v>-1274</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-1832.6</v>
+        <v>-1636.25</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-2278</v>
+        <v>-2009.9999999999998</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -17736,19 +17737,19 @@
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-1050.4000000000001</v>
+        <v>-984.75</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-1491.6</v>
+        <v>-1356</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-1953</v>
+        <v>-1743.75</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-2431</v>
+        <v>-2145</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -17791,19 +17792,19 @@
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-1112.8</v>
+        <v>-1043.25</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-1581.8000000000002</v>
+        <v>-1438</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-2073.4</v>
+        <v>-1851.25</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-2584</v>
+        <v>-2280</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -17846,19 +17847,19 @@
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-1175.1999999999998</v>
+        <v>-1101.75</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-1672</v>
+        <v>-1520</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-2193.8000000000002</v>
+        <v>-1958.75</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-2737</v>
+        <v>-2415</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -17901,19 +17902,19 @@
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-1237.5999999999999</v>
+        <v>-1160.25</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-1762.2</v>
+        <v>-1602</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-2314.1999999999998</v>
+        <v>-2066.25</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-2890</v>
+        <v>-2550</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -17956,19 +17957,19 @@
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-1300</v>
+        <v>-1218.75</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-1852.3999999999999</v>
+        <v>-1684</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-2434.6</v>
+        <v>-2173.75</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-3043</v>
+        <v>-2685</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -18011,19 +18012,19 @@
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-1362.4</v>
+        <v>-1277.25</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-1942.6000000000001</v>
+        <v>-1766</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-2555</v>
+        <v>-2281.25</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-3196</v>
+        <v>-2820</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>
@@ -18107,7 +18108,7 @@
     </row>
     <row r="161" spans="2:22">
       <c r="B161" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C161" s="30"/>
       <c r="D161" s="30"/>
@@ -18132,67 +18133,67 @@
     </row>
     <row r="164" spans="2:22">
       <c r="B164" t="s">
+        <v>63</v>
+      </c>
+      <c r="C164" t="s">
         <v>64</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>65</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>66</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
+        <v>21</v>
+      </c>
+      <c r="G164" t="s">
+        <v>82</v>
+      </c>
+      <c r="H164" t="s">
         <v>67</v>
       </c>
-      <c r="F164" t="s">
-        <v>22</v>
-      </c>
-      <c r="G164" t="s">
+      <c r="I164" t="s">
+        <v>57</v>
+      </c>
+      <c r="J164" t="s">
+        <v>68</v>
+      </c>
+      <c r="K164" t="s">
         <v>83</v>
       </c>
-      <c r="H164" t="s">
-        <v>68</v>
-      </c>
-      <c r="I164" t="s">
-        <v>58</v>
-      </c>
-      <c r="J164" t="s">
+      <c r="L164" t="s">
         <v>69</v>
       </c>
-      <c r="K164" t="s">
-        <v>84</v>
-      </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164" t="s">
         <v>70</v>
       </c>
-      <c r="M164" t="s">
-        <v>29</v>
-      </c>
-      <c r="N164" t="s">
-        <v>30</v>
-      </c>
-      <c r="O164" t="s">
+      <c r="P164" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q164" t="s">
         <v>71</v>
       </c>
-      <c r="P164" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q164" t="s">
+      <c r="R164" t="s">
         <v>72</v>
       </c>
-      <c r="R164" t="s">
+      <c r="S164" t="s">
         <v>73</v>
       </c>
-      <c r="S164" t="s">
+      <c r="T164" t="s">
         <v>74</v>
       </c>
-      <c r="T164" t="s">
+      <c r="U164" t="s">
         <v>75</v>
       </c>
-      <c r="U164" t="s">
+      <c r="V164" t="s">
         <v>76</v>
-      </c>
-      <c r="V164" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="165" spans="2:22">
@@ -18238,7 +18239,7 @@
       </c>
       <c r="M165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="N165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
@@ -18250,7 +18251,7 @@
       </c>
       <c r="P165">
         <f>M165*O165</f>
-        <v>1804</v>
+        <v>1640</v>
       </c>
       <c r="Q165">
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A50490-75B4-4926-9251-292E108C01E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DCEB5D-1A26-4980-AE5D-B24DCA0DE274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -483,22 +483,10 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -507,8 +495,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -682,64 +682,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>180</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270</c:v>
+                  <c:v>139</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>360</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>450</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>540</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>630</c:v>
+                  <c:v>295</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>666</c:v>
+                  <c:v>334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>702</c:v>
+                  <c:v>373</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>738</c:v>
+                  <c:v>412</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>774</c:v>
+                  <c:v>451.00000000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>810</c:v>
+                  <c:v>490</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>871</c:v>
+                  <c:v>654.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>932</c:v>
+                  <c:v>818</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>993</c:v>
+                  <c:v>982</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1054</c:v>
+                  <c:v>1146.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1115</c:v>
+                  <c:v>1310</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1176</c:v>
+                  <c:v>1474</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1237</c:v>
+                  <c:v>1638</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1298</c:v>
+                  <c:v>1802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,64 +858,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120</c:v>
+                  <c:v>87.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>240</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>249.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>320.07500000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>600</c:v>
+                  <c:v>390.95000000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>720</c:v>
+                  <c:v>461.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>840</c:v>
+                  <c:v>532.70000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>894</c:v>
+                  <c:v>603.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>948</c:v>
+                  <c:v>674.45</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1002</c:v>
+                  <c:v>745.32500000000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1056</c:v>
+                  <c:v>816.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1110</c:v>
+                  <c:v>887.07499999999993</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1189</c:v>
+                  <c:v>1082.9500000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1268</c:v>
+                  <c:v>1278.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1347</c:v>
+                  <c:v>1474.7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1426</c:v>
+                  <c:v>1670.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1505</c:v>
+                  <c:v>1866.45</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1584</c:v>
+                  <c:v>2062.3250000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1663</c:v>
+                  <c:v>2258.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1742</c:v>
+                  <c:v>2454.0749999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1034,64 +1034,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1125</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1200</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1275</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1350</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1425</c:v>
+                  <c:v>1308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1525</c:v>
+                  <c:v>1538</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1625</c:v>
+                  <c:v>1768</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1725</c:v>
+                  <c:v>1998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1825</c:v>
+                  <c:v>2228</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1925</c:v>
+                  <c:v>2458</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025</c:v>
+                  <c:v>2688</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2125</c:v>
+                  <c:v>2918</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2225</c:v>
+                  <c:v>3148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1210,64 +1210,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>162.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>479.04999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>620.42499999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>761.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>903.17499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1260</c:v>
+                  <c:v>1044.55</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1359</c:v>
+                  <c:v>1185.9250000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1458</c:v>
+                  <c:v>1327.3000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1557</c:v>
+                  <c:v>1468.675</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1656.0000000000002</c:v>
+                  <c:v>1610.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1755</c:v>
+                  <c:v>1751.425</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1879</c:v>
+                  <c:v>2017.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2003</c:v>
+                  <c:v>2284.1749999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2127</c:v>
+                  <c:v>2550.5500000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2251</c:v>
+                  <c:v>2816.9250000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2375</c:v>
+                  <c:v>3083.3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2499</c:v>
+                  <c:v>3349.6750000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2623</c:v>
+                  <c:v>3616.0499999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2747</c:v>
+                  <c:v>3882.4250000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1386,64 +1386,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>210</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>420</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>630</c:v>
+                  <c:v>595.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>840</c:v>
+                  <c:v>776</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1050</c:v>
+                  <c:v>956</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1260</c:v>
+                  <c:v>1136</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1470</c:v>
+                  <c:v>1316</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1596</c:v>
+                  <c:v>1496</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1722</c:v>
+                  <c:v>1676</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1848</c:v>
+                  <c:v>1856</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1974.0000000000002</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2100</c:v>
+                  <c:v>2216</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2251</c:v>
+                  <c:v>2521</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2402</c:v>
+                  <c:v>2826</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2553</c:v>
+                  <c:v>3131</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2704</c:v>
+                  <c:v>3436</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2855</c:v>
+                  <c:v>3741</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3006</c:v>
+                  <c:v>4046</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3157</c:v>
+                  <c:v>4351</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3308</c:v>
+                  <c:v>4656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,64 +1762,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>825</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>975</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1125</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1340</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1495</c:v>
+                  <c:v>1375</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1649.9999999999998</c:v>
+                  <c:v>1475</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1805</c:v>
+                  <c:v>1575</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1960</c:v>
+                  <c:v>1675</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2115</c:v>
+                  <c:v>1775</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2270</c:v>
+                  <c:v>1875</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2425</c:v>
+                  <c:v>1975</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2580</c:v>
+                  <c:v>2075</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1938,64 +1938,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>975</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1125</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1337.5</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1530</c:v>
+                  <c:v>1450</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1722.4999999999998</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1915</c:v>
+                  <c:v>1650</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2107.5</c:v>
+                  <c:v>1750</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2300</c:v>
+                  <c:v>1850</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2492.5</c:v>
+                  <c:v>1950</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2685</c:v>
+                  <c:v>2050</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2877.5</c:v>
+                  <c:v>2150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,64 +2114,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>1125</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1320</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1550</c:v>
+                  <c:v>1525</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1779.9999999999998</c:v>
+                  <c:v>1625</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2010</c:v>
+                  <c:v>1725</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2240</c:v>
+                  <c:v>1825</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2470</c:v>
+                  <c:v>1925</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2700</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2930</c:v>
+                  <c:v>2125</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3160</c:v>
+                  <c:v>2225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2290,64 +2290,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1320</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1555</c:v>
+                  <c:v>1600</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1822.4999999999995</c:v>
+                  <c:v>1700</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2090</c:v>
+                  <c:v>1800</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2357.5</c:v>
+                  <c:v>1900</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2625</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2892.5</c:v>
+                  <c:v>2100</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3160</c:v>
+                  <c:v>2200</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3427.5</c:v>
+                  <c:v>2300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,64 +2466,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1425</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1320</c:v>
+                  <c:v>1575</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1545</c:v>
+                  <c:v>1675</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1849.9999999999995</c:v>
+                  <c:v>1775</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2155</c:v>
+                  <c:v>1875</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2460</c:v>
+                  <c:v>1975</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2765</c:v>
+                  <c:v>2075</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3070</c:v>
+                  <c:v>2175</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3375</c:v>
+                  <c:v>2275</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3680</c:v>
+                  <c:v>2375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2842,64 +2842,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>225</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>300</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>375</c:v>
+                  <c:v>244.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>412.5</c:v>
+                  <c:v>280.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>450</c:v>
+                  <c:v>316.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>487.5</c:v>
+                  <c:v>352.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>525</c:v>
+                  <c:v>388.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>562.5</c:v>
+                  <c:v>424.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>600</c:v>
+                  <c:v>460.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>637.5</c:v>
+                  <c:v>496.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>675</c:v>
+                  <c:v>532.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>712.5</c:v>
+                  <c:v>568.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>750</c:v>
+                  <c:v>604.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>787.5</c:v>
+                  <c:v>640.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>825</c:v>
+                  <c:v>676.4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>862.5</c:v>
+                  <c:v>712.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>900</c:v>
+                  <c:v>748.4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>937.5</c:v>
+                  <c:v>784.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3018,64 +3018,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>400</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>500</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>577</c:v>
+                  <c:v>433.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>631</c:v>
+                  <c:v>490.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>685</c:v>
+                  <c:v>547.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>739</c:v>
+                  <c:v>604.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>793</c:v>
+                  <c:v>661.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>847</c:v>
+                  <c:v>718.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>901</c:v>
+                  <c:v>775.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>955</c:v>
+                  <c:v>832.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1009</c:v>
+                  <c:v>889.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1063</c:v>
+                  <c:v>946.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1117</c:v>
+                  <c:v>1003.8000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1171</c:v>
+                  <c:v>1060.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1225</c:v>
+                  <c:v>1117.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1279</c:v>
+                  <c:v>1174.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1333</c:v>
+                  <c:v>1231.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,64 +3194,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>625</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>750</c:v>
+                  <c:v>591.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>822.5</c:v>
+                  <c:v>671.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>895</c:v>
+                  <c:v>752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>967.5</c:v>
+                  <c:v>832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1040</c:v>
+                  <c:v>912</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1112.5</c:v>
+                  <c:v>992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1185</c:v>
+                  <c:v>1072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1257.5</c:v>
+                  <c:v>1152</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1330</c:v>
+                  <c:v>1232</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1402.5</c:v>
+                  <c:v>1312</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1475</c:v>
+                  <c:v>1392</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1547.5</c:v>
+                  <c:v>1472</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1620</c:v>
+                  <c:v>1552</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1692.5</c:v>
+                  <c:v>1632</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1765</c:v>
+                  <c:v>1712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3370,64 +3370,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>900</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>1021.4999999999999</c:v>
+                  <c:v>857</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1114.5</c:v>
+                  <c:v>962</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1207.5</c:v>
+                  <c:v>1067</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1300.5</c:v>
+                  <c:v>1172</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1393.5</c:v>
+                  <c:v>1277</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1486.5</c:v>
+                  <c:v>1382</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1579.5</c:v>
+                  <c:v>1487</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1672.5</c:v>
+                  <c:v>1592</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1765.5</c:v>
+                  <c:v>1697</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1858.5</c:v>
+                  <c:v>1802</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1951.5</c:v>
+                  <c:v>1907</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2044.5</c:v>
+                  <c:v>2012</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2137.5</c:v>
+                  <c:v>2117</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2230.5</c:v>
+                  <c:v>2222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3546,64 +3546,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>350</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>525</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1050</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1225</c:v>
+                  <c:v>1042.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1340.5</c:v>
+                  <c:v>1174.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1456</c:v>
+                  <c:v>1306.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1571.5</c:v>
+                  <c:v>1438.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1687.0000000000002</c:v>
+                  <c:v>1570.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1802.5</c:v>
+                  <c:v>1702.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1918</c:v>
+                  <c:v>1834.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2033.5</c:v>
+                  <c:v>1966.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2149</c:v>
+                  <c:v>2098.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2264.5</c:v>
+                  <c:v>2230.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2380</c:v>
+                  <c:v>2362.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2495.5</c:v>
+                  <c:v>2494.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2611</c:v>
+                  <c:v>2626.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2726.5</c:v>
+                  <c:v>2758.7999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3921,58 +3921,58 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>143.4</c:v>
+                  <c:v>139</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>182.4</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>221.4</c:v>
+                  <c:v>217</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>260.39999999999998</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>299.39999999999998</c:v>
+                  <c:v>295</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>338.40000000000003</c:v>
+                  <c:v>334</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>377.40000000000003</c:v>
+                  <c:v>373</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>416.4</c:v>
+                  <c:v>412</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>455.40000000000003</c:v>
+                  <c:v>451.00000000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>514.4</c:v>
+                  <c:v>510</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>603.40000000000009</c:v>
+                  <c:v>599</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>692.4</c:v>
+                  <c:v>688</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>781.4</c:v>
+                  <c:v>777</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>870.4000000000002</c:v>
+                  <c:v>866.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>959.4</c:v>
+                  <c:v>955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1048.4000000000001</c:v>
+                  <c:v>1044</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1137.4000000000001</c:v>
+                  <c:v>1133</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1226.4000000000001</c:v>
+                  <c:v>1222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4097,58 +4097,58 @@
                   <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>257.51249999999999</c:v>
+                  <c:v>249.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>328.38750000000005</c:v>
+                  <c:v>320.07500000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>399.26250000000005</c:v>
+                  <c:v>390.95000000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>470.13749999999999</c:v>
+                  <c:v>461.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>541.01249999999993</c:v>
+                  <c:v>532.70000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>611.88750000000005</c:v>
+                  <c:v>603.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>682.76250000000005</c:v>
+                  <c:v>674.45</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>753.63749999999993</c:v>
+                  <c:v>745.32500000000005</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>824.51250000000005</c:v>
+                  <c:v>816.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>912.88749999999993</c:v>
+                  <c:v>904.57499999999993</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1071.2625</c:v>
+                  <c:v>1062.95</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1229.6375</c:v>
+                  <c:v>1221.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1388.0125</c:v>
+                  <c:v>1379.7</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1546.3875000000003</c:v>
+                  <c:v>1538.0750000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1704.7625</c:v>
+                  <c:v>1696.45</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1863.1375000000003</c:v>
+                  <c:v>1854.8250000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2021.5124999999998</c:v>
+                  <c:v>2013.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2179.8874999999998</c:v>
+                  <c:v>2171.5749999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4273,58 +4273,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>585</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>795</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1005.0000000000001</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1110</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1215</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1320</c:v>
+                  <c:v>1308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1550</c:v>
+                  <c:v>1538</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1779.9999999999998</c:v>
+                  <c:v>1768</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2010</c:v>
+                  <c:v>1998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2240</c:v>
+                  <c:v>2228</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2470</c:v>
+                  <c:v>2458</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2700</c:v>
+                  <c:v>2688</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2930</c:v>
+                  <c:v>2918</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3160</c:v>
+                  <c:v>3148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4449,58 +4449,58 @@
                   <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>487.5</c:v>
+                  <c:v>479.04999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>633.1</c:v>
+                  <c:v>620.42499999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>774.47500000000002</c:v>
+                  <c:v>761.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>915.84999999999991</c:v>
+                  <c:v>903.17499999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1057.2249999999999</c:v>
+                  <c:v>1044.55</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1198.5999999999999</c:v>
+                  <c:v>1185.9250000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1339.9750000000001</c:v>
+                  <c:v>1327.3000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1481.35</c:v>
+                  <c:v>1468.675</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1622.7250000000001</c:v>
+                  <c:v>1610.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1764.1</c:v>
+                  <c:v>1751.425</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2035.4749999999999</c:v>
+                  <c:v>2022.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2339.3499999999995</c:v>
+                  <c:v>2326.6749999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2643.2249999999999</c:v>
+                  <c:v>2630.55</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2947.1000000000004</c:v>
+                  <c:v>2934.4250000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3250.9749999999999</c:v>
+                  <c:v>3238.3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3554.85</c:v>
+                  <c:v>3542.1750000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3858.7249999999999</c:v>
+                  <c:v>3846.0499999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4162.6000000000004</c:v>
+                  <c:v>4149.9250000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4625,58 +4625,58 @@
                   <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>600</c:v>
+                  <c:v>595.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>788</c:v>
+                  <c:v>776</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>968</c:v>
+                  <c:v>956</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1148</c:v>
+                  <c:v>1136</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1328</c:v>
+                  <c:v>1316</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1508</c:v>
+                  <c:v>1496</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1688</c:v>
+                  <c:v>1676</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1867.9999999999998</c:v>
+                  <c:v>1856</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2048</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2228</c:v>
+                  <c:v>2216</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2528</c:v>
+                  <c:v>2516</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2908</c:v>
+                  <c:v>2896</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3288</c:v>
+                  <c:v>3276</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3668</c:v>
+                  <c:v>3656</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4048</c:v>
+                  <c:v>4036</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4428</c:v>
+                  <c:v>4416</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4807.9999999999991</c:v>
+                  <c:v>4796</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5188</c:v>
+                  <c:v>5176</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4807,52 +4807,52 @@
                   <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-250</c:v>
+                  <c:v>-244.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-300</c:v>
+                  <c:v>-280.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-337</c:v>
+                  <c:v>-316.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-374</c:v>
+                  <c:v>-352.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-411</c:v>
+                  <c:v>-388.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-448</c:v>
+                  <c:v>-424.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-485</c:v>
+                  <c:v>-460.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-522</c:v>
+                  <c:v>-496.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-559</c:v>
+                  <c:v>-532.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-596</c:v>
+                  <c:v>-568.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-633</c:v>
+                  <c:v>-604.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-670</c:v>
+                  <c:v>-640.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-707</c:v>
+                  <c:v>-676.4</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-744</c:v>
+                  <c:v>-712.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-781</c:v>
+                  <c:v>-748.4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-818</c:v>
+                  <c:v>-784.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4986,49 +4986,49 @@
                   <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-450</c:v>
+                  <c:v>-433.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-516.75</c:v>
+                  <c:v>-490.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-575.25</c:v>
+                  <c:v>-547.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-633.75</c:v>
+                  <c:v>-604.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-692.25</c:v>
+                  <c:v>-661.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-750.75</c:v>
+                  <c:v>-718.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-809.25</c:v>
+                  <c:v>-775.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-867.75</c:v>
+                  <c:v>-832.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-926.25</c:v>
+                  <c:v>-889.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-984.75</c:v>
+                  <c:v>-946.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1043.25</c:v>
+                  <c:v>-1003.8000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1101.75</c:v>
+                  <c:v>-1060.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1160.25</c:v>
+                  <c:v>-1117.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1218.75</c:v>
+                  <c:v>-1174.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1277.25</c:v>
+                  <c:v>-1231.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5162,49 +5162,49 @@
                   <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-600</c:v>
+                  <c:v>-591.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-700</c:v>
+                  <c:v>-671.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-782.00000000000011</c:v>
+                  <c:v>-752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-864</c:v>
+                  <c:v>-832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-946</c:v>
+                  <c:v>-912</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1028</c:v>
+                  <c:v>-992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1110</c:v>
+                  <c:v>-1072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1192</c:v>
+                  <c:v>-1152</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1274</c:v>
+                  <c:v>-1232</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1356</c:v>
+                  <c:v>-1312</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1438</c:v>
+                  <c:v>-1392</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1520</c:v>
+                  <c:v>-1472</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1602</c:v>
+                  <c:v>-1552</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1684</c:v>
+                  <c:v>-1632</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1766</c:v>
+                  <c:v>-1712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5341,46 +5341,46 @@
                   <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-875</c:v>
+                  <c:v>-857</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-991.25</c:v>
+                  <c:v>-962</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1098.75</c:v>
+                  <c:v>-1067</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1206.25</c:v>
+                  <c:v>-1172</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1313.75</c:v>
+                  <c:v>-1277</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1421.25</c:v>
+                  <c:v>-1382</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1528.75</c:v>
+                  <c:v>-1487</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1636.25</c:v>
+                  <c:v>-1592</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1743.75</c:v>
+                  <c:v>-1697</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1851.25</c:v>
+                  <c:v>-1802</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1958.75</c:v>
+                  <c:v>-1907</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2066.25</c:v>
+                  <c:v>-2012</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2173.75</c:v>
+                  <c:v>-2117</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2281.25</c:v>
+                  <c:v>-2222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5517,46 +5517,46 @@
                   <c:v>-900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1050</c:v>
+                  <c:v>-1042.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1200</c:v>
+                  <c:v>-1174.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1335</c:v>
+                  <c:v>-1306.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1470</c:v>
+                  <c:v>-1438.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1605</c:v>
+                  <c:v>-1570.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1740</c:v>
+                  <c:v>-1702.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1875</c:v>
+                  <c:v>-1834.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-2009.9999999999998</c:v>
+                  <c:v>-1966.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2145</c:v>
+                  <c:v>-2098.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2280</c:v>
+                  <c:v>-2230.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2415</c:v>
+                  <c:v>-2362.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2550</c:v>
+                  <c:v>-2494.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2685</c:v>
+                  <c:v>-2626.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2820</c:v>
+                  <c:v>-2758.7999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6126,20 +6126,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6169,17 +6169,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6210,13 +6210,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6254,16 +6254,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="27">
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>2240</v>
-      </c>
-      <c r="J8" s="27"/>
+        <v>2228</v>
+      </c>
+      <c r="J8" s="24"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -6301,16 +6301,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="27">
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="24">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1438</v>
-      </c>
-      <c r="J10" s="27"/>
+        <v>1392</v>
+      </c>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -6362,13 +6362,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
         <v>2500</v>
@@ -6415,11 +6415,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
         <v>2100</v>
@@ -6439,11 +6439,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
         <v>2500</v>
@@ -6463,11 +6463,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
         <v>4600</v>
@@ -6509,11 +6509,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -6533,14 +6533,14 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>22</v>
@@ -6574,14 +6574,14 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>23</v>
@@ -6598,11 +6598,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
@@ -6622,14 +6622,14 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>23</v>
@@ -6676,20 +6676,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -6950,6 +6950,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -6957,17 +6968,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -7028,20 +7028,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7068,20 +7068,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7111,17 +7111,17 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7705,20 +7705,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7792,20 +7792,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7832,20 +7832,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7875,17 +7875,17 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8469,20 +8469,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8556,20 +8556,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8596,20 +8596,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8632,20 +8632,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9229,20 +9229,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9312,20 +9312,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9355,17 +9355,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9388,20 +9388,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9985,20 +9985,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10072,40 +10072,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10129,21 +10129,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -10365,21 +10365,21 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="5">
         <f>(D11+F11)/2</f>
-        <v>0.13500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="F11" s="4">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="G11" s="5">
         <f>(F11+H11)/2</f>
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H11" s="4">
-        <v>0.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="4">
@@ -10428,21 +10428,21 @@
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="4">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="K12" s="5">
         <f>(J12+L12)/2</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="L12" s="4">
         <v>0.5</v>
       </c>
       <c r="M12" s="5">
         <f>(L12+N12)/2</f>
-        <v>0.55000000000000004</v>
+        <v>0.53</v>
       </c>
       <c r="N12" s="4">
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="O12" s="1"/>
     </row>
@@ -10658,39 +10658,39 @@
         <v>23</v>
       </c>
       <c r="D18" s="4">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="E18" s="5">
         <f>(D18+F18)/2</f>
-        <v>0.32499999999999996</v>
+        <v>0.255</v>
       </c>
       <c r="F18" s="4">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G18" s="5">
         <f>(F18+H18)/2</f>
-        <v>0.375</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="H18" s="4">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="K18" s="5">
         <f>(J18+L18)/2</f>
-        <v>0.27500000000000002</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="L18" s="4">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M18" s="5">
         <f>(L18+N18)/2</f>
-        <v>0.32499999999999996</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="N18" s="4">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="O18" s="1"/>
     </row>
@@ -10703,21 +10703,21 @@
         <v>25</v>
       </c>
       <c r="D19" s="4">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="E19" s="5">
         <f>(D19+F19)/2</f>
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F19" s="4">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="G19" s="5">
         <f>(F19+H19)/2</f>
-        <v>0.86</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="H19" s="4">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4">
@@ -10775,73 +10775,73 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="22"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10859,25 +10859,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="22"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -10899,154 +10899,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11153,17 +11153,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -11172,6 +11161,17 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11351,23 +11351,23 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11375,23 +11375,23 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>1220</v>
+        <v>3280</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11438,23 +11438,23 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>2400</v>
+        <v>1750</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.45</v>
+        <v>0.81</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>1080</v>
+        <v>1417.5</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11462,23 +11462,23 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>1580</v>
+        <v>3917.5</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.27500000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11525,23 +11525,23 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11549,23 +11549,23 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.3</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -11612,23 +11612,23 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3600</v>
+        <v>3250</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.55000000000000004</v>
+        <v>0.87</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>1980.0000000000002</v>
+        <v>2827.5</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11636,23 +11636,23 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>2480</v>
+        <v>5327.5</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.32499999999999996</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.62</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>1860</v>
+        <v>2100</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11699,23 +11699,23 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.35</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>2520</v>
+        <v>3600</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11723,23 +11723,23 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>3020</v>
+        <v>6100</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>2310</v>
+        <v>2640</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11927,23 +11927,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>87.5</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -11968,23 +11968,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -12009,23 +12009,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>249.2</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>479.04999999999995</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>630</v>
+        <v>595.99999999999989</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12050,23 +12050,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>178</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>320.07500000000005</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>720</v>
+        <v>620.42499999999995</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>840</v>
+        <v>776</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -12091,23 +12091,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>217</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>390.95000000000005</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>900</v>
+        <v>761.8</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>1050</v>
+        <v>956</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -12132,23 +12132,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>256</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>461.82499999999999</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>678</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>1080</v>
+        <v>903.17499999999995</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1260</v>
+        <v>1136</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -12173,23 +12173,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>295</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>532.70000000000005</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>783</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1260</v>
+        <v>1044.55</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1470</v>
+        <v>1316</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -12214,23 +12214,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>666</v>
+        <v>334</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>894</v>
+        <v>603.57500000000005</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>888</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1359</v>
+        <v>1185.9250000000002</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>1596</v>
+        <v>1496</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -12255,23 +12255,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>702</v>
+        <v>373</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>948</v>
+        <v>674.45</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1200</v>
+        <v>993</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>1458</v>
+        <v>1327.3000000000002</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>1722</v>
+        <v>1676</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -12296,23 +12296,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>738</v>
+        <v>412</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>1002</v>
+        <v>745.32500000000005</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1275</v>
+        <v>1098</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>1557</v>
+        <v>1468.675</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>1848</v>
+        <v>1856</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -12337,23 +12337,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>774</v>
+        <v>451.00000000000006</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>1056</v>
+        <v>816.2</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>1350</v>
+        <v>1203</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>1656.0000000000002</v>
+        <v>1610.0500000000002</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>1974.0000000000002</v>
+        <v>2036</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -12378,23 +12378,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>490</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>1110</v>
+        <v>887.07499999999993</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>1425</v>
+        <v>1308</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>1755</v>
+        <v>1751.425</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>2100</v>
+        <v>2216</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -12419,23 +12419,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>871</v>
+        <v>654.00000000000011</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1189</v>
+        <v>1082.9500000000003</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1525</v>
+        <v>1538</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>1879</v>
+        <v>2017.8000000000002</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2251</v>
+        <v>2521</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12460,23 +12460,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>932</v>
+        <v>818</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1268</v>
+        <v>1278.8249999999998</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1625</v>
+        <v>1768</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>2003</v>
+        <v>2284.1749999999997</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2402</v>
+        <v>2826</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12501,23 +12501,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1347</v>
+        <v>1474.7</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>1725</v>
+        <v>1998</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2127</v>
+        <v>2550.5500000000002</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>2553</v>
+        <v>3131</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12542,23 +12542,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1054</v>
+        <v>1146.0000000000002</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1426</v>
+        <v>1670.5750000000003</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>1825</v>
+        <v>2228</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2251</v>
+        <v>2816.9250000000002</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>2704</v>
+        <v>3436</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12583,23 +12583,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1115</v>
+        <v>1310</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>1505</v>
+        <v>1866.45</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>1925</v>
+        <v>2458</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>2375</v>
+        <v>3083.3</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>2855</v>
+        <v>3741</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12624,23 +12624,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1176</v>
+        <v>1474</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>1584</v>
+        <v>2062.3250000000003</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2025</v>
+        <v>2688</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>2499</v>
+        <v>3349.6750000000002</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>3006</v>
+        <v>4046</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12665,23 +12665,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1237</v>
+        <v>1638</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>1663</v>
+        <v>2258.1999999999998</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>2125</v>
+        <v>2918</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>2623</v>
+        <v>3616.0499999999997</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>3157</v>
+        <v>4351</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12706,23 +12706,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1298</v>
+        <v>1802</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>1742</v>
+        <v>2454.0749999999998</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>2225</v>
+        <v>3148</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>2747</v>
+        <v>3882.4250000000002</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>3308</v>
+        <v>4656</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -13041,47 +13041,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>3100</v>
+        <v>2000</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -13127,47 +13127,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>3850</v>
+        <v>2000</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.32499999999999996</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>1170</v>
+        <v>1080</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -13213,23 +13213,23 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13237,23 +13237,23 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>4600</v>
+        <v>2000</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.82</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>1640</v>
+        <v>1450</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -13299,47 +13299,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>3250</v>
+        <v>500</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>5350</v>
+        <v>2000</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.375</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>2150</v>
+        <v>1860</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -13385,47 +13385,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>6100</v>
+        <v>2000</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>2700</v>
+        <v>2310</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -13607,23 +13607,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -13647,23 +13647,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -13687,23 +13687,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -13727,23 +13727,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -13767,23 +13767,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -13807,23 +13807,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>690</v>
+        <v>825</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>690</v>
+        <v>900</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -13847,23 +13847,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>795</v>
+        <v>900</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>795</v>
+        <v>975</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>795</v>
+        <v>1050</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>795</v>
+        <v>1050</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>795</v>
+        <v>1050</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -13887,23 +13887,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>900</v>
+        <v>975</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -13927,23 +13927,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1005.0000000000001</v>
+        <v>1050</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1005.0000000000001</v>
+        <v>1125</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1005.0000000000001</v>
+        <v>1200</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1005.0000000000001</v>
+        <v>1275</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1005.0000000000001</v>
+        <v>1350</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -13967,23 +13967,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1110</v>
+        <v>1200</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1110</v>
+        <v>1275</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>1110</v>
+        <v>1350</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>1110</v>
+        <v>1425</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -14007,23 +14007,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1215</v>
+        <v>1200</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>1215</v>
+        <v>1275</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>1215</v>
+        <v>1350</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>1215</v>
+        <v>1425</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>1215</v>
+        <v>1500</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -14047,23 +14047,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1340</v>
+        <v>1275</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1337.5</v>
+        <v>1350</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>1320</v>
+        <v>1425</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>1320</v>
+        <v>1500</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>1320</v>
+        <v>1575</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -14087,23 +14087,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1495</v>
+        <v>1375</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1530</v>
+        <v>1450</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1555</v>
+        <v>1600</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1545</v>
+        <v>1675</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14127,23 +14127,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1649.9999999999998</v>
+        <v>1475</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1722.4999999999998</v>
+        <v>1550</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1779.9999999999998</v>
+        <v>1625</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1822.4999999999995</v>
+        <v>1700</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1849.9999999999995</v>
+        <v>1775</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14167,23 +14167,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1805</v>
+        <v>1575</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1915</v>
+        <v>1650</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>2010</v>
+        <v>1725</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>2090</v>
+        <v>1800</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>2155</v>
+        <v>1875</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14207,23 +14207,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>1960</v>
+        <v>1675</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>2107.5</v>
+        <v>1750</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>2240</v>
+        <v>1825</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>2357.5</v>
+        <v>1900</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>2460</v>
+        <v>1975</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14247,23 +14247,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>2115</v>
+        <v>1775</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>2470</v>
+        <v>1925</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2625</v>
+        <v>2000</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2765</v>
+        <v>2075</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14287,23 +14287,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>2270</v>
+        <v>1875</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>2492.5</v>
+        <v>1950</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2700</v>
+        <v>2025</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2892.5</v>
+        <v>2100</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>3070</v>
+        <v>2175</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14327,23 +14327,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>2425</v>
+        <v>1975</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2685</v>
+        <v>2050</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>2930</v>
+        <v>2125</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>3160</v>
+        <v>2200</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>3375</v>
+        <v>2275</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14367,23 +14367,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2580</v>
+        <v>2075</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2877.5</v>
+        <v>2150</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>3160</v>
+        <v>2225</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>3427.5</v>
+        <v>2300</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>3680</v>
+        <v>2375</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14694,47 +14694,47 @@
       </c>
       <c r="F85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>720</v>
+        <v>780</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1220</v>
+        <v>1780</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="O85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -14780,47 +14780,47 @@
       </c>
       <c r="F86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>2400</v>
+        <v>1750</v>
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.45</v>
+        <v>0.81</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>1080</v>
+        <v>1417.5</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="K86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>1580</v>
+        <v>3167.5</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.27500000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="O86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -14866,23 +14866,23 @@
       </c>
       <c r="F87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I87" s="8">
         <f>F87*H87</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -14890,23 +14890,23 @@
       </c>
       <c r="L87" s="8">
         <f>I87+J87</f>
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.3</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -14952,47 +14952,47 @@
       </c>
       <c r="F88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>3600</v>
+        <v>3250</v>
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.55000000000000004</v>
+        <v>0.87</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>1980.0000000000002</v>
+        <v>2827.5</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>500</v>
+        <v>3250</v>
       </c>
       <c r="K88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>2480</v>
+        <v>6077.5</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.32499999999999996</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.62</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>1860</v>
+        <v>2100</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -15038,47 +15038,47 @@
       </c>
       <c r="F89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.45</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>2520</v>
+        <v>3600</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="K89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>3020</v>
+        <v>7600</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="O89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>2310</v>
+        <v>2640</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -15260,23 +15260,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -15300,23 +15300,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -15340,23 +15340,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -15380,23 +15380,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -15420,23 +15420,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>375</v>
+        <v>244.4</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -15460,23 +15460,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>412.5</v>
+        <v>280.39999999999998</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>577</v>
+        <v>433.79999999999995</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>750</v>
+        <v>591.99999999999989</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -15500,23 +15500,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>450</v>
+        <v>316.39999999999998</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>631</v>
+        <v>490.79999999999995</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>822.5</v>
+        <v>671.99999999999989</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>1021.4999999999999</v>
+        <v>857</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1225</v>
+        <v>1042.8</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -15540,23 +15540,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>487.5</v>
+        <v>352.4</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>685</v>
+        <v>547.79999999999995</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>895</v>
+        <v>752</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>1114.5</v>
+        <v>962</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>1340.5</v>
+        <v>1174.8</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -15580,23 +15580,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>525</v>
+        <v>388.4</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>739</v>
+        <v>604.79999999999995</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>967.5</v>
+        <v>832</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1207.5</v>
+        <v>1067</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>1456</v>
+        <v>1306.8</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -15620,23 +15620,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>562.5</v>
+        <v>424.4</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>793</v>
+        <v>661.8</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>1040</v>
+        <v>912</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>1300.5</v>
+        <v>1172</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>1571.5</v>
+        <v>1438.8</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -15660,23 +15660,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>600</v>
+        <v>460.40000000000003</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>847</v>
+        <v>718.80000000000007</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>1112.5</v>
+        <v>992</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>1393.5</v>
+        <v>1277</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>1687.0000000000002</v>
+        <v>1570.8000000000002</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -15700,23 +15700,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>637.5</v>
+        <v>496.4</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>901</v>
+        <v>775.8</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>1185</v>
+        <v>1072</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>1486.5</v>
+        <v>1382</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>1802.5</v>
+        <v>1702.8</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -15740,23 +15740,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>675</v>
+        <v>532.40000000000009</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>955</v>
+        <v>832.8</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>1257.5</v>
+        <v>1152</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>1579.5</v>
+        <v>1487</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>1918</v>
+        <v>1834.8000000000002</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -15780,23 +15780,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>712.5</v>
+        <v>568.4</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>1009</v>
+        <v>889.8</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>1330</v>
+        <v>1232</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>1672.5</v>
+        <v>1592</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>2033.5</v>
+        <v>1966.7999999999997</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -15820,23 +15820,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>750</v>
+        <v>604.40000000000009</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>1063</v>
+        <v>946.8</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>1402.5</v>
+        <v>1312</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>1765.5</v>
+        <v>1697</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>2149</v>
+        <v>2098.8000000000002</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -15860,23 +15860,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>787.5</v>
+        <v>640.40000000000009</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>1117</v>
+        <v>1003.8000000000001</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>1475</v>
+        <v>1392</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>1858.5</v>
+        <v>1802</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>2264.5</v>
+        <v>2230.8000000000002</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -15900,23 +15900,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>825</v>
+        <v>676.4</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>1171</v>
+        <v>1060.8</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>1547.5</v>
+        <v>1472</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>1951.5</v>
+        <v>1907</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>2380</v>
+        <v>2362.8000000000002</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -15940,23 +15940,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>862.5</v>
+        <v>712.40000000000009</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>1225</v>
+        <v>1117.8000000000002</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>1620</v>
+        <v>1552</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>2044.5</v>
+        <v>2012</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>2495.5</v>
+        <v>2494.8000000000002</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -15980,23 +15980,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>900</v>
+        <v>748.4</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>1279</v>
+        <v>1174.8</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>1692.5</v>
+        <v>1632</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>2137.5</v>
+        <v>2117</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>2611</v>
+        <v>2626.7999999999997</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -16020,23 +16020,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>937.5</v>
+        <v>784.4</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>1333</v>
+        <v>1231.8</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>1765</v>
+        <v>1712</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>2230.5</v>
+        <v>2222</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>2726.5</v>
+        <v>2758.7999999999997</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="H125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
@@ -16379,15 +16379,15 @@
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="O125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
-        <v>0.13500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
@@ -16465,15 +16465,15 @@
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.32499999999999996</v>
+        <v>0.255</v>
       </c>
       <c r="O126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>1170</v>
+        <v>1140</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
@@ -16551,15 +16551,15 @@
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -16609,7 +16609,7 @@
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
@@ -16637,15 +16637,15 @@
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.375</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
-        <v>0.86</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
-        <v>0.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
@@ -16723,15 +16723,15 @@
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>2700</v>
+        <v>2640</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -17053,23 +17053,23 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>143.4</v>
+        <v>139</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>257.51249999999999</v>
+        <v>249.2</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>487.5</v>
+        <v>479.04999999999995</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>600</v>
+        <v>595.99999999999989</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
@@ -17108,23 +17108,23 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>182.4</v>
+        <v>178</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>328.38750000000005</v>
+        <v>320.07500000000005</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>633.1</v>
+        <v>620.42499999999995</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
@@ -17163,27 +17163,27 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>221.4</v>
+        <v>217</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>399.26250000000005</v>
+        <v>390.95000000000005</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>774.47500000000002</v>
+        <v>761.8</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-250</v>
+        <v>-244.4</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
@@ -17218,35 +17218,35 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>260.39999999999998</v>
+        <v>256</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>470.13749999999999</v>
+        <v>461.82499999999999</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>915.84999999999991</v>
+        <v>903.17499999999995</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1148</v>
+        <v>1136</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-300</v>
+        <v>-280.39999999999998</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-450</v>
+        <v>-433.79999999999995</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-600</v>
+        <v>-591.99999999999989</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
@@ -17273,43 +17273,43 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>299.39999999999998</v>
+        <v>295</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>541.01249999999993</v>
+        <v>532.70000000000005</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1057.2249999999999</v>
+        <v>1044.55</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-337</v>
+        <v>-316.39999999999998</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-516.75</v>
+        <v>-490.79999999999995</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-700</v>
+        <v>-671.99999999999989</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-875</v>
+        <v>-857</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1050</v>
+        <v>-1042.8</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -17328,43 +17328,43 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>338.40000000000003</v>
+        <v>334</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>611.88750000000005</v>
+        <v>603.57500000000005</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>1198.5999999999999</v>
+        <v>1185.9250000000002</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>1508</v>
+        <v>1496</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-374</v>
+        <v>-352.4</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-575.25</v>
+        <v>-547.79999999999995</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-782.00000000000011</v>
+        <v>-752</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-991.25</v>
+        <v>-962</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1200</v>
+        <v>-1174.8</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -17383,43 +17383,43 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>377.40000000000003</v>
+        <v>373</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>682.76250000000005</v>
+        <v>674.45</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>1005.0000000000001</v>
+        <v>993</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>1339.9750000000001</v>
+        <v>1327.3000000000002</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>1688</v>
+        <v>1676</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-411</v>
+        <v>-388.4</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-633.75</v>
+        <v>-604.79999999999995</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-864</v>
+        <v>-832</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1098.75</v>
+        <v>-1067</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-1335</v>
+        <v>-1306.8</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -17438,43 +17438,43 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>416.4</v>
+        <v>412</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>753.63749999999993</v>
+        <v>745.32500000000005</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>1481.35</v>
+        <v>1468.675</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>1867.9999999999998</v>
+        <v>1856</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-448</v>
+        <v>-424.4</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-692.25</v>
+        <v>-661.8</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-946</v>
+        <v>-912</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-1206.25</v>
+        <v>-1172</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-1470</v>
+        <v>-1438.8</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -17493,43 +17493,43 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>455.40000000000003</v>
+        <v>451.00000000000006</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>824.51250000000005</v>
+        <v>816.2</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>1622.7250000000001</v>
+        <v>1610.0500000000002</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>2048</v>
+        <v>2036</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-485</v>
+        <v>-460.40000000000003</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-750.75</v>
+        <v>-718.80000000000007</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-1028</v>
+        <v>-992</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-1313.75</v>
+        <v>-1277</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-1605</v>
+        <v>-1570.8000000000002</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -17548,43 +17548,43 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>514.4</v>
+        <v>510</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>912.88749999999993</v>
+        <v>904.57499999999993</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>1764.1</v>
+        <v>1751.425</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>2228</v>
+        <v>2216</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-522</v>
+        <v>-496.4</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-809.25</v>
+        <v>-775.8</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-1110</v>
+        <v>-1072</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-1421.25</v>
+        <v>-1382</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-1740</v>
+        <v>-1702.8</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -17603,43 +17603,43 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>603.40000000000009</v>
+        <v>599</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1071.2625</v>
+        <v>1062.95</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>1550</v>
+        <v>1538</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>2035.4749999999999</v>
+        <v>2022.8000000000002</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>2528</v>
+        <v>2516</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-559</v>
+        <v>-532.40000000000009</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-867.75</v>
+        <v>-832.8</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-1192</v>
+        <v>-1152</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-1528.75</v>
+        <v>-1487</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-1875</v>
+        <v>-1834.8000000000002</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -17658,43 +17658,43 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>692.4</v>
+        <v>688</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>1229.6375</v>
+        <v>1221.3249999999998</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>1779.9999999999998</v>
+        <v>1768</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>2339.3499999999995</v>
+        <v>2326.6749999999997</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>2908</v>
+        <v>2896</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-596</v>
+        <v>-568.4</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-926.25</v>
+        <v>-889.8</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-1274</v>
+        <v>-1232</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-1636.25</v>
+        <v>-1592</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-2009.9999999999998</v>
+        <v>-1966.7999999999997</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -17713,43 +17713,43 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>781.4</v>
+        <v>777</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>1388.0125</v>
+        <v>1379.7</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>2010</v>
+        <v>1998</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>2643.2249999999999</v>
+        <v>2630.55</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>3288</v>
+        <v>3276</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-633</v>
+        <v>-604.40000000000009</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-984.75</v>
+        <v>-946.8</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-1356</v>
+        <v>-1312</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-1743.75</v>
+        <v>-1697</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-2145</v>
+        <v>-2098.8000000000002</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -17768,43 +17768,43 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>870.4000000000002</v>
+        <v>866.00000000000011</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>1546.3875000000003</v>
+        <v>1538.0750000000003</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>2240</v>
+        <v>2228</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>2947.1000000000004</v>
+        <v>2934.4250000000002</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>3668</v>
+        <v>3656</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-670</v>
+        <v>-640.40000000000009</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-1043.25</v>
+        <v>-1003.8000000000001</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-1438</v>
+        <v>-1392</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-1851.25</v>
+        <v>-1802</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-2280</v>
+        <v>-2230.8000000000002</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -17823,43 +17823,43 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>959.4</v>
+        <v>955</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>1704.7625</v>
+        <v>1696.45</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>2470</v>
+        <v>2458</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>3250.9749999999999</v>
+        <v>3238.3</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>4048</v>
+        <v>4036</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-707</v>
+        <v>-676.4</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-1101.75</v>
+        <v>-1060.8</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-1520</v>
+        <v>-1472</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-1958.75</v>
+        <v>-1907</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-2415</v>
+        <v>-2362.8000000000002</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -17878,43 +17878,43 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1048.4000000000001</v>
+        <v>1044</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>1863.1375000000003</v>
+        <v>1854.8250000000003</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>2700</v>
+        <v>2688</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>3554.85</v>
+        <v>3542.1750000000002</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>4428</v>
+        <v>4416</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-744</v>
+        <v>-712.40000000000009</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-1160.25</v>
+        <v>-1117.8000000000002</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-1602</v>
+        <v>-1552</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-2066.25</v>
+        <v>-2012</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-2550</v>
+        <v>-2494.8000000000002</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -17933,43 +17933,43 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>1137.4000000000001</v>
+        <v>1133</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>2021.5124999999998</v>
+        <v>2013.2</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>2930</v>
+        <v>2918</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>3858.7249999999999</v>
+        <v>3846.0499999999997</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>4807.9999999999991</v>
+        <v>4796</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-781</v>
+        <v>-748.4</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-1218.75</v>
+        <v>-1174.8</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-1684</v>
+        <v>-1632</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-2173.75</v>
+        <v>-2117</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-2685</v>
+        <v>-2626.7999999999997</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -17988,43 +17988,43 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>1226.4000000000001</v>
+        <v>1222</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>2179.8874999999998</v>
+        <v>2171.5749999999998</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>3160</v>
+        <v>3148</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>4162.6000000000004</v>
+        <v>4149.9250000000002</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>5188</v>
+        <v>5176</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-818</v>
+        <v>-784.4</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-1277.25</v>
+        <v>-1231.8</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-1766</v>
+        <v>-1712</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-2281.25</v>
+        <v>-2222</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-2820</v>
+        <v>-2758.7999999999997</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>
@@ -18215,7 +18215,7 @@
       </c>
       <c r="G165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R165)+(INDEX(Parameters!$J$11:$N$11,1,R165+1)-INDEX(Parameters!$J$11:$N$11,1,R165))*U165,INDEX(Parameters!$D$11:$H$11,1,Q165)+(INDEX(Parameters!$D$11:$H$11,1,Q165+1)-INDEX(Parameters!$D$11:$H$11,1,Q165))*T165)</f>
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q165)+(INDEX(Parameters!$J$12:$N$12,1,Q165+1)-INDEX(Parameters!$J$12:$N$12,1,Q165))*T165,INDEX(Parameters!$D$12:$H$12,1,Q165)+(INDEX(Parameters!$D$12:$H$12,1,Q165+1)-INDEX(Parameters!$D$12:$H$12,1,Q165))*T165)</f>
@@ -18243,15 +18243,15 @@
       </c>
       <c r="N165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S165)+(INDEX(Parameters!$J$19:$N$19,1,S165+1)-INDEX(Parameters!$J$19:$N$19,1,S165))*V165,INDEX(Parameters!$D$19:$H$19,1,S165)+(INDEX(Parameters!$D$19:$H$19,1,S165+1)-INDEX(Parameters!$D$19:$H$19,1,S165))*V165)</f>
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="P165">
         <f>M165*O165</f>
-        <v>1640</v>
+        <v>1600</v>
       </c>
       <c r="Q165">
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DCEB5D-1A26-4980-AE5D-B24DCA0DE274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -483,10 +483,22 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -495,20 +507,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6126,20 +6126,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6169,17 +6169,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6210,13 +6210,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6254,16 +6254,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="24">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="27">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>2228</v>
       </c>
-      <c r="J8" s="24"/>
+      <c r="J8" s="27"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -6301,16 +6301,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="24">
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="27">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1392</v>
       </c>
-      <c r="J10" s="24"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -6362,13 +6362,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
         <v>2500</v>
@@ -6415,11 +6415,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
         <v>2100</v>
@@ -6439,11 +6439,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
         <v>2500</v>
@@ -6463,11 +6463,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
         <v>4600</v>
@@ -6509,11 +6509,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -6533,11 +6533,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
         <v>1600</v>
@@ -6574,11 +6574,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -6598,11 +6598,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
@@ -6622,11 +6622,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
         <v>0.28000000000000003</v>
@@ -6676,20 +6676,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -6950,17 +6950,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -6968,6 +6957,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -7028,20 +7028,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7071,17 +7071,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7111,17 +7111,17 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7705,20 +7705,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7792,20 +7792,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7835,17 +7835,17 @@
         <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7875,17 +7875,17 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8469,20 +8469,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8556,20 +8556,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8599,17 +8599,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8632,20 +8632,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9229,20 +9229,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9312,20 +9312,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9355,17 +9355,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9388,20 +9388,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9985,20 +9985,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10072,40 +10072,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10129,21 +10129,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -10775,73 +10775,73 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="20"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="20"/>
+      <c r="C24" s="22"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="20"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10859,25 +10859,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="20"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -10899,154 +10899,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11153,6 +11153,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -11161,17 +11172,6 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DCEB5D-1A26-4980-AE5D-B24DCA0DE274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F438803-EFD2-48DE-BEA3-6E7F30242DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <t>Type-A</t>
   </si>
   <si>
-    <t>Type-B · 独立设计草稿；切换仅作用于本页。</t>
+    <t>Type-A / Type-B · 切换仅作用于本页。</t>
   </si>
   <si>
     <t>固定 HSC</t>
@@ -83,10 +83,10 @@
     <t>Astral · Valving parameters</t>
   </si>
   <si>
-    <t>黄色单元格可编辑；Type-B 是当前 Type-A 的独立副本，用于设计草稿。</t>
+    <t>黄色单元格可编辑；Type-A 与 Type-B 分别标定。</t>
   </si>
   <si>
-    <t>Type-B · Draft</t>
+    <t>Type-B</t>
   </si>
   <si>
     <t>调节位置</t>
@@ -167,7 +167,7 @@
     <t>连续分段接续仍为工作假设；这里计算基础阻尼，不叠加气体、弹簧、HBS/HRS 或 LRS/DSV。</t>
   </si>
   <si>
-    <t>采样 0～1 m/s，间隔 0.05；关闭平滑，采样点以直线连接。</t>
+    <t>LSC 只调斜率；Type-A 的 HSC 调第二 knee，Type-B 的 HSC 调第一 knee。</t>
   </si>
   <si>
     <t>研究来源：chatgpt-conversation://6a9ed043-7848-83e8-9d36-6e63c8202898</t>
@@ -483,22 +483,10 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -507,8 +495,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -682,64 +682,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>178</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>217</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>256</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>295</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>334</c:v>
+                  <c:v>673.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>373</c:v>
+                  <c:v>716.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>412</c:v>
+                  <c:v>759.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>451.00000000000006</c:v>
+                  <c:v>802.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>490</c:v>
+                  <c:v>846</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>654.00000000000011</c:v>
+                  <c:v>914.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>818</c:v>
+                  <c:v>982.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>982</c:v>
+                  <c:v>1050.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1146.0000000000002</c:v>
+                  <c:v>1118.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1310</c:v>
+                  <c:v>1187</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1474</c:v>
+                  <c:v>1255.2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1638</c:v>
+                  <c:v>1323.4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1802</c:v>
+                  <c:v>1391.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,64 +858,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>249.2</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>320.07500000000005</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>390.95000000000005</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>461.82499999999999</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>532.70000000000005</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>603.57500000000005</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>674.45</c:v>
+                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>745.32500000000005</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>816.2</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>887.07499999999993</c:v>
+                  <c:v>1140</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1082.9500000000003</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1278.8249999999998</c:v>
+                  <c:v>1310</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1474.7</c:v>
+                  <c:v>1395</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1670.5750000000003</c:v>
+                  <c:v>1480</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1866.45</c:v>
+                  <c:v>1565</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2062.3250000000003</c:v>
+                  <c:v>1650</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2258.1999999999998</c:v>
+                  <c:v>1735</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2454.0749999999998</c:v>
+                  <c:v>1820</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1034,64 +1034,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1284</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1362</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1308</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1538</c:v>
+                  <c:v>1543</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1768</c:v>
+                  <c:v>1646</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1998</c:v>
+                  <c:v>1749</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2228</c:v>
+                  <c:v>1852</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2458</c:v>
+                  <c:v>1955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2688</c:v>
+                  <c:v>2058</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2918</c:v>
+                  <c:v>2161</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3148</c:v>
+                  <c:v>2264</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1210,64 +1210,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>479.04999999999995</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>620.42499999999995</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>761.8</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>903.17499999999995</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1044.55</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1185.9250000000002</c:v>
+                  <c:v>1357.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1327.3000000000002</c:v>
+                  <c:v>1454.4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1468.675</c:v>
+                  <c:v>1551.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1610.0500000000002</c:v>
+                  <c:v>1648.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1751.425</c:v>
+                  <c:v>1746</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2017.8000000000002</c:v>
+                  <c:v>1868.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2284.1749999999997</c:v>
+                  <c:v>1990.4</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2550.5500000000002</c:v>
+                  <c:v>2112.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2816.9250000000002</c:v>
+                  <c:v>2234.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3083.3</c:v>
+                  <c:v>2357</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3349.6750000000002</c:v>
+                  <c:v>2479.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3616.0499999999997</c:v>
+                  <c:v>2601.4</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3882.4250000000002</c:v>
+                  <c:v>2723.6000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1386,64 +1386,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>595.99999999999989</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>776</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>956</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1136</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1316</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1496</c:v>
+                  <c:v>1587.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1676</c:v>
+                  <c:v>1705.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1856</c:v>
+                  <c:v>1822.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2036</c:v>
+                  <c:v>1940.4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2216</c:v>
+                  <c:v>2058</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2521</c:v>
+                  <c:v>2200.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2826</c:v>
+                  <c:v>2343.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3131</c:v>
+                  <c:v>2485.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3436</c:v>
+                  <c:v>2628.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3741</c:v>
+                  <c:v>2771</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4046</c:v>
+                  <c:v>2913.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4351</c:v>
+                  <c:v>3056.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4656</c:v>
+                  <c:v>3198.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1762,64 +1762,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>825</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>900</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>975</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1050</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1125</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1200</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1275</c:v>
+                  <c:v>1328</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1375</c:v>
+                  <c:v>1483</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1475</c:v>
+                  <c:v>1638</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1575</c:v>
+                  <c:v>1793</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1675</c:v>
+                  <c:v>1948</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1775</c:v>
+                  <c:v>2103</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1875</c:v>
+                  <c:v>2258</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1975</c:v>
+                  <c:v>2413</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2075</c:v>
+                  <c:v>2568</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1938,64 +1938,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>975</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1050</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1125</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1200</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1275</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1350</c:v>
+                  <c:v>1325.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1450</c:v>
+                  <c:v>1518</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1550</c:v>
+                  <c:v>1710.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1650</c:v>
+                  <c:v>1903</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1750</c:v>
+                  <c:v>2095.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1850</c:v>
+                  <c:v>2288</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1950</c:v>
+                  <c:v>2480.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2050</c:v>
+                  <c:v>2673</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2150</c:v>
+                  <c:v>2865.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,64 +2114,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1125</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1200</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1275</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1350</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1425</c:v>
+                  <c:v>1308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1525</c:v>
+                  <c:v>1538</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1625</c:v>
+                  <c:v>1768</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1725</c:v>
+                  <c:v>1998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1825</c:v>
+                  <c:v>2228</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1925</c:v>
+                  <c:v>2458</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2025</c:v>
+                  <c:v>2688</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2125</c:v>
+                  <c:v>2918</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2225</c:v>
+                  <c:v>3148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2290,64 +2290,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1200</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1275</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1350</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1425</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1500</c:v>
+                  <c:v>1308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1600</c:v>
+                  <c:v>1543</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1700</c:v>
+                  <c:v>1810.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1800</c:v>
+                  <c:v>2078</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1900</c:v>
+                  <c:v>2345.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2000</c:v>
+                  <c:v>2613</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2100</c:v>
+                  <c:v>2880.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2200</c:v>
+                  <c:v>3148</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2300</c:v>
+                  <c:v>3415.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,64 +2466,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>363</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>678</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>783</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1200</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1350</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1425</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1500</c:v>
+                  <c:v>1203</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1575</c:v>
+                  <c:v>1308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1675</c:v>
+                  <c:v>1533</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1775</c:v>
+                  <c:v>1837.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1875</c:v>
+                  <c:v>2143</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1975</c:v>
+                  <c:v>2448</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2075</c:v>
+                  <c:v>2753</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2175</c:v>
+                  <c:v>3058</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2275</c:v>
+                  <c:v>3363</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2375</c:v>
+                  <c:v>3668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3915,64 +3915,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>139</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>178</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>217</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>256</c:v>
+                  <c:v>493.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>295</c:v>
+                  <c:v>536.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>334</c:v>
+                  <c:v>579.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>373</c:v>
+                  <c:v>622.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>412</c:v>
+                  <c:v>666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>451.00000000000006</c:v>
+                  <c:v>709.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>510</c:v>
+                  <c:v>752.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>599</c:v>
+                  <c:v>820.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>688</c:v>
+                  <c:v>888.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>777</c:v>
+                  <c:v>957</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>866.00000000000011</c:v>
+                  <c:v>1025.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>955</c:v>
+                  <c:v>1093.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1044</c:v>
+                  <c:v>1161.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1133</c:v>
+                  <c:v>1229.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1222</c:v>
+                  <c:v>1298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4091,64 +4091,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>249.2</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>320.07500000000005</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>390.95000000000005</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>461.82499999999999</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>532.70000000000005</c:v>
+                  <c:v>780</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>603.57500000000005</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>674.45</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>745.32500000000005</c:v>
+                  <c:v>960</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>816.2</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>904.57499999999993</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1062.95</c:v>
+                  <c:v>1165</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1221.3249999999998</c:v>
+                  <c:v>1250</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1379.7</c:v>
+                  <c:v>1335</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1538.0750000000003</c:v>
+                  <c:v>1420</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1696.45</c:v>
+                  <c:v>1505</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1854.8250000000003</c:v>
+                  <c:v>1590</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2013.2</c:v>
+                  <c:v>1675</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2171.5749999999998</c:v>
+                  <c:v>1760</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4267,64 +4267,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1284</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1362</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1308</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1538</c:v>
+                  <c:v>1543</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1768</c:v>
+                  <c:v>1646</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1998</c:v>
+                  <c:v>1749</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2228</c:v>
+                  <c:v>1852</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2458</c:v>
+                  <c:v>1955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2688</c:v>
+                  <c:v>2058</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2918</c:v>
+                  <c:v>2161</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3148</c:v>
+                  <c:v>2264</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4443,64 +4443,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>479.04999999999995</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>620.42499999999995</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>761.8</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>903.17499999999995</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1044.55</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1185.9250000000002</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1327.3000000000002</c:v>
+                  <c:v>1537.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1468.675</c:v>
+                  <c:v>1634.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1610.0500000000002</c:v>
+                  <c:v>1731.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1751.425</c:v>
+                  <c:v>1828.8</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2022.8000000000002</c:v>
+                  <c:v>1951</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2326.6749999999997</c:v>
+                  <c:v>2073.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2630.55</c:v>
+                  <c:v>2195.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2934.4250000000002</c:v>
+                  <c:v>2317.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3238.3</c:v>
+                  <c:v>2439.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3542.1750000000002</c:v>
+                  <c:v>2562</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3846.0499999999997</c:v>
+                  <c:v>2684.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4149.9250000000002</c:v>
+                  <c:v>2806.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4619,64 +4619,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>595.99999999999989</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>776</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>956</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1136</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1316</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1496</c:v>
+                  <c:v>1680</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1676</c:v>
+                  <c:v>1890</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1856</c:v>
+                  <c:v>2007.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2036</c:v>
+                  <c:v>2125.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2216</c:v>
+                  <c:v>2242.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2516</c:v>
+                  <c:v>2385.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2896</c:v>
+                  <c:v>2528</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3276</c:v>
+                  <c:v>2670.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3656</c:v>
+                  <c:v>2813.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4036</c:v>
+                  <c:v>2955.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4416</c:v>
+                  <c:v>3098.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4796</c:v>
+                  <c:v>3241</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5176</c:v>
+                  <c:v>3383.6000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4795,64 +4795,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-100</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-150</c:v>
+                  <c:v>-225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-200</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-244.4</c:v>
+                  <c:v>-337.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-280.39999999999998</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-316.39999999999998</c:v>
+                  <c:v>-412.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-352.4</c:v>
+                  <c:v>-450</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-388.4</c:v>
+                  <c:v>-487.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-424.4</c:v>
+                  <c:v>-525</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-460.40000000000003</c:v>
+                  <c:v>-562.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-496.4</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-532.40000000000009</c:v>
+                  <c:v>-637.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-568.4</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-604.40000000000009</c:v>
+                  <c:v>-712.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-640.40000000000009</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-676.4</c:v>
+                  <c:v>-787.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-712.40000000000009</c:v>
+                  <c:v>-825</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-748.4</c:v>
+                  <c:v>-862.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-784.4</c:v>
+                  <c:v>-900</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4971,64 +4971,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-75</c:v>
+                  <c:v>-100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-150</c:v>
+                  <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-225</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-300</c:v>
+                  <c:v>-400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-375</c:v>
+                  <c:v>-477</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-433.79999999999995</c:v>
+                  <c:v>-531</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-490.79999999999995</c:v>
+                  <c:v>-585</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-547.79999999999995</c:v>
+                  <c:v>-639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-604.79999999999995</c:v>
+                  <c:v>-693</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-661.8</c:v>
+                  <c:v>-747</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-718.80000000000007</c:v>
+                  <c:v>-801</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-775.8</c:v>
+                  <c:v>-855</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-832.8</c:v>
+                  <c:v>-909</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-889.8</c:v>
+                  <c:v>-963</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-946.8</c:v>
+                  <c:v>-1017</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1003.8000000000001</c:v>
+                  <c:v>-1071</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1060.8</c:v>
+                  <c:v>-1125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1117.8000000000002</c:v>
+                  <c:v>-1179</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1174.8</c:v>
+                  <c:v>-1233</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1231.8</c:v>
+                  <c:v>-1287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5147,64 +5147,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-100</c:v>
+                  <c:v>-125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-200</c:v>
+                  <c:v>-250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-300</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-400</c:v>
+                  <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-500</c:v>
+                  <c:v>-625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-591.99999999999989</c:v>
+                  <c:v>-697.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-671.99999999999989</c:v>
+                  <c:v>-770</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-752</c:v>
+                  <c:v>-842.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-832</c:v>
+                  <c:v>-915</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-912</c:v>
+                  <c:v>-987.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-992</c:v>
+                  <c:v>-1060</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1072</c:v>
+                  <c:v>-1132.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1152</c:v>
+                  <c:v>-1205</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1232</c:v>
+                  <c:v>-1277.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1312</c:v>
+                  <c:v>-1350</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1392</c:v>
+                  <c:v>-1422.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1472</c:v>
+                  <c:v>-1495</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1552</c:v>
+                  <c:v>-1567.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1632</c:v>
+                  <c:v>-1640</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1712</c:v>
+                  <c:v>-1712.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5323,64 +5323,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-125</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-250</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-375</c:v>
+                  <c:v>-450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-500</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-625</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-750</c:v>
+                  <c:v>-871.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-857</c:v>
+                  <c:v>-964.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-962</c:v>
+                  <c:v>-1057.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1067</c:v>
+                  <c:v>-1150.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1172</c:v>
+                  <c:v>-1243.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1277</c:v>
+                  <c:v>-1336.5000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1382</c:v>
+                  <c:v>-1429.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1487</c:v>
+                  <c:v>-1522.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1592</c:v>
+                  <c:v>-1615.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1697</c:v>
+                  <c:v>-1708.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1802</c:v>
+                  <c:v>-1801.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1907</c:v>
+                  <c:v>-1894.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2012</c:v>
+                  <c:v>-1987.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2117</c:v>
+                  <c:v>-2080.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2222</c:v>
+                  <c:v>-2173.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5499,64 +5499,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-150</c:v>
+                  <c:v>-175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-300</c:v>
+                  <c:v>-350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-450</c:v>
+                  <c:v>-525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-600</c:v>
+                  <c:v>-700</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-750</c:v>
+                  <c:v>-875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-900</c:v>
+                  <c:v>-1050</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1042.8</c:v>
+                  <c:v>-1165.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1174.8</c:v>
+                  <c:v>-1281</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1306.8</c:v>
+                  <c:v>-1396.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1438.8</c:v>
+                  <c:v>-1512</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1570.8000000000002</c:v>
+                  <c:v>-1627.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1702.8</c:v>
+                  <c:v>-1743</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1834.8000000000002</c:v>
+                  <c:v>-1858.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1966.7999999999997</c:v>
+                  <c:v>-1974</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2098.8000000000002</c:v>
+                  <c:v>-2089.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2230.8000000000002</c:v>
+                  <c:v>-2205</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2362.8000000000002</c:v>
+                  <c:v>-2320.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2494.8000000000002</c:v>
+                  <c:v>-2436</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2626.7999999999997</c:v>
+                  <c:v>-2551.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2758.7999999999997</c:v>
+                  <c:v>-2667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6126,20 +6126,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6169,17 +6169,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6210,13 +6210,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6254,16 +6254,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="27">
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>2228</v>
-      </c>
-      <c r="J8" s="27"/>
+        <v>1308</v>
+      </c>
+      <c r="J8" s="24"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -6297,20 +6297,20 @@
         <v>51</v>
       </c>
       <c r="C10" s="16">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="27">
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="24">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1392</v>
-      </c>
-      <c r="J10" s="27"/>
+        <v>1072</v>
+      </c>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -6362,13 +6362,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
         <v>2500</v>
@@ -6415,11 +6415,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
         <v>2100</v>
@@ -6439,11 +6439,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
         <v>2500</v>
@@ -6463,11 +6463,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
         <v>4600</v>
@@ -6509,11 +6509,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -6533,11 +6533,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
         <v>1600</v>
@@ -6574,11 +6574,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -6598,11 +6598,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
@@ -6622,11 +6622,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
         <v>0.28000000000000003</v>
@@ -6676,20 +6676,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -6950,6 +6950,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -6957,17 +6968,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -7028,20 +7028,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7068,20 +7068,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7111,17 +7111,17 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7705,20 +7705,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7792,20 +7792,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7832,20 +7832,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7875,17 +7875,17 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8469,20 +8469,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8556,20 +8556,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8599,17 +8599,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8632,20 +8632,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9229,20 +9229,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9312,20 +9312,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9352,20 +9352,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9388,20 +9388,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9985,20 +9985,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10072,40 +10072,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10129,21 +10129,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -10365,21 +10365,21 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E11" s="5">
         <f>(D11+F11)/2</f>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F11" s="4">
         <v>0.12</v>
       </c>
       <c r="G11" s="5">
         <f>(F11+H11)/2</f>
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H11" s="4">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="4">
@@ -10410,36 +10410,36 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="E12" s="5">
         <f>(D12+F12)/2</f>
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="F12" s="4">
         <v>0.84</v>
       </c>
       <c r="G12" s="5">
         <f>(F12+H12)/2</f>
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="H12" s="4">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="4">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="K12" s="5">
         <f>(J12+L12)/2</f>
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="L12" s="4">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="M12" s="5">
         <f>(L12+N12)/2</f>
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="N12" s="4">
         <v>0.56000000000000005</v>
@@ -10775,73 +10775,73 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="22"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10859,25 +10859,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="22"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -10899,154 +10899,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11153,17 +11153,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -11172,6 +11161,17 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11351,23 +11351,23 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.78</v>
+        <v>0.48</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>780</v>
+        <v>864</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11375,23 +11375,23 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>3280</v>
+        <v>1364</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11438,23 +11438,23 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.81</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>1417.5</v>
+        <v>1200</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11462,23 +11462,23 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>3917.5</v>
+        <v>1700</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11525,23 +11525,23 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>2100</v>
+        <v>1560</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11549,23 +11549,23 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>4600</v>
+        <v>2060</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -11612,23 +11612,23 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>2827.5</v>
+        <v>1944.0000000000002</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11636,23 +11636,23 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>5327.5</v>
+        <v>2444</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.84000000000000008</v>
+        <v>0.62</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>2100</v>
+        <v>1860</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11699,23 +11699,23 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.14000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.9</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>3600</v>
+        <v>2352</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11723,23 +11723,23 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>6100</v>
+        <v>2852</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>2640</v>
+        <v>2310</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11927,23 +11927,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>162.5</v>
+        <v>180</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -11968,23 +11968,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -12009,23 +12009,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>249.2</v>
+        <v>360</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>363</v>
+        <v>450</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>479.04999999999995</v>
+        <v>540</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>595.99999999999989</v>
+        <v>630</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12050,23 +12050,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>360</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>320.07500000000005</v>
+        <v>480</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>468</v>
+        <v>600</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>620.42499999999995</v>
+        <v>720</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>776</v>
+        <v>840</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -12091,23 +12091,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>217</v>
+        <v>450</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>390.95000000000005</v>
+        <v>600</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>573</v>
+        <v>750</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>761.8</v>
+        <v>900</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>956</v>
+        <v>1050</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -12132,23 +12132,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>540</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>461.82499999999999</v>
+        <v>720</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>678</v>
+        <v>900</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>903.17499999999995</v>
+        <v>1080</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1136</v>
+        <v>1260</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -12173,23 +12173,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>295</v>
+        <v>630</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>532.70000000000005</v>
+        <v>840</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>783</v>
+        <v>1050</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1044.55</v>
+        <v>1260</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1316</v>
+        <v>1470</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -12214,23 +12214,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>334</v>
+        <v>673.2</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>603.57500000000005</v>
+        <v>900</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>888</v>
+        <v>1128</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1185.9250000000002</v>
+        <v>1357.2</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>1496</v>
+        <v>1587.6000000000001</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -12255,23 +12255,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>373</v>
+        <v>716.40000000000009</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>674.45</v>
+        <v>960</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>993</v>
+        <v>1206</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>1327.3000000000002</v>
+        <v>1454.4</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>1676</v>
+        <v>1705.2</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -12296,23 +12296,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>412</v>
+        <v>759.6</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>745.32500000000005</v>
+        <v>1020</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1098</v>
+        <v>1284</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>1468.675</v>
+        <v>1551.6000000000001</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>1856</v>
+        <v>1822.8000000000002</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -12337,23 +12337,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>451.00000000000006</v>
+        <v>802.80000000000007</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>816.2</v>
+        <v>1080</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>1203</v>
+        <v>1362</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>1610.0500000000002</v>
+        <v>1648.8000000000002</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>2036</v>
+        <v>1940.4</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -12378,23 +12378,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>490</v>
+        <v>846</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>887.07499999999993</v>
+        <v>1140</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>1308</v>
+        <v>1440</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>1751.425</v>
+        <v>1746</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>2216</v>
+        <v>2058</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -12419,23 +12419,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>654.00000000000011</v>
+        <v>914.2</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1082.9500000000003</v>
+        <v>1225</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>2017.8000000000002</v>
+        <v>1868.2000000000003</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2521</v>
+        <v>2200.6000000000004</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12460,23 +12460,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>818</v>
+        <v>982.4</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1278.8249999999998</v>
+        <v>1310</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1768</v>
+        <v>1646</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>2284.1749999999997</v>
+        <v>1990.4</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2826</v>
+        <v>2343.1999999999998</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12501,23 +12501,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>982</v>
+        <v>1050.6000000000001</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1474.7</v>
+        <v>1395</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>1998</v>
+        <v>1749</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2550.5500000000002</v>
+        <v>2112.6000000000004</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>3131</v>
+        <v>2485.8000000000002</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12542,23 +12542,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1146.0000000000002</v>
+        <v>1118.8000000000002</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1670.5750000000003</v>
+        <v>1480</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>2228</v>
+        <v>1852</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2816.9250000000002</v>
+        <v>2234.8000000000002</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>3436</v>
+        <v>2628.4</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12583,23 +12583,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1187</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>1866.45</v>
+        <v>1565</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>2458</v>
+        <v>1955</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>3083.3</v>
+        <v>2357</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>3741</v>
+        <v>2771</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12624,23 +12624,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1474</v>
+        <v>1255.2</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>2062.3250000000003</v>
+        <v>1650</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2688</v>
+        <v>2058</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>3349.6750000000002</v>
+        <v>2479.2000000000003</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>4046</v>
+        <v>2913.6000000000004</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12665,23 +12665,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1638</v>
+        <v>1323.4</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>2258.1999999999998</v>
+        <v>1735</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>2918</v>
+        <v>2161</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>3616.0499999999997</v>
+        <v>2601.4</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>4351</v>
+        <v>3056.2</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12706,23 +12706,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1802</v>
+        <v>1391.6</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>2454.0749999999998</v>
+        <v>1820</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>3148</v>
+        <v>2264</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>3882.4250000000002</v>
+        <v>2723.6000000000004</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>4656</v>
+        <v>3198.8</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -13041,47 +13041,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>2000</v>
+        <v>3100</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -13127,47 +13127,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>2000</v>
+        <v>3850</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -13213,23 +13213,23 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13237,23 +13237,23 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>2000</v>
+        <v>4600</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -13299,47 +13299,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>500</v>
+        <v>3250</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>2000</v>
+        <v>5350</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.62</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>1860</v>
+        <v>2100</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -13385,47 +13385,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>2000</v>
+        <v>6100</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>2310</v>
+        <v>2640</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -13607,23 +13607,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -13647,23 +13647,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -13687,23 +13687,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>450</v>
+        <v>363</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -13727,23 +13727,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>468</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -13767,23 +13767,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>750</v>
+        <v>573</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -13807,23 +13807,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>825</v>
+        <v>678</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>678</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>678</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>900</v>
+        <v>678</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>900</v>
+        <v>678</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -13847,23 +13847,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>900</v>
+        <v>783</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>975</v>
+        <v>783</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>1050</v>
+        <v>783</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>1050</v>
+        <v>783</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>1050</v>
+        <v>783</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -13887,23 +13887,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>975</v>
+        <v>888</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>1050</v>
+        <v>888</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>1125</v>
+        <v>888</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>1200</v>
+        <v>888</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>1200</v>
+        <v>888</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -13927,23 +13927,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1050</v>
+        <v>993</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1125</v>
+        <v>993</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1200</v>
+        <v>993</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1275</v>
+        <v>993</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>993</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -13967,23 +13967,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1125</v>
+        <v>1098</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1200</v>
+        <v>1098</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1275</v>
+        <v>1098</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>1350</v>
+        <v>1098</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>1425</v>
+        <v>1098</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -14007,23 +14007,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>1275</v>
+        <v>1203</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>1350</v>
+        <v>1203</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>1425</v>
+        <v>1203</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>1500</v>
+        <v>1203</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -14047,23 +14047,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1275</v>
+        <v>1328</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1350</v>
+        <v>1325.5</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>1425</v>
+        <v>1308</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>1500</v>
+        <v>1308</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>1575</v>
+        <v>1308</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -14087,23 +14087,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1375</v>
+        <v>1483</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1450</v>
+        <v>1518</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1525</v>
+        <v>1538</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1600</v>
+        <v>1543</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1675</v>
+        <v>1533</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14127,23 +14127,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1475</v>
+        <v>1638</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1550</v>
+        <v>1710.5</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1625</v>
+        <v>1768</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1700</v>
+        <v>1810.5</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1775</v>
+        <v>1837.9999999999998</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14167,23 +14167,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1575</v>
+        <v>1793</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1650</v>
+        <v>1903</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>1725</v>
+        <v>1998</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>1800</v>
+        <v>2078</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>1875</v>
+        <v>2143</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14207,23 +14207,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>1675</v>
+        <v>1948</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>1750</v>
+        <v>2095.5</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>1825</v>
+        <v>2228</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>1900</v>
+        <v>2345.5</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>1975</v>
+        <v>2448</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14247,23 +14247,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>1775</v>
+        <v>2103</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>1850</v>
+        <v>2288</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>1925</v>
+        <v>2458</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2000</v>
+        <v>2613</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2075</v>
+        <v>2753</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14287,23 +14287,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>1875</v>
+        <v>2258</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>1950</v>
+        <v>2480.5</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2025</v>
+        <v>2688</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2100</v>
+        <v>2880.5</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>2175</v>
+        <v>3058</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14327,23 +14327,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>1975</v>
+        <v>2413</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2050</v>
+        <v>2673</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>2125</v>
+        <v>2918</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>2200</v>
+        <v>3148</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>2275</v>
+        <v>3363</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14367,23 +14367,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2075</v>
+        <v>2568</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2150</v>
+        <v>2865.5</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>2225</v>
+        <v>3148</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>2300</v>
+        <v>3415.5</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>2375</v>
+        <v>3668</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14698,15 +14698,15 @@
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1780</v>
+        <v>1820</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
@@ -14784,15 +14784,15 @@
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>1417.5</v>
+        <v>1452.5</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>3167.5</v>
+        <v>3202.5</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
@@ -14956,15 +14956,15 @@
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>2827.5</v>
+        <v>2762.5</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>6077.5</v>
+        <v>6012.5</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
@@ -15042,15 +15042,15 @@
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>3600</v>
+        <v>3440</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>7600</v>
+        <v>7440</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
@@ -16347,47 +16347,47 @@
       </c>
       <c r="F125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="H125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
-        <v>0.78</v>
+        <v>0.48</v>
       </c>
       <c r="I125" s="8">
         <f>F125*H125</f>
-        <v>780</v>
+        <v>864</v>
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>1780</v>
+        <v>1364</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -16433,47 +16433,47 @@
       </c>
       <c r="F126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
-        <v>0.81</v>
+        <v>0.5</v>
       </c>
       <c r="I126" s="8">
         <f>F126*H126</f>
-        <v>1417.5</v>
+        <v>1200</v>
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>3167.5</v>
+        <v>1700</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>1140</v>
+        <v>1080</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -16519,23 +16519,23 @@
       </c>
       <c r="F127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="I127" s="8">
         <f>F127*H127</f>
-        <v>2100</v>
+        <v>1560</v>
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -16543,23 +16543,23 @@
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>4600</v>
+        <v>2060</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -16605,47 +16605,47 @@
       </c>
       <c r="F128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="H128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
       <c r="I128" s="8">
         <f>F128*H128</f>
-        <v>2827.5</v>
+        <v>1944.0000000000002</v>
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>3250</v>
+        <v>500</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>6077.5</v>
+        <v>2444</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
-        <v>0.84000000000000008</v>
+        <v>0.62</v>
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>2100</v>
+        <v>1860</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -16691,47 +16691,47 @@
       </c>
       <c r="F129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
-        <v>0.14000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="H129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
-        <v>0.9</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I129" s="8">
         <f>F129*H129</f>
-        <v>3600</v>
+        <v>2352</v>
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>7600</v>
+        <v>2852</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>2640</v>
+        <v>2310</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -16943,43 +16943,43 @@
       </c>
       <c r="C135" s="15">
         <f t="shared" si="15"/>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D135" s="15">
         <f t="shared" si="16"/>
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="E135" s="15">
         <f t="shared" si="17"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F135" s="15">
         <f t="shared" si="18"/>
-        <v>162.5</v>
+        <v>180</v>
       </c>
       <c r="G135" s="15">
         <f t="shared" si="19"/>
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H135" s="15">
         <f t="shared" si="20"/>
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
-        <v>-100</v>
+        <v>-125</v>
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-125</v>
+        <v>-150</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-150</v>
+        <v>-175</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -16998,43 +16998,43 @@
       </c>
       <c r="C136" s="15">
         <f t="shared" si="15"/>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D136" s="15">
         <f t="shared" si="16"/>
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="E136" s="15">
         <f t="shared" si="17"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F136" s="15">
         <f t="shared" si="18"/>
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="G136" s="15">
         <f t="shared" si="19"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H136" s="15">
         <f t="shared" si="20"/>
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-250</v>
+        <v>-300</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-300</v>
+        <v>-350</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -17053,43 +17053,43 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>249.2</v>
+        <v>360</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>363</v>
+        <v>450</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>479.04999999999995</v>
+        <v>540</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>595.99999999999989</v>
+        <v>630</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
-        <v>-150</v>
+        <v>-225</v>
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-225</v>
+        <v>-300</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
-        <v>-300</v>
+        <v>-375</v>
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-375</v>
+        <v>-450</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-450</v>
+        <v>-525</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -17108,43 +17108,43 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>178</v>
+        <v>360</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>320.07500000000005</v>
+        <v>480</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>468</v>
+        <v>600</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>620.42499999999995</v>
+        <v>720</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>776</v>
+        <v>840</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -17163,43 +17163,43 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>217</v>
+        <v>450</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>390.95000000000005</v>
+        <v>600</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>573</v>
+        <v>750</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>761.8</v>
+        <v>900</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>956</v>
+        <v>1050</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-244.4</v>
+        <v>-337.5</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-375</v>
+        <v>-477</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
-        <v>-500</v>
+        <v>-625</v>
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-625</v>
+        <v>-750</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-750</v>
+        <v>-875</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -17218,43 +17218,43 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>256</v>
+        <v>493.2</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>461.82499999999999</v>
+        <v>720</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>678</v>
+        <v>900</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>903.17499999999995</v>
+        <v>1080</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1136</v>
+        <v>1260</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-280.39999999999998</v>
+        <v>-375</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-433.79999999999995</v>
+        <v>-531</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-591.99999999999989</v>
+        <v>-697.5</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-750</v>
+        <v>-871.5</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-900</v>
+        <v>-1050</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -17273,43 +17273,43 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>295</v>
+        <v>536.4</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>532.70000000000005</v>
+        <v>780</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>783</v>
+        <v>1050</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1044.55</v>
+        <v>1260</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>1316</v>
+        <v>1470</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-316.39999999999998</v>
+        <v>-412.5</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-490.79999999999995</v>
+        <v>-585</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-671.99999999999989</v>
+        <v>-770</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-857</v>
+        <v>-964.5</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1042.8</v>
+        <v>-1165.5</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -17328,43 +17328,43 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>334</v>
+        <v>579.6</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>603.57500000000005</v>
+        <v>840</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>888</v>
+        <v>1128</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>1185.9250000000002</v>
+        <v>1440</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>1496</v>
+        <v>1680</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-352.4</v>
+        <v>-450</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-547.79999999999995</v>
+        <v>-639</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-752</v>
+        <v>-842.5</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-962</v>
+        <v>-1057.5</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1174.8</v>
+        <v>-1281</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -17383,43 +17383,43 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>373</v>
+        <v>622.79999999999995</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>674.45</v>
+        <v>900</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>993</v>
+        <v>1206</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>1327.3000000000002</v>
+        <v>1537.2</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>1676</v>
+        <v>1890</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-388.4</v>
+        <v>-487.5</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-604.79999999999995</v>
+        <v>-693</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-832</v>
+        <v>-915</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1067</v>
+        <v>-1150.5</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-1306.8</v>
+        <v>-1396.5</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -17438,43 +17438,43 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>412</v>
+        <v>666</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>745.32500000000005</v>
+        <v>960</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>1098</v>
+        <v>1284</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>1468.675</v>
+        <v>1634.4</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>1856</v>
+        <v>2007.6</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-424.4</v>
+        <v>-525</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-661.8</v>
+        <v>-747</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-912</v>
+        <v>-987.5</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-1172</v>
+        <v>-1243.5</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-1438.8</v>
+        <v>-1512</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -17493,43 +17493,43 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>451.00000000000006</v>
+        <v>709.2</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>816.2</v>
+        <v>1020</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>1203</v>
+        <v>1362</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>1610.0500000000002</v>
+        <v>1731.6000000000001</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>2036</v>
+        <v>2125.2000000000003</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-460.40000000000003</v>
+        <v>-562.5</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-718.80000000000007</v>
+        <v>-801</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-992</v>
+        <v>-1060</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-1277</v>
+        <v>-1336.5000000000002</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-1570.8000000000002</v>
+        <v>-1627.5</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -17548,43 +17548,43 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>510</v>
+        <v>752.4</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>904.57499999999993</v>
+        <v>1080</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>1308</v>
+        <v>1440</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>1751.425</v>
+        <v>1828.8</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>2216</v>
+        <v>2242.7999999999997</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-496.4</v>
+        <v>-600</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-775.8</v>
+        <v>-855</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-1072</v>
+        <v>-1132.5</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-1382</v>
+        <v>-1429.5</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-1702.8</v>
+        <v>-1743</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -17603,43 +17603,43 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>599</v>
+        <v>820.6</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1062.95</v>
+        <v>1165</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>2022.8000000000002</v>
+        <v>1951</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>2516</v>
+        <v>2385.4</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-532.40000000000009</v>
+        <v>-637.5</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-832.8</v>
+        <v>-909</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-1152</v>
+        <v>-1205</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-1487</v>
+        <v>-1522.5</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-1834.8000000000002</v>
+        <v>-1858.5</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -17658,43 +17658,43 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>688</v>
+        <v>888.8</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>1221.3249999999998</v>
+        <v>1250</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>1768</v>
+        <v>1646</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>2326.6749999999997</v>
+        <v>2073.1999999999998</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>2896</v>
+        <v>2528</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-568.4</v>
+        <v>-675</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-889.8</v>
+        <v>-963</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-1232</v>
+        <v>-1277.5</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-1592</v>
+        <v>-1615.5</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-1966.7999999999997</v>
+        <v>-1974</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -17713,43 +17713,43 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>777</v>
+        <v>957</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>1379.7</v>
+        <v>1335</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>1998</v>
+        <v>1749</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>2630.55</v>
+        <v>2195.4</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>3276</v>
+        <v>2670.6</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-604.40000000000009</v>
+        <v>-712.5</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-946.8</v>
+        <v>-1017</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-1312</v>
+        <v>-1350</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-1697</v>
+        <v>-1708.5</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-2098.8000000000002</v>
+        <v>-2089.5</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -17768,43 +17768,43 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>866.00000000000011</v>
+        <v>1025.2</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>1538.0750000000003</v>
+        <v>1420</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>2228</v>
+        <v>1852</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>2934.4250000000002</v>
+        <v>2317.6000000000004</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>3656</v>
+        <v>2813.2</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-640.40000000000009</v>
+        <v>-750</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-1003.8000000000001</v>
+        <v>-1071</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-1392</v>
+        <v>-1422.5</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-1802</v>
+        <v>-1801.5</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-2230.8000000000002</v>
+        <v>-2205</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -17823,43 +17823,43 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>955</v>
+        <v>1093.4000000000001</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>1696.45</v>
+        <v>1505</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>2458</v>
+        <v>1955</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>3238.3</v>
+        <v>2439.8000000000002</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>4036</v>
+        <v>2955.8</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-676.4</v>
+        <v>-787.5</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-1060.8</v>
+        <v>-1125</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-1472</v>
+        <v>-1495</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-1907</v>
+        <v>-1894.5</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-2362.8000000000002</v>
+        <v>-2320.5</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -17878,43 +17878,43 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1044</v>
+        <v>1161.6000000000001</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>1854.8250000000003</v>
+        <v>1590</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>2688</v>
+        <v>2058</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>3542.1750000000002</v>
+        <v>2562</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>4416</v>
+        <v>3098.4</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-712.40000000000009</v>
+        <v>-825</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-1117.8000000000002</v>
+        <v>-1179</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-1552</v>
+        <v>-1567.5</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-2012</v>
+        <v>-1987.5</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-2494.8000000000002</v>
+        <v>-2436</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -17933,43 +17933,43 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>1133</v>
+        <v>1229.8</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>2013.2</v>
+        <v>1675</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>2918</v>
+        <v>2161</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>3846.0499999999997</v>
+        <v>2684.2</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>4796</v>
+        <v>3241</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-748.4</v>
+        <v>-862.5</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-1174.8</v>
+        <v>-1233</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-1632</v>
+        <v>-1640</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-2117</v>
+        <v>-2080.5</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-2626.7999999999997</v>
+        <v>-2551.5</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -17988,43 +17988,43 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>1222</v>
+        <v>1298</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>2171.5749999999998</v>
+        <v>1760</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>3148</v>
+        <v>2264</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>4149.9250000000002</v>
+        <v>2806.4</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>5176</v>
+        <v>3383.6000000000004</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-784.4</v>
+        <v>-900</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-1231.8</v>
+        <v>-1287</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-1712</v>
+        <v>-1712.5</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-2222</v>
+        <v>-2173.5</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-2758.7999999999997</v>
+        <v>-2667</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F438803-EFD2-48DE-BEA3-6E7F30242DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C7AD3-A72E-4DCC-B1BE-08E4B09FC385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="86">
   <si>
     <t>Astral · LSC Sweep</t>
   </si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t>Calculator · 插值参数</t>
-  </si>
-  <si>
-    <t>Type-B</t>
   </si>
   <si>
     <t>第一 knee</t>
@@ -682,64 +679,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>180</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270</c:v>
+                  <c:v>148.80000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>360</c:v>
+                  <c:v>196.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>450</c:v>
+                  <c:v>244.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>540</c:v>
+                  <c:v>292.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>630</c:v>
+                  <c:v>340.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>673.2</c:v>
+                  <c:v>388.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>716.40000000000009</c:v>
+                  <c:v>436.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>759.6</c:v>
+                  <c:v>484.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>802.80000000000007</c:v>
+                  <c:v>532.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>846</c:v>
+                  <c:v>580.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>914.2</c:v>
+                  <c:v>753.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>982.4</c:v>
+                  <c:v>926.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1050.6000000000001</c:v>
+                  <c:v>1099.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1118.8000000000002</c:v>
+                  <c:v>1272.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1187</c:v>
+                  <c:v>1445.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1255.2</c:v>
+                  <c:v>1618.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1323.4</c:v>
+                  <c:v>1791.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1391.6</c:v>
+                  <c:v>1964.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -858,64 +855,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120</c:v>
+                  <c:v>87.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>240</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>258.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>340.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>600</c:v>
+                  <c:v>421.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>720</c:v>
+                  <c:v>502.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>840</c:v>
+                  <c:v>584.32500000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>900</c:v>
+                  <c:v>665.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>960</c:v>
+                  <c:v>747.07500000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1020</c:v>
+                  <c:v>828.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1080</c:v>
+                  <c:v>909.82500000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1140</c:v>
+                  <c:v>991.19999999999993</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1225</c:v>
+                  <c:v>1197.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1310</c:v>
+                  <c:v>1403.9499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1395</c:v>
+                  <c:v>1610.325</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1480</c:v>
+                  <c:v>1816.7000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1565</c:v>
+                  <c:v>2023.075</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1650</c:v>
+                  <c:v>2229.4500000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1735</c:v>
+                  <c:v>2435.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1820</c:v>
+                  <c:v>2642.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1034,64 +1031,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1128</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1206</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1284</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1362</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1440</c:v>
+                  <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1543</c:v>
+                  <c:v>1617.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1646</c:v>
+                  <c:v>1855</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1749</c:v>
+                  <c:v>2092.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1852</c:v>
+                  <c:v>2330</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1955</c:v>
+                  <c:v>2567.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2058</c:v>
+                  <c:v>2805</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2161</c:v>
+                  <c:v>3042.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2264</c:v>
+                  <c:v>3280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1210,64 +1207,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>162.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>474.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>616.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>757.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>898.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1260</c:v>
+                  <c:v>1040.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1357.2</c:v>
+                  <c:v>1181.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1454.4</c:v>
+                  <c:v>1323.075</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1551.6000000000001</c:v>
+                  <c:v>1464.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1648.8000000000002</c:v>
+                  <c:v>1605.825</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1746</c:v>
+                  <c:v>1747.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1868.2000000000003</c:v>
+                  <c:v>2013.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1990.4</c:v>
+                  <c:v>2279.9499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2112.6000000000004</c:v>
+                  <c:v>2546.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2234.8000000000002</c:v>
+                  <c:v>2812.7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2357</c:v>
+                  <c:v>3079.0749999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2479.2000000000003</c:v>
+                  <c:v>3345.4500000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2601.4</c:v>
+                  <c:v>3611.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2723.6000000000004</c:v>
+                  <c:v>3878.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1386,64 +1383,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>210</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>420</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>630</c:v>
+                  <c:v>580.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>840</c:v>
+                  <c:v>748.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1050</c:v>
+                  <c:v>916.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1260</c:v>
+                  <c:v>1084.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1470</c:v>
+                  <c:v>1252.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1587.6000000000001</c:v>
+                  <c:v>1420.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1705.2</c:v>
+                  <c:v>1588.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1822.8000000000002</c:v>
+                  <c:v>1756.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1940.4</c:v>
+                  <c:v>1924.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2058</c:v>
+                  <c:v>2092.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2200.6000000000004</c:v>
+                  <c:v>2385.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2343.1999999999998</c:v>
+                  <c:v>2678.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2485.8000000000002</c:v>
+                  <c:v>2971.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2628.4</c:v>
+                  <c:v>3264.8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2771</c:v>
+                  <c:v>3557.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2913.6000000000004</c:v>
+                  <c:v>3850.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3056.2</c:v>
+                  <c:v>4143.7999999999993</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3198.8</c:v>
+                  <c:v>4436.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1768,58 +1765,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1328</c:v>
+                  <c:v>1400</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1483</c:v>
+                  <c:v>1562.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1638</c:v>
+                  <c:v>1725</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1793</c:v>
+                  <c:v>1887.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1948</c:v>
+                  <c:v>2050</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2103</c:v>
+                  <c:v>2212.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2258</c:v>
+                  <c:v>2375</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2413</c:v>
+                  <c:v>2537.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2568</c:v>
+                  <c:v>2700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1944,58 +1941,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1325.5</c:v>
+                  <c:v>1397.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1518</c:v>
+                  <c:v>1597.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1710.5</c:v>
+                  <c:v>1797.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1903</c:v>
+                  <c:v>1997.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2095.5</c:v>
+                  <c:v>2197.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2288</c:v>
+                  <c:v>2397.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2480.5</c:v>
+                  <c:v>2597.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2673</c:v>
+                  <c:v>2797.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2865.5</c:v>
+                  <c:v>2997.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2120,58 +2117,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1308</c:v>
+                  <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1538</c:v>
+                  <c:v>1617.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1768</c:v>
+                  <c:v>1855</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1998</c:v>
+                  <c:v>2092.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2228</c:v>
+                  <c:v>2330</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2458</c:v>
+                  <c:v>2567.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2688</c:v>
+                  <c:v>2805</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2918</c:v>
+                  <c:v>3042.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3148</c:v>
+                  <c:v>3280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2296,58 +2293,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1308</c:v>
+                  <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1543</c:v>
+                  <c:v>1622.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1810.5</c:v>
+                  <c:v>1897.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2078</c:v>
+                  <c:v>2172.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2345.5</c:v>
+                  <c:v>2447.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2613</c:v>
+                  <c:v>2722.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2880.5</c:v>
+                  <c:v>2997.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3148</c:v>
+                  <c:v>3272.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3415.5</c:v>
+                  <c:v>3547.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2472,58 +2469,58 @@
                   <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>468</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>573</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>678</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>783</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>888</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>993</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1098</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1203</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1308</c:v>
+                  <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1533</c:v>
+                  <c:v>1612.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1837.9999999999998</c:v>
+                  <c:v>1924.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2143</c:v>
+                  <c:v>2237.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2448</c:v>
+                  <c:v>2550</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2753</c:v>
+                  <c:v>2862.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3058</c:v>
+                  <c:v>3175</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3363</c:v>
+                  <c:v>3487.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3668</c:v>
+                  <c:v>3800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2842,64 +2839,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>150</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>200</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>244.4</c:v>
+                  <c:v>349.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>280.39999999999998</c:v>
+                  <c:v>399</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>316.39999999999998</c:v>
+                  <c:v>448.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>352.4</c:v>
+                  <c:v>498</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>388.4</c:v>
+                  <c:v>547.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>424.4</c:v>
+                  <c:v>597</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>460.40000000000003</c:v>
+                  <c:v>646.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>496.4</c:v>
+                  <c:v>696</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>532.40000000000009</c:v>
+                  <c:v>745.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>568.4</c:v>
+                  <c:v>795</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>604.40000000000009</c:v>
+                  <c:v>844.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>640.40000000000009</c:v>
+                  <c:v>894.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>676.4</c:v>
+                  <c:v>943.49999999999989</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>712.40000000000009</c:v>
+                  <c:v>993</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>748.4</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>784.4</c:v>
+                  <c:v>1092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3018,64 +3015,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>150</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>225</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>375</c:v>
+                  <c:v>481</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>433.79999999999995</c:v>
+                  <c:v>543</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>490.79999999999995</c:v>
+                  <c:v>605</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>547.79999999999995</c:v>
+                  <c:v>667</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>604.79999999999995</c:v>
+                  <c:v>729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>661.8</c:v>
+                  <c:v>791</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>718.80000000000007</c:v>
+                  <c:v>853</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>775.8</c:v>
+                  <c:v>915</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>832.8</c:v>
+                  <c:v>977</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>889.8</c:v>
+                  <c:v>1039</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>946.8</c:v>
+                  <c:v>1101</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1003.8000000000001</c:v>
+                  <c:v>1163</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1060.8</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1117.8000000000002</c:v>
+                  <c:v>1287</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1174.8</c:v>
+                  <c:v>1349</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1231.8</c:v>
+                  <c:v>1411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,64 +3191,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>300</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>400</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500</c:v>
+                  <c:v>625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>591.99999999999989</c:v>
+                  <c:v>697.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>671.99999999999989</c:v>
+                  <c:v>770</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>752</c:v>
+                  <c:v>842.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>832</c:v>
+                  <c:v>915</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>912</c:v>
+                  <c:v>987.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>992</c:v>
+                  <c:v>1060</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1072</c:v>
+                  <c:v>1132.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1152</c:v>
+                  <c:v>1205</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1232</c:v>
+                  <c:v>1277.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1312</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1392</c:v>
+                  <c:v>1422.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1472</c:v>
+                  <c:v>1495</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1552</c:v>
+                  <c:v>1567.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1632</c:v>
+                  <c:v>1640</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1712</c:v>
+                  <c:v>1712.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3370,64 +3367,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>500</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>625</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>750</c:v>
+                  <c:v>865.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>857</c:v>
+                  <c:v>946.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>962</c:v>
+                  <c:v>1027.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1067</c:v>
+                  <c:v>1108.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1172</c:v>
+                  <c:v>1189.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1277</c:v>
+                  <c:v>1270.5000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1382</c:v>
+                  <c:v>1351.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1487</c:v>
+                  <c:v>1432.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1592</c:v>
+                  <c:v>1513.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1697</c:v>
+                  <c:v>1594.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1802</c:v>
+                  <c:v>1675.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1907</c:v>
+                  <c:v>1756.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2012</c:v>
+                  <c:v>1837.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2117</c:v>
+                  <c:v>1918.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2222</c:v>
+                  <c:v>1999.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3546,64 +3543,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>700</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1042.8</c:v>
+                  <c:v>1137.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1174.8</c:v>
+                  <c:v>1225</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1306.8</c:v>
+                  <c:v>1312.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1438.8</c:v>
+                  <c:v>1400</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1570.8000000000002</c:v>
+                  <c:v>1487.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1702.8</c:v>
+                  <c:v>1575</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1834.8000000000002</c:v>
+                  <c:v>1662.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1966.7999999999997</c:v>
+                  <c:v>1750</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2098.8000000000002</c:v>
+                  <c:v>1837.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2230.8000000000002</c:v>
+                  <c:v>1925</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2362.8000000000002</c:v>
+                  <c:v>2012.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2494.8000000000002</c:v>
+                  <c:v>2100</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2626.7999999999997</c:v>
+                  <c:v>2187.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2758.7999999999997</c:v>
+                  <c:v>2275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3915,64 +3912,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>180</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270</c:v>
+                  <c:v>148.80000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>360</c:v>
+                  <c:v>196.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>450</c:v>
+                  <c:v>244.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>493.2</c:v>
+                  <c:v>292.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>536.4</c:v>
+                  <c:v>340.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>579.6</c:v>
+                  <c:v>388.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>622.79999999999995</c:v>
+                  <c:v>436.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>666</c:v>
+                  <c:v>484.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>709.2</c:v>
+                  <c:v>532.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>752.4</c:v>
+                  <c:v>600.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>820.6</c:v>
+                  <c:v>698.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>888.8</c:v>
+                  <c:v>796.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>957</c:v>
+                  <c:v>894.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1025.2</c:v>
+                  <c:v>992.80000000000018</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1093.4000000000001</c:v>
+                  <c:v>1090.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1161.6000000000001</c:v>
+                  <c:v>1188.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1229.8</c:v>
+                  <c:v>1286.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1298</c:v>
+                  <c:v>1384.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4091,64 +4088,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120</c:v>
+                  <c:v>87.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>240</c:v>
+                  <c:v>175</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>258.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>340.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>600</c:v>
+                  <c:v>421.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>720</c:v>
+                  <c:v>502.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>780</c:v>
+                  <c:v>584.32500000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>840</c:v>
+                  <c:v>665.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>900</c:v>
+                  <c:v>747.07500000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>960</c:v>
+                  <c:v>828.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1020</c:v>
+                  <c:v>909.82500000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1080</c:v>
+                  <c:v>1008.6999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1165</c:v>
+                  <c:v>1177.575</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1250</c:v>
+                  <c:v>1346.4499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1335</c:v>
+                  <c:v>1515.325</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1420</c:v>
+                  <c:v>1684.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1505</c:v>
+                  <c:v>1853.075</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1590</c:v>
+                  <c:v>2021.9500000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1675</c:v>
+                  <c:v>2190.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1760</c:v>
+                  <c:v>2359.6999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4267,64 +4264,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>592.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>705</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>817.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1128</c:v>
+                  <c:v>930.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1206</c:v>
+                  <c:v>1042.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1284</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1362</c:v>
+                  <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1440</c:v>
+                  <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1543</c:v>
+                  <c:v>1617.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1646</c:v>
+                  <c:v>1855</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1749</c:v>
+                  <c:v>2092.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1852</c:v>
+                  <c:v>2330</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1955</c:v>
+                  <c:v>2567.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2058</c:v>
+                  <c:v>2805</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2161</c:v>
+                  <c:v>3042.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2264</c:v>
+                  <c:v>3280</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4443,64 +4440,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>162.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>474.82499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>616.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>757.57500000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>898.95</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1260</c:v>
+                  <c:v>1040.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1440</c:v>
+                  <c:v>1181.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1537.2</c:v>
+                  <c:v>1323.075</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1634.4</c:v>
+                  <c:v>1464.45</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1731.6000000000001</c:v>
+                  <c:v>1605.825</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1828.8</c:v>
+                  <c:v>1747.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1951</c:v>
+                  <c:v>2018.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2073.1999999999998</c:v>
+                  <c:v>2322.4499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2195.4</c:v>
+                  <c:v>2626.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2317.6000000000004</c:v>
+                  <c:v>2930.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2439.8000000000002</c:v>
+                  <c:v>3234.0749999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2562</c:v>
+                  <c:v>3537.9500000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2684.2</c:v>
+                  <c:v>3841.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2806.4</c:v>
+                  <c:v>4145.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4619,64 +4616,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>210</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>420</c:v>
+                  <c:v>400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>630</c:v>
+                  <c:v>580.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>840</c:v>
+                  <c:v>748.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1050</c:v>
+                  <c:v>916.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1260</c:v>
+                  <c:v>1084.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1470</c:v>
+                  <c:v>1252.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1680</c:v>
+                  <c:v>1420.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1890</c:v>
+                  <c:v>1588.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2007.6</c:v>
+                  <c:v>1756.8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2125.2000000000003</c:v>
+                  <c:v>1924.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2242.7999999999997</c:v>
+                  <c:v>2092.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2385.4</c:v>
+                  <c:v>2380.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2528</c:v>
+                  <c:v>2748.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2670.6</c:v>
+                  <c:v>3116.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2813.2</c:v>
+                  <c:v>3484.8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2955.8</c:v>
+                  <c:v>3852.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3098.4</c:v>
+                  <c:v>4220.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3241</c:v>
+                  <c:v>4588.7999999999993</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3383.6000000000004</c:v>
+                  <c:v>4956.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4795,64 +4792,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-75</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>-100</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>-150</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>-225</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>-300</c:v>
+                  <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-337.5</c:v>
+                  <c:v>-247.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-375</c:v>
+                  <c:v>-291.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-412.5</c:v>
+                  <c:v>-335.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-450</c:v>
+                  <c:v>-379.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-487.5</c:v>
+                  <c:v>-423.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-525</c:v>
+                  <c:v>-467.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-562.5</c:v>
+                  <c:v>-511.60000000000008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-600</c:v>
+                  <c:v>-555.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-637.5</c:v>
+                  <c:v>-599.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-675</c:v>
+                  <c:v>-643.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-712.5</c:v>
+                  <c:v>-687.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-750</c:v>
+                  <c:v>-731.60000000000014</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-787.5</c:v>
+                  <c:v>-775.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-825</c:v>
+                  <c:v>-819.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-862.5</c:v>
+                  <c:v>-863.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-900</c:v>
+                  <c:v>-907.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4971,64 +4968,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-100</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-200</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-225</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>-300</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>-400</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>-477</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-531</c:v>
+                  <c:v>-439.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-585</c:v>
+                  <c:v>-502.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-639</c:v>
+                  <c:v>-565.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-693</c:v>
+                  <c:v>-628.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-747</c:v>
+                  <c:v>-691.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-801</c:v>
+                  <c:v>-754.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-855</c:v>
+                  <c:v>-817.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-909</c:v>
+                  <c:v>-880.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-963</c:v>
+                  <c:v>-943.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1017</c:v>
+                  <c:v>-1006.2000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1071</c:v>
+                  <c:v>-1069.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1125</c:v>
+                  <c:v>-1132.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1179</c:v>
+                  <c:v>-1195.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1233</c:v>
+                  <c:v>-1258.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1287</c:v>
+                  <c:v>-1321.2000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5147,64 +5144,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-125</c:v>
+                  <c:v>-100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-250</c:v>
+                  <c:v>-200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-375</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>-400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-500</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>-625</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>-697.5</c:v>
+                  <c:v>-591.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-770</c:v>
+                  <c:v>-671.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-842.5</c:v>
+                  <c:v>-752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-915</c:v>
+                  <c:v>-832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-987.5</c:v>
+                  <c:v>-912</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1060</c:v>
+                  <c:v>-992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1132.5</c:v>
+                  <c:v>-1072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1205</c:v>
+                  <c:v>-1152</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1277.5</c:v>
+                  <c:v>-1232</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1350</c:v>
+                  <c:v>-1312</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1422.5</c:v>
+                  <c:v>-1392</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1495</c:v>
+                  <c:v>-1472</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1567.5</c:v>
+                  <c:v>-1552</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1640</c:v>
+                  <c:v>-1632</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1712.5</c:v>
+                  <c:v>-1712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5323,64 +5320,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-150</c:v>
+                  <c:v>-125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-300</c:v>
+                  <c:v>-250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-450</c:v>
+                  <c:v>-375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-600</c:v>
+                  <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>-625</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>-750</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>-871.5</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>-964.5</c:v>
+                  <c:v>-848</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1057.5</c:v>
+                  <c:v>-943</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1150.5</c:v>
+                  <c:v>-1038</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1243.5</c:v>
+                  <c:v>-1133</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1336.5000000000002</c:v>
+                  <c:v>-1228</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1429.5</c:v>
+                  <c:v>-1323</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1522.5</c:v>
+                  <c:v>-1418</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1615.5</c:v>
+                  <c:v>-1513</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1708.5</c:v>
+                  <c:v>-1608</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1801.5</c:v>
+                  <c:v>-1703</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1894.5</c:v>
+                  <c:v>-1798</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1987.5</c:v>
+                  <c:v>-1893</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2080.5</c:v>
+                  <c:v>-1988</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2173.5</c:v>
+                  <c:v>-2083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5499,64 +5496,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-175</c:v>
+                  <c:v>-150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-350</c:v>
+                  <c:v>-300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-525</c:v>
+                  <c:v>-450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-700</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-875</c:v>
+                  <c:v>-750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-1050</c:v>
+                  <c:v>-900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1165.5</c:v>
+                  <c:v>-1033.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1281</c:v>
+                  <c:v>-1141.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1396.5</c:v>
+                  <c:v>-1249.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1512</c:v>
+                  <c:v>-1357.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1627.5</c:v>
+                  <c:v>-1465.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1743</c:v>
+                  <c:v>-1573.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1858.5</c:v>
+                  <c:v>-1681.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1974</c:v>
+                  <c:v>-1789.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-2089.5</c:v>
+                  <c:v>-1897.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2205</c:v>
+                  <c:v>-2005.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2320.5</c:v>
+                  <c:v>-2113.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2436</c:v>
+                  <c:v>-2221.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2551.5</c:v>
+                  <c:v>-2329.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2667</c:v>
+                  <c:v>-2437.1999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6261,7 +6258,7 @@
       <c r="H8" s="20"/>
       <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>1308</v>
+        <v>1380</v>
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="1"/>
@@ -6422,7 +6419,7 @@
       <c r="H15" s="20"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>22</v>
@@ -6470,7 +6467,7 @@
       <c r="H17" s="20"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
-        <v>4600</v>
+        <v>4750</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>22</v>
@@ -6575,7 +6572,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
@@ -6599,7 +6596,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
@@ -7068,7 +7065,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="21" t="s">
@@ -7793,7 +7790,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -8596,7 +8593,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="21" t="s">
@@ -9352,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="21" t="s">
@@ -10359,7 +10356,7 @@
     <row r="11" spans="1:15" ht="23" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>23</v>
@@ -10410,39 +10407,39 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="E12" s="5">
         <f>(D12+F12)/2</f>
-        <v>0.83</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="F12" s="4">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="G12" s="5">
         <f>(F12+H12)/2</f>
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H12" s="4">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="4">
-        <v>0.48</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K12" s="5">
         <f>(J12+L12)/2</f>
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="L12" s="4">
         <v>0.52</v>
       </c>
       <c r="M12" s="5">
         <f>(L12+N12)/2</f>
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="N12" s="4">
-        <v>0.56000000000000005</v>
+        <v>0.48</v>
       </c>
       <c r="O12" s="1"/>
     </row>
@@ -10494,7 +10491,7 @@
     <row r="14" spans="1:15" ht="23" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>23</v>
@@ -10703,39 +10700,39 @@
         <v>25</v>
       </c>
       <c r="D19" s="4">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="E19" s="5">
         <f>(D19+F19)/2</f>
-        <v>0.76</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="F19" s="4">
         <v>0.8</v>
       </c>
       <c r="G19" s="5">
         <f>(F19+H19)/2</f>
-        <v>0.84000000000000008</v>
+        <v>0.76</v>
       </c>
       <c r="H19" s="4">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4">
-        <v>0.5</v>
+        <v>0.66</v>
       </c>
       <c r="K19" s="5">
         <f>(J19+L19)/2</f>
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="L19" s="4">
         <v>0.57999999999999996</v>
       </c>
       <c r="M19" s="5">
         <f>(L19+N19)/2</f>
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="N19" s="4">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="O19" s="1"/>
     </row>
@@ -10938,7 +10935,7 @@
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -11014,7 +11011,7 @@
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -11283,7 +11280,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>67</v>
@@ -11295,7 +11292,7 @@
         <v>68</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L4" s="12" t="s">
         <v>69</v>
@@ -11351,23 +11348,23 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>864</v>
+        <v>960</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11375,23 +11372,23 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>1364</v>
+        <v>3460</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>750</v>
+        <v>880</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11438,23 +11435,23 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>2400</v>
+        <v>1750</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.5</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>1200</v>
+        <v>1627.5</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11462,23 +11459,23 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>1700</v>
+        <v>4127.5</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.54</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1080</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11525,23 +11522,23 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.52</v>
+        <v>0.9</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>1560</v>
+        <v>2250</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11549,23 +11546,23 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>2060</v>
+        <v>4750</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -11612,23 +11609,23 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3600</v>
+        <v>3250</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.54</v>
+        <v>0.87</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>1944.0000000000002</v>
+        <v>2827.5</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11636,23 +11633,23 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>2444</v>
+        <v>5327.5</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>1860</v>
+        <v>1900</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11699,23 +11696,23 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.56000000000000005</v>
+        <v>0.84</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>2352</v>
+        <v>3360</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11723,23 +11720,23 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>2852</v>
+        <v>5860</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>2310</v>
+        <v>2160</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11927,23 +11924,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>87.5</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -11968,23 +11965,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -12009,23 +12006,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>148.80000000000001</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>258.82499999999999</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>367.5</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>474.82499999999999</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>630</v>
+        <v>580.79999999999995</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12050,23 +12047,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>196.8</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>340.20000000000005</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>720</v>
+        <v>616.20000000000005</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>840</v>
+        <v>748.80000000000007</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -12091,23 +12088,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>244.8</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>421.57500000000005</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>592.5</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>900</v>
+        <v>757.57500000000005</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>1050</v>
+        <v>916.8</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -12132,23 +12129,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>292.79999999999995</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>502.95</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>705</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>1080</v>
+        <v>898.95</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1260</v>
+        <v>1084.8</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -12173,23 +12170,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>340.79999999999995</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>584.32500000000005</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>817.5</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1260</v>
+        <v>1040.3249999999998</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1470</v>
+        <v>1252.8</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -12214,23 +12211,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>673.2</v>
+        <v>388.8</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>900</v>
+        <v>665.7</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>1128</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1357.2</v>
+        <v>1181.7</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>1587.6000000000001</v>
+        <v>1420.8000000000002</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -12255,23 +12252,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>716.40000000000009</v>
+        <v>436.8</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>747.07500000000005</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1206</v>
+        <v>1042.5</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>1454.4</v>
+        <v>1323.075</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>1705.2</v>
+        <v>1588.8</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -12296,23 +12293,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>759.6</v>
+        <v>484.8</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>828.45</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1284</v>
+        <v>1155</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>1551.6000000000001</v>
+        <v>1464.45</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>1822.8000000000002</v>
+        <v>1756.8</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -12337,23 +12334,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>802.80000000000007</v>
+        <v>532.80000000000007</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>1080</v>
+        <v>909.82500000000005</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>1362</v>
+        <v>1267.5</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>1648.8000000000002</v>
+        <v>1605.825</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>1940.4</v>
+        <v>1924.8000000000002</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -12378,23 +12375,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>846</v>
+        <v>580.79999999999995</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>1140</v>
+        <v>991.19999999999993</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>1440</v>
+        <v>1380</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>1746</v>
+        <v>1747.2</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>2058</v>
+        <v>2092.8000000000002</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -12419,23 +12416,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>914.2</v>
+        <v>753.80000000000007</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1225</v>
+        <v>1197.5750000000003</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1543</v>
+        <v>1617.5</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>1868.2000000000003</v>
+        <v>2013.5750000000003</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2200.6000000000004</v>
+        <v>2385.8000000000002</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12460,23 +12457,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>982.4</v>
+        <v>926.8</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1310</v>
+        <v>1403.9499999999998</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1646</v>
+        <v>1855</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>1990.4</v>
+        <v>2279.9499999999998</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2343.1999999999998</v>
+        <v>2678.8</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12501,23 +12498,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>1050.6000000000001</v>
+        <v>1099.8</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1395</v>
+        <v>1610.325</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>1749</v>
+        <v>2092.5</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2112.6000000000004</v>
+        <v>2546.3249999999998</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>2485.8000000000002</v>
+        <v>2971.8</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12542,23 +12539,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1118.8000000000002</v>
+        <v>1272.8000000000002</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1480</v>
+        <v>1816.7000000000003</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>1852</v>
+        <v>2330</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2234.8000000000002</v>
+        <v>2812.7</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>2628.4</v>
+        <v>3264.8</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12583,23 +12580,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1187</v>
+        <v>1445.8</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>1565</v>
+        <v>2023.075</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>1955</v>
+        <v>2567.5</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>2357</v>
+        <v>3079.0749999999998</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>2771</v>
+        <v>3557.7999999999997</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12624,23 +12621,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1255.2</v>
+        <v>1618.8000000000002</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>1650</v>
+        <v>2229.4500000000003</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2058</v>
+        <v>2805</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>2479.2000000000003</v>
+        <v>3345.4500000000003</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>2913.6000000000004</v>
+        <v>3850.8</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12665,23 +12662,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1323.4</v>
+        <v>1791.8</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>1735</v>
+        <v>2435.8249999999998</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>2161</v>
+        <v>3042.5</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>2601.4</v>
+        <v>3611.8249999999998</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>3056.2</v>
+        <v>4143.7999999999993</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12706,23 +12703,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1391.6</v>
+        <v>1964.8</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>1820</v>
+        <v>2642.2</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>2264</v>
+        <v>3280</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>2723.6000000000004</v>
+        <v>3878.2</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>3198.8</v>
+        <v>4436.8</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -12974,7 +12971,7 @@
         <v>21</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H44" s="13" t="s">
         <v>67</v>
@@ -12986,7 +12983,7 @@
         <v>68</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L44" s="13" t="s">
         <v>69</v>
@@ -13049,11 +13046,11 @@
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
@@ -13065,7 +13062,7 @@
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>3100</v>
+        <v>3250</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
@@ -13077,11 +13074,11 @@
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -13135,11 +13132,11 @@
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
@@ -13151,7 +13148,7 @@
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>3850</v>
+        <v>4000</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
@@ -13163,11 +13160,11 @@
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.76</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>1140</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -13221,11 +13218,11 @@
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
@@ -13237,7 +13234,7 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>4600</v>
+        <v>4750</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
@@ -13307,11 +13304,11 @@
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
@@ -13323,7 +13320,7 @@
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>5350</v>
+        <v>5500</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
@@ -13335,11 +13332,11 @@
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.84000000000000008</v>
+        <v>0.76</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>2100</v>
+        <v>1900</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -13393,11 +13390,11 @@
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
@@ -13409,7 +13406,7 @@
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>6100</v>
+        <v>6250</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
@@ -13421,11 +13418,11 @@
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>2640</v>
+        <v>2160</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -13687,23 +13684,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>363</v>
+        <v>367.5</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -13727,23 +13724,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -13767,23 +13764,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>573</v>
+        <v>592.5</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>573</v>
+        <v>592.5</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>573</v>
+        <v>592.5</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>573</v>
+        <v>592.5</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>573</v>
+        <v>592.5</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -13807,23 +13804,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -13847,23 +13844,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>783</v>
+        <v>817.5</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>783</v>
+        <v>817.5</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>783</v>
+        <v>817.5</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>783</v>
+        <v>817.5</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>783</v>
+        <v>817.5</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -13887,23 +13884,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>888</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>888</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>888</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>888</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>888</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -13927,23 +13924,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>993</v>
+        <v>1042.5</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>993</v>
+        <v>1042.5</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>993</v>
+        <v>1042.5</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>993</v>
+        <v>1042.5</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>993</v>
+        <v>1042.5</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -13967,23 +13964,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1098</v>
+        <v>1155</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1098</v>
+        <v>1155</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1098</v>
+        <v>1155</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>1098</v>
+        <v>1155</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>1098</v>
+        <v>1155</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -14007,23 +14004,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1203</v>
+        <v>1267.5</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>1203</v>
+        <v>1267.5</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>1203</v>
+        <v>1267.5</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>1203</v>
+        <v>1267.5</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>1203</v>
+        <v>1267.5</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -14047,23 +14044,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1328</v>
+        <v>1400</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1325.5</v>
+        <v>1397.5</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>1308</v>
+        <v>1380</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>1308</v>
+        <v>1380</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>1308</v>
+        <v>1380</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -14087,23 +14084,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1483</v>
+        <v>1562.5</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1518</v>
+        <v>1597.5</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1538</v>
+        <v>1617.5</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1543</v>
+        <v>1622.5</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1533</v>
+        <v>1612.5</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14127,23 +14124,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1638</v>
+        <v>1725</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1710.5</v>
+        <v>1797.5</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1768</v>
+        <v>1855</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1810.5</v>
+        <v>1897.5</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1837.9999999999998</v>
+        <v>1924.9999999999998</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14167,23 +14164,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1793</v>
+        <v>1887.5</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1903</v>
+        <v>1997.5</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>1998</v>
+        <v>2092.5</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>2078</v>
+        <v>2172.5</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>2143</v>
+        <v>2237.5</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14207,23 +14204,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>1948</v>
+        <v>2050</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>2095.5</v>
+        <v>2197.5</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>2228</v>
+        <v>2330</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>2345.5</v>
+        <v>2447.5</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>2448</v>
+        <v>2550</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14247,23 +14244,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>2103</v>
+        <v>2212.5</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>2288</v>
+        <v>2397.5</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>2458</v>
+        <v>2567.5</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2613</v>
+        <v>2722.5</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2753</v>
+        <v>2862.5</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14287,23 +14284,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>2258</v>
+        <v>2375</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>2480.5</v>
+        <v>2597.5</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2688</v>
+        <v>2805</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2880.5</v>
+        <v>2997.5</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>3058</v>
+        <v>3175</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14327,23 +14324,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>2413</v>
+        <v>2537.5</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2673</v>
+        <v>2797.5</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>2918</v>
+        <v>3042.5</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>3148</v>
+        <v>3272.5</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>3363</v>
+        <v>3487.5</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14367,23 +14364,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2568</v>
+        <v>2700</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2865.5</v>
+        <v>2997.5</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>3148</v>
+        <v>3280</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>3415.5</v>
+        <v>3547.5</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>3668</v>
+        <v>3800</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14627,7 +14624,7 @@
         <v>21</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H84" s="13" t="s">
         <v>67</v>
@@ -14639,7 +14636,7 @@
         <v>68</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L84" s="13" t="s">
         <v>69</v>
@@ -14694,47 +14691,47 @@
       </c>
       <c r="F85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.82</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>820</v>
+        <v>1008.0000000000001</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1820</v>
+        <v>1508</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>720</v>
+        <v>990</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -14780,47 +14777,47 @@
       </c>
       <c r="F86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.83</v>
+        <v>0.54</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>1452.5</v>
+        <v>1296</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>1750</v>
+        <v>500</v>
       </c>
       <c r="K86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>3202.5</v>
+        <v>1796</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>1140</v>
+        <v>1240</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -14866,23 +14863,23 @@
       </c>
       <c r="F87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.84</v>
+        <v>0.52</v>
       </c>
       <c r="I87" s="8">
         <f>F87*H87</f>
-        <v>2100</v>
+        <v>1560</v>
       </c>
       <c r="J87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -14890,23 +14887,23 @@
       </c>
       <c r="L87" s="8">
         <f>I87+J87</f>
-        <v>4600</v>
+        <v>2060</v>
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -14952,47 +14949,47 @@
       </c>
       <c r="F88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>2762.5</v>
+        <v>1800</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>3250</v>
+        <v>500</v>
       </c>
       <c r="K88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>6012.5</v>
+        <v>2300</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.84000000000000008</v>
+        <v>0.54</v>
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>2100</v>
+        <v>1620</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -15038,47 +15035,47 @@
       </c>
       <c r="F89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.86</v>
+        <v>0.48</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>3440</v>
+        <v>2016</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="K89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>7440</v>
+        <v>2516</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>2640</v>
+        <v>1750</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -15260,23 +15257,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -15300,23 +15297,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -15340,23 +15337,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -15380,23 +15377,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -15420,23 +15417,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>244.4</v>
+        <v>349.5</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>375</v>
+        <v>481</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>750</v>
+        <v>875</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -15460,23 +15457,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>280.39999999999998</v>
+        <v>399</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>433.79999999999995</v>
+        <v>543</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>591.99999999999989</v>
+        <v>697.5</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>750</v>
+        <v>865.5</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -15500,23 +15497,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>316.39999999999998</v>
+        <v>448.5</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>490.79999999999995</v>
+        <v>605</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>671.99999999999989</v>
+        <v>770</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>857</v>
+        <v>946.5</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1042.8</v>
+        <v>1137.5</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -15540,23 +15537,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>352.4</v>
+        <v>498</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>547.79999999999995</v>
+        <v>667</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>752</v>
+        <v>842.5</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>962</v>
+        <v>1027.5</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>1174.8</v>
+        <v>1225</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -15580,23 +15577,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>388.4</v>
+        <v>547.5</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>604.79999999999995</v>
+        <v>729</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>832</v>
+        <v>915</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1067</v>
+        <v>1108.5</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>1306.8</v>
+        <v>1312.5</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -15620,23 +15617,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>424.4</v>
+        <v>597</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>661.8</v>
+        <v>791</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>912</v>
+        <v>987.5</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>1172</v>
+        <v>1189.5</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>1438.8</v>
+        <v>1400</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -15660,23 +15657,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>460.40000000000003</v>
+        <v>646.5</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>718.80000000000007</v>
+        <v>853</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>992</v>
+        <v>1060</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>1277</v>
+        <v>1270.5000000000002</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>1570.8000000000002</v>
+        <v>1487.5</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -15700,23 +15697,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>496.4</v>
+        <v>696</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>775.8</v>
+        <v>915</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>1072</v>
+        <v>1132.5</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>1382</v>
+        <v>1351.5</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>1702.8</v>
+        <v>1575</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -15740,23 +15737,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>532.40000000000009</v>
+        <v>745.5</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>832.8</v>
+        <v>977</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>1152</v>
+        <v>1205</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>1487</v>
+        <v>1432.5</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>1834.8000000000002</v>
+        <v>1662.5</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -15780,23 +15777,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>568.4</v>
+        <v>795</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>889.8</v>
+        <v>1039</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>1232</v>
+        <v>1277.5</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>1592</v>
+        <v>1513.5</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>1966.7999999999997</v>
+        <v>1750</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -15820,23 +15817,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>604.40000000000009</v>
+        <v>844.5</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>946.8</v>
+        <v>1101</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>1312</v>
+        <v>1350</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>1697</v>
+        <v>1594.5</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>2098.8000000000002</v>
+        <v>1837.5</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -15860,23 +15857,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>640.40000000000009</v>
+        <v>894.00000000000011</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>1003.8000000000001</v>
+        <v>1163</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>1392</v>
+        <v>1422.5</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>1802</v>
+        <v>1675.5</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>2230.8000000000002</v>
+        <v>1925</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -15900,23 +15897,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>676.4</v>
+        <v>943.49999999999989</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>1060.8</v>
+        <v>1225</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>1472</v>
+        <v>1495</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>1907</v>
+        <v>1756.5</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>2362.8000000000002</v>
+        <v>2012.5</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -15940,23 +15937,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>712.40000000000009</v>
+        <v>993</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>1117.8000000000002</v>
+        <v>1287</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>1552</v>
+        <v>1567.5</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>2012</v>
+        <v>1837.5</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>2494.8000000000002</v>
+        <v>2100</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -15980,23 +15977,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>748.4</v>
+        <v>1042.5</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>1174.8</v>
+        <v>1349</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>2117</v>
+        <v>1918.5</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>2626.7999999999997</v>
+        <v>2187.5</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -16020,23 +16017,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>784.4</v>
+        <v>1092</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>1231.8</v>
+        <v>1411</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1712.5</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>2222</v>
+        <v>1999.5</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>2758.7999999999997</v>
+        <v>2275</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -16280,7 +16277,7 @@
         <v>21</v>
       </c>
       <c r="G124" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H124" s="13" t="s">
         <v>67</v>
@@ -16292,7 +16289,7 @@
         <v>68</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L124" s="13" t="s">
         <v>69</v>
@@ -16347,47 +16344,47 @@
       </c>
       <c r="F125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="I125" s="8">
         <f>F125*H125</f>
-        <v>864</v>
+        <v>960</v>
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>1364</v>
+        <v>1960</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>750</v>
+        <v>880</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -16433,47 +16430,47 @@
       </c>
       <c r="F126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>2400</v>
+        <v>1750</v>
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
-        <v>0.5</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="I126" s="8">
         <f>F126*H126</f>
-        <v>1200</v>
+        <v>1627.5</v>
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>1700</v>
+        <v>3377.5</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
-        <v>0.54</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>1080</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -16519,23 +16516,23 @@
       </c>
       <c r="F127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
-        <v>0.52</v>
+        <v>0.9</v>
       </c>
       <c r="I127" s="8">
         <f>F127*H127</f>
-        <v>1560</v>
+        <v>2250</v>
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="K127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -16543,23 +16540,23 @@
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>2060</v>
+        <v>4750</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P127" s="8">
         <f>M127*O127</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q127" s="8">
         <f>MIN(4,MAX(1,INT((1+C127/Parameters!$D$23)*4)+1))</f>
@@ -16605,47 +16602,47 @@
       </c>
       <c r="F128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>3600</v>
+        <v>3250</v>
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
-        <v>0.54</v>
+        <v>0.87</v>
       </c>
       <c r="I128" s="8">
         <f>F128*H128</f>
-        <v>1944.0000000000002</v>
+        <v>2827.5</v>
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>500</v>
+        <v>3250</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>2444</v>
+        <v>6077.5</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>1860</v>
+        <v>1900</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -16691,47 +16688,47 @@
       </c>
       <c r="F129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
-        <v>0.56000000000000005</v>
+        <v>0.84</v>
       </c>
       <c r="I129" s="8">
         <f>F129*H129</f>
-        <v>2352</v>
+        <v>3360</v>
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>500</v>
+        <v>4000</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>2852</v>
+        <v>7360</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>2310</v>
+        <v>2160</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -16943,43 +16940,43 @@
       </c>
       <c r="C135" s="15">
         <f t="shared" si="15"/>
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D135" s="15">
         <f t="shared" si="16"/>
-        <v>120</v>
+        <v>87.5</v>
       </c>
       <c r="E135" s="15">
         <f t="shared" si="17"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F135" s="15">
         <f t="shared" si="18"/>
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="G135" s="15">
         <f t="shared" si="19"/>
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H135" s="15">
         <f t="shared" si="20"/>
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
-        <v>-125</v>
+        <v>-100</v>
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-150</v>
+        <v>-125</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-175</v>
+        <v>-150</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -16998,43 +16995,43 @@
       </c>
       <c r="C136" s="15">
         <f t="shared" si="15"/>
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="D136" s="15">
         <f t="shared" si="16"/>
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="E136" s="15">
         <f t="shared" si="17"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F136" s="15">
         <f t="shared" si="18"/>
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="G136" s="15">
         <f t="shared" si="19"/>
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H136" s="15">
         <f t="shared" si="20"/>
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
-        <v>-250</v>
+        <v>-200</v>
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-300</v>
+        <v>-250</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-350</v>
+        <v>-300</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -17053,43 +17050,43 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>270</v>
+        <v>148.80000000000001</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>360</v>
+        <v>258.82499999999999</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>450</v>
+        <v>367.5</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>540</v>
+        <v>474.82499999999999</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>630</v>
+        <v>580.79999999999995</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
-        <v>-225</v>
+        <v>-150</v>
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-300</v>
+        <v>-225</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
-        <v>-375</v>
+        <v>-300</v>
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-450</v>
+        <v>-375</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-525</v>
+        <v>-450</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -17108,43 +17105,43 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>360</v>
+        <v>196.8</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>480</v>
+        <v>340.20000000000005</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>720</v>
+        <v>616.20000000000005</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>840</v>
+        <v>748.80000000000007</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -17163,43 +17160,43 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>450</v>
+        <v>244.8</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>600</v>
+        <v>421.57500000000005</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>750</v>
+        <v>592.5</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>900</v>
+        <v>757.57500000000005</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>1050</v>
+        <v>916.8</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-337.5</v>
+        <v>-247.6</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-477</v>
+        <v>-375</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
-        <v>-625</v>
+        <v>-500</v>
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-750</v>
+        <v>-625</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-875</v>
+        <v>-750</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -17218,43 +17215,43 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>493.2</v>
+        <v>292.79999999999995</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>720</v>
+        <v>502.95</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>900</v>
+        <v>705</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>1080</v>
+        <v>898.95</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1260</v>
+        <v>1084.8</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-375</v>
+        <v>-291.59999999999997</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-531</v>
+        <v>-439.2</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
-        <v>-697.5</v>
+        <v>-591.99999999999989</v>
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-871.5</v>
+        <v>-750</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-1050</v>
+        <v>-900</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -17273,43 +17270,43 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>536.4</v>
+        <v>340.79999999999995</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>780</v>
+        <v>584.32500000000005</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>1050</v>
+        <v>817.5</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1260</v>
+        <v>1040.3249999999998</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>1470</v>
+        <v>1252.8</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-412.5</v>
+        <v>-335.59999999999997</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-585</v>
+        <v>-502.2</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
-        <v>-770</v>
+        <v>-671.99999999999989</v>
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-964.5</v>
+        <v>-848</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1165.5</v>
+        <v>-1033.1999999999998</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -17328,43 +17325,43 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>579.6</v>
+        <v>388.8</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>840</v>
+        <v>665.7</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>1128</v>
+        <v>930.00000000000011</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>1440</v>
+        <v>1181.7</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>1680</v>
+        <v>1420.8000000000002</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-450</v>
+        <v>-379.6</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-639</v>
+        <v>-565.20000000000005</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
-        <v>-842.5</v>
+        <v>-752</v>
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-1057.5</v>
+        <v>-943</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1281</v>
+        <v>-1141.2</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -17383,43 +17380,43 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>622.79999999999995</v>
+        <v>436.8</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>900</v>
+        <v>747.07500000000005</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>1206</v>
+        <v>1042.5</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>1537.2</v>
+        <v>1323.075</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>1890</v>
+        <v>1588.8</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-487.5</v>
+        <v>-423.6</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-693</v>
+        <v>-628.20000000000005</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
-        <v>-915</v>
+        <v>-832</v>
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1150.5</v>
+        <v>-1038</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-1396.5</v>
+        <v>-1249.2</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -17438,43 +17435,43 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>666</v>
+        <v>484.8</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>960</v>
+        <v>828.45</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>1284</v>
+        <v>1155</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>1634.4</v>
+        <v>1464.45</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>2007.6</v>
+        <v>1756.8</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-525</v>
+        <v>-467.6</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-747</v>
+        <v>-691.2</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
-        <v>-987.5</v>
+        <v>-912</v>
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-1243.5</v>
+        <v>-1133</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-1512</v>
+        <v>-1357.2</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -17493,43 +17490,43 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>709.2</v>
+        <v>532.80000000000007</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>1020</v>
+        <v>909.82500000000005</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>1362</v>
+        <v>1267.5</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>1731.6000000000001</v>
+        <v>1605.825</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>2125.2000000000003</v>
+        <v>1924.8000000000002</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-562.5</v>
+        <v>-511.60000000000008</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-801</v>
+        <v>-754.2</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
-        <v>-1060</v>
+        <v>-992</v>
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-1336.5000000000002</v>
+        <v>-1228</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-1627.5</v>
+        <v>-1465.2</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -17548,43 +17545,43 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>752.4</v>
+        <v>600.79999999999995</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>1080</v>
+        <v>1008.6999999999999</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>1440</v>
+        <v>1380</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>1828.8</v>
+        <v>1747.2</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>2242.7999999999997</v>
+        <v>2092.8000000000002</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-600</v>
+        <v>-555.6</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-855</v>
+        <v>-817.2</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
-        <v>-1132.5</v>
+        <v>-1072</v>
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-1429.5</v>
+        <v>-1323</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-1743</v>
+        <v>-1573.1999999999998</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -17603,43 +17600,43 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>820.6</v>
+        <v>698.8</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1165</v>
+        <v>1177.575</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>1543</v>
+        <v>1617.5</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>1951</v>
+        <v>2018.5750000000003</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>2385.4</v>
+        <v>2380.8000000000002</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-637.5</v>
+        <v>-599.6</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-909</v>
+        <v>-880.2</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
-        <v>-1205</v>
+        <v>-1152</v>
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-1522.5</v>
+        <v>-1418</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-1858.5</v>
+        <v>-1681.2</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -17658,43 +17655,43 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>888.8</v>
+        <v>796.8</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>1250</v>
+        <v>1346.4499999999998</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>1646</v>
+        <v>1855</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>2073.1999999999998</v>
+        <v>2322.4499999999998</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>2528</v>
+        <v>2748.8</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-675</v>
+        <v>-643.59999999999991</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-963</v>
+        <v>-943.2</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
-        <v>-1277.5</v>
+        <v>-1232</v>
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-1615.5</v>
+        <v>-1513</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-1974</v>
+        <v>-1789.1999999999998</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -17713,43 +17710,43 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>957</v>
+        <v>894.8</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>1335</v>
+        <v>1515.325</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>1749</v>
+        <v>2092.5</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>2195.4</v>
+        <v>2626.3249999999998</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>2670.6</v>
+        <v>3116.8</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-712.5</v>
+        <v>-687.6</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-1017</v>
+        <v>-1006.2000000000002</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
-        <v>-1350</v>
+        <v>-1312</v>
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-1708.5</v>
+        <v>-1608</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-2089.5</v>
+        <v>-1897.1999999999998</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -17768,43 +17765,43 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>1025.2</v>
+        <v>992.80000000000018</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>1420</v>
+        <v>1684.2000000000003</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>1852</v>
+        <v>2330</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>2317.6000000000004</v>
+        <v>2930.2</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>2813.2</v>
+        <v>3484.8</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-750</v>
+        <v>-731.60000000000014</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-1071</v>
+        <v>-1069.2000000000003</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
-        <v>-1422.5</v>
+        <v>-1392</v>
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-1801.5</v>
+        <v>-1703</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-2205</v>
+        <v>-2005.2</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -17823,43 +17820,43 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>1093.4000000000001</v>
+        <v>1090.8</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>1505</v>
+        <v>1853.075</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>1955</v>
+        <v>2567.5</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>2439.8000000000002</v>
+        <v>3234.0749999999998</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>2955.8</v>
+        <v>3852.7999999999997</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-787.5</v>
+        <v>-775.6</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-1125</v>
+        <v>-1132.2</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
-        <v>-1495</v>
+        <v>-1472</v>
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-1894.5</v>
+        <v>-1798</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-2320.5</v>
+        <v>-2113.1999999999998</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -17878,43 +17875,43 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1161.6000000000001</v>
+        <v>1188.8000000000002</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>1590</v>
+        <v>2021.9500000000003</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>2058</v>
+        <v>2805</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>2562</v>
+        <v>3537.9500000000003</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>3098.4</v>
+        <v>4220.8</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-825</v>
+        <v>-819.6</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-1179</v>
+        <v>-1195.2000000000003</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
-        <v>-1567.5</v>
+        <v>-1552</v>
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-1987.5</v>
+        <v>-1893</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-2436</v>
+        <v>-2221.1999999999998</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -17933,43 +17930,43 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>1229.8</v>
+        <v>1286.8</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>1675</v>
+        <v>2190.8249999999998</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>2161</v>
+        <v>3042.5</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>2684.2</v>
+        <v>3841.8249999999998</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>3241</v>
+        <v>4588.7999999999993</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-862.5</v>
+        <v>-863.6</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-1233</v>
+        <v>-1258.2</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
-        <v>-1640</v>
+        <v>-1632</v>
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-2080.5</v>
+        <v>-1988</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-2551.5</v>
+        <v>-2329.1999999999998</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -17988,43 +17985,43 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>1298</v>
+        <v>1384.8</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>1760</v>
+        <v>2359.6999999999998</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>2264</v>
+        <v>3280</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>2806.4</v>
+        <v>4145.7</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>3383.6000000000004</v>
+        <v>4956.8</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-900</v>
+        <v>-907.6</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-1287</v>
+        <v>-1321.2000000000003</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
-        <v>-1712.5</v>
+        <v>-1712</v>
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-2173.5</v>
+        <v>-2083</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-2667</v>
+        <v>-2437.1999999999998</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>
@@ -18148,7 +18145,7 @@
         <v>21</v>
       </c>
       <c r="G164" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H164" t="s">
         <v>67</v>
@@ -18160,7 +18157,7 @@
         <v>68</v>
       </c>
       <c r="K164" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L164" t="s">
         <v>69</v>
@@ -18219,11 +18216,11 @@
       </c>
       <c r="H165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q165)+(INDEX(Parameters!$J$12:$N$12,1,Q165+1)-INDEX(Parameters!$J$12:$N$12,1,Q165))*T165,INDEX(Parameters!$D$12:$H$12,1,Q165)+(INDEX(Parameters!$D$12:$H$12,1,Q165+1)-INDEX(Parameters!$D$12:$H$12,1,Q165))*T165)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I165">
         <f>F165*H165</f>
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="J165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
@@ -18235,7 +18232,7 @@
       </c>
       <c r="L165">
         <f>I165+J165</f>
-        <v>4600</v>
+        <v>4750</v>
       </c>
       <c r="M165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>

--- a/docs/damping_curve.xlsx
+++ b/docs/damping_curve.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C7AD3-A72E-4DCC-B1BE-08E4B09FC385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052424E7-9232-490B-BD6E-DAC815AA6112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -480,10 +480,22 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -492,20 +504,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -679,64 +679,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>148.80000000000001</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.8</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>244.8</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>292.79999999999995</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>340.79999999999995</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>388.8</c:v>
+                  <c:v>680.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>436.8</c:v>
+                  <c:v>730.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>484.8</c:v>
+                  <c:v>781.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>532.80000000000007</c:v>
+                  <c:v>831.60000000000014</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>580.79999999999995</c:v>
+                  <c:v>882</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>753.80000000000007</c:v>
+                  <c:v>957.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>926.8</c:v>
+                  <c:v>1032.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1099.8</c:v>
+                  <c:v>1108.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1272.8000000000002</c:v>
+                  <c:v>1183.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1445.8</c:v>
+                  <c:v>1259</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1618.8000000000002</c:v>
+                  <c:v>1334.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1791.8</c:v>
+                  <c:v>1409.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1964.8</c:v>
+                  <c:v>1485.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -855,64 +855,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>258.82499999999999</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>340.20000000000005</c:v>
+                  <c:v>480</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>421.57500000000005</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>502.95</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>584.32500000000005</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>665.7</c:v>
+                  <c:v>904.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>747.07500000000005</c:v>
+                  <c:v>969.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>828.45</c:v>
+                  <c:v>1034.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>909.82500000000005</c:v>
+                  <c:v>1099.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>991.19999999999993</c:v>
+                  <c:v>1164</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1197.5750000000003</c:v>
+                  <c:v>1253.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1403.9499999999998</c:v>
+                  <c:v>1343.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1610.325</c:v>
+                  <c:v>1433.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1816.7000000000003</c:v>
+                  <c:v>1523.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2023.075</c:v>
+                  <c:v>1613</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2229.4500000000003</c:v>
+                  <c:v>1702.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2435.8249999999998</c:v>
+                  <c:v>1792.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2642.2</c:v>
+                  <c:v>1882.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,64 +1031,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1284</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1362</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1380</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1617.5</c:v>
+                  <c:v>1543</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1855</c:v>
+                  <c:v>1646</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2092.5</c:v>
+                  <c:v>1749</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2330</c:v>
+                  <c:v>1852</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2567.5</c:v>
+                  <c:v>1955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2805</c:v>
+                  <c:v>2058</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3042.5</c:v>
+                  <c:v>2161</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3280</c:v>
+                  <c:v>2264</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1207,64 +1207,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>474.82499999999999</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>616.20000000000005</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>757.57500000000005</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>898.95</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1040.3249999999998</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1181.7</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1323.075</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1464.45</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1605.825</c:v>
+                  <c:v>1620</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1747.2</c:v>
+                  <c:v>1710</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2013.5750000000003</c:v>
+                  <c:v>1825</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2279.9499999999998</c:v>
+                  <c:v>1940</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2546.3249999999998</c:v>
+                  <c:v>2055</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2812.7</c:v>
+                  <c:v>2170</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3079.0749999999998</c:v>
+                  <c:v>2285</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3345.4500000000003</c:v>
+                  <c:v>2400</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3611.8249999999998</c:v>
+                  <c:v>2515</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3878.2</c:v>
+                  <c:v>2630</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1383,64 +1383,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>580.79999999999995</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>748.80000000000007</c:v>
+                  <c:v>840</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>916.8</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1084.8</c:v>
+                  <c:v>1260</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1252.8</c:v>
+                  <c:v>1470</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1420.8000000000002</c:v>
+                  <c:v>1570.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1588.8</c:v>
+                  <c:v>1671.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1756.8</c:v>
+                  <c:v>1772.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1924.8000000000002</c:v>
+                  <c:v>1873.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2092.8000000000002</c:v>
+                  <c:v>1974</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2385.8000000000002</c:v>
+                  <c:v>2099.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2678.8</c:v>
+                  <c:v>2225.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2971.8</c:v>
+                  <c:v>2351.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3264.8</c:v>
+                  <c:v>2477.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3557.7999999999997</c:v>
+                  <c:v>2603</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3850.8</c:v>
+                  <c:v>2728.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4143.7999999999993</c:v>
+                  <c:v>2854.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4436.8</c:v>
+                  <c:v>2980.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1792,31 +1792,31 @@
                   <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1400</c:v>
+                  <c:v>1390</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1562.5</c:v>
+                  <c:v>1527.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1725</c:v>
+                  <c:v>1665</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1887.5</c:v>
+                  <c:v>1802.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2050</c:v>
+                  <c:v>1940</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2212.5</c:v>
+                  <c:v>2077.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2375</c:v>
+                  <c:v>2215</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2537.5</c:v>
+                  <c:v>2352.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2700</c:v>
+                  <c:v>2490</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1968,31 +1968,31 @@
                   <c:v>1267.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1397.5</c:v>
+                  <c:v>1392.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1597.5</c:v>
+                  <c:v>1567.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1797.5</c:v>
+                  <c:v>1742.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1997.5</c:v>
+                  <c:v>1917.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2197.5</c:v>
+                  <c:v>2092.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2397.5</c:v>
+                  <c:v>2267.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2597.5</c:v>
+                  <c:v>2442.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2797.5</c:v>
+                  <c:v>2617.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2997.5</c:v>
+                  <c:v>2792.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2147,28 +2147,28 @@
                   <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1617.5</c:v>
+                  <c:v>1592.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1855</c:v>
+                  <c:v>1805</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2092.5</c:v>
+                  <c:v>2017.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2330</c:v>
+                  <c:v>2230</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2567.5</c:v>
+                  <c:v>2442.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2805</c:v>
+                  <c:v>2655</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3042.5</c:v>
+                  <c:v>2867.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3280</c:v>
+                  <c:v>3080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2323,28 +2323,28 @@
                   <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1622.5</c:v>
+                  <c:v>1602.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1897.5</c:v>
+                  <c:v>1852.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2172.5</c:v>
+                  <c:v>2102.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2447.5</c:v>
+                  <c:v>2352.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2722.5</c:v>
+                  <c:v>2602.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2997.5</c:v>
+                  <c:v>2852.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3272.5</c:v>
+                  <c:v>3102.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3547.5</c:v>
+                  <c:v>3352.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2499,28 +2499,28 @@
                   <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1612.5</c:v>
+                  <c:v>1597.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1924.9999999999998</c:v>
+                  <c:v>1885</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2237.5</c:v>
+                  <c:v>2172.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2550</c:v>
+                  <c:v>2460</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2862.5</c:v>
+                  <c:v>2747.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3175</c:v>
+                  <c:v>3035</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3487.5</c:v>
+                  <c:v>3322.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3800</c:v>
+                  <c:v>3610</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2839,64 +2839,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>225</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>300</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>349.5</c:v>
+                  <c:v>247.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>399</c:v>
+                  <c:v>291.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>448.5</c:v>
+                  <c:v>335.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>498</c:v>
+                  <c:v>379.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>547.5</c:v>
+                  <c:v>423.6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>597</c:v>
+                  <c:v>467.6</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>646.5</c:v>
+                  <c:v>511.60000000000008</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>696</c:v>
+                  <c:v>555.6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>745.5</c:v>
+                  <c:v>599.6</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>795</c:v>
+                  <c:v>643.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>844.5</c:v>
+                  <c:v>687.6</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>894.00000000000011</c:v>
+                  <c:v>731.60000000000014</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>943.49999999999989</c:v>
+                  <c:v>775.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>993</c:v>
+                  <c:v>819.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1042.5</c:v>
+                  <c:v>863.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1092</c:v>
+                  <c:v>907.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3015,64 +3015,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>300</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>400</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>481</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>543</c:v>
+                  <c:v>439.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>605</c:v>
+                  <c:v>502.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>667</c:v>
+                  <c:v>565.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>729</c:v>
+                  <c:v>628.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>791</c:v>
+                  <c:v>691.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>853</c:v>
+                  <c:v>754.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>915</c:v>
+                  <c:v>817.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>977</c:v>
+                  <c:v>880.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1039</c:v>
+                  <c:v>943.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1101</c:v>
+                  <c:v>1006.2000000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1163</c:v>
+                  <c:v>1069.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1225</c:v>
+                  <c:v>1132.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1287</c:v>
+                  <c:v>1195.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1349</c:v>
+                  <c:v>1258.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1411</c:v>
+                  <c:v>1321.2000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3191,64 +3191,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>500</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>625</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>697.5</c:v>
+                  <c:v>591.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>770</c:v>
+                  <c:v>671.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>842.5</c:v>
+                  <c:v>752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>915</c:v>
+                  <c:v>832</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>987.5</c:v>
+                  <c:v>912</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1060</c:v>
+                  <c:v>992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1132.5</c:v>
+                  <c:v>1072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1205</c:v>
+                  <c:v>1152</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1277.5</c:v>
+                  <c:v>1232</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1350</c:v>
+                  <c:v>1312</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1422.5</c:v>
+                  <c:v>1392</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1495</c:v>
+                  <c:v>1472</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1567.5</c:v>
+                  <c:v>1552</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1640</c:v>
+                  <c:v>1632</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1712.5</c:v>
+                  <c:v>1712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3367,64 +3367,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>865.5</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>946.5</c:v>
+                  <c:v>848</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1027.5</c:v>
+                  <c:v>943</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1108.5</c:v>
+                  <c:v>1038</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1189.5</c:v>
+                  <c:v>1133</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1270.5000000000002</c:v>
+                  <c:v>1228</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1351.5</c:v>
+                  <c:v>1323</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1432.5</c:v>
+                  <c:v>1418</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1513.5</c:v>
+                  <c:v>1513</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1594.5</c:v>
+                  <c:v>1608</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1675.5</c:v>
+                  <c:v>1703</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1756.5</c:v>
+                  <c:v>1798</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1837.5</c:v>
+                  <c:v>1893</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1918.5</c:v>
+                  <c:v>1988</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1999.5</c:v>
+                  <c:v>2083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3543,64 +3543,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>350</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>525</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>700</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>875</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1050</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1137.5</c:v>
+                  <c:v>1033.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1225</c:v>
+                  <c:v>1141.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1312.5</c:v>
+                  <c:v>1249.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1400</c:v>
+                  <c:v>1357.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1487.5</c:v>
+                  <c:v>1465.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1575</c:v>
+                  <c:v>1573.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1662.5</c:v>
+                  <c:v>1681.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1750</c:v>
+                  <c:v>1789.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1837.5</c:v>
+                  <c:v>1897.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1925</c:v>
+                  <c:v>2005.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2012.5</c:v>
+                  <c:v>2113.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2100</c:v>
+                  <c:v>2221.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2187.5</c:v>
+                  <c:v>2329.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2275</c:v>
+                  <c:v>2437.1999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3945,31 +3945,31 @@
                   <c:v>532.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>600.79999999999995</c:v>
+                  <c:v>590.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>698.8</c:v>
+                  <c:v>663.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>796.8</c:v>
+                  <c:v>736.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>894.8</c:v>
+                  <c:v>809.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>992.80000000000018</c:v>
+                  <c:v>882.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1090.8</c:v>
+                  <c:v>955.8</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1188.8000000000002</c:v>
+                  <c:v>1028.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1286.8</c:v>
+                  <c:v>1101.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1384.8</c:v>
+                  <c:v>1174.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,31 +4121,31 @@
                   <c:v>909.82500000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1008.6999999999999</c:v>
+                  <c:v>1003.6999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1177.575</c:v>
+                  <c:v>1147.575</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1346.4499999999998</c:v>
+                  <c:v>1291.4499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1515.325</c:v>
+                  <c:v>1435.325</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1684.2000000000003</c:v>
+                  <c:v>1579.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1853.075</c:v>
+                  <c:v>1723.075</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2021.9500000000003</c:v>
+                  <c:v>1866.95</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2190.8249999999998</c:v>
+                  <c:v>2010.825</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2359.6999999999998</c:v>
+                  <c:v>2154.6999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4300,28 +4300,28 @@
                   <c:v>1380</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1617.5</c:v>
+                  <c:v>1592.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1855</c:v>
+                  <c:v>1805</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2092.5</c:v>
+                  <c:v>2017.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2330</c:v>
+                  <c:v>2230</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2567.5</c:v>
+                  <c:v>2442.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2805</c:v>
+                  <c:v>2655</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3042.5</c:v>
+                  <c:v>2867.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3280</c:v>
+                  <c:v>3080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4476,28 +4476,28 @@
                   <c:v>1747.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2018.5750000000003</c:v>
+                  <c:v>1998.575</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2322.4499999999998</c:v>
+                  <c:v>2277.4499999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2626.3249999999998</c:v>
+                  <c:v>2556.3249999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2930.2</c:v>
+                  <c:v>2835.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3234.0749999999998</c:v>
+                  <c:v>3114.0749999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3537.9500000000003</c:v>
+                  <c:v>3392.9500000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3841.8249999999998</c:v>
+                  <c:v>3671.8249999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4145.7</c:v>
+                  <c:v>3950.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4652,28 +4652,28 @@
                   <c:v>2092.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2380.8000000000002</c:v>
+                  <c:v>2365.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2748.8</c:v>
+                  <c:v>2708.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3116.8</c:v>
+                  <c:v>3051.8</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3484.8</c:v>
+                  <c:v>3394.8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3852.7999999999997</c:v>
+                  <c:v>3737.7999999999997</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4220.8</c:v>
+                  <c:v>4080.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4588.7999999999993</c:v>
+                  <c:v>4423.7999999999993</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4956.8</c:v>
+                  <c:v>4766.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6123,20 +6123,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6166,17 +6166,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6207,13 +6207,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6251,16 +6251,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="24">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="27">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>1380</v>
-      </c>
-      <c r="J8" s="24"/>
+        <v>817.5</v>
+      </c>
+      <c r="J8" s="27"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -6294,20 +6294,20 @@
         <v>51</v>
       </c>
       <c r="C10" s="16">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="24">
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="27">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1072</v>
-      </c>
-      <c r="J10" s="24"/>
+        <v>671.99999999999989</v>
+      </c>
+      <c r="J10" s="27"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -6359,13 +6359,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6383,11 +6383,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
         <v>2500</v>
@@ -6412,11 +6412,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
         <v>2250</v>
@@ -6436,14 +6436,14 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>22</v>
@@ -6460,14 +6460,14 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
-        <v>4750</v>
+        <v>4250</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>22</v>
@@ -6506,11 +6506,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -6530,11 +6530,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
         <v>1600</v>
@@ -6571,11 +6571,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -6595,11 +6595,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
@@ -6619,11 +6619,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
         <v>0.28000000000000003</v>
@@ -6673,20 +6673,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -6947,17 +6947,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -6965,6 +6954,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <dataValidations count="6">
@@ -7025,20 +7025,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7065,20 +7065,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7108,17 +7108,17 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7702,20 +7702,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7789,20 +7789,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7832,17 +7832,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7872,17 +7872,17 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8466,20 +8466,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8553,20 +8553,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8593,20 +8593,20 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8629,20 +8629,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9226,20 +9226,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9309,20 +9309,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9352,17 +9352,17 @@
         <v>2</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9385,20 +9385,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9982,20 +9982,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10069,40 +10069,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10126,21 +10126,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
@@ -10452,21 +10452,21 @@
         <v>22</v>
       </c>
       <c r="D13" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E13" s="6">
         <f>(D13+F13)/2</f>
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="F13" s="3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="6">
         <f>(F13+H13)/2</f>
-        <v>3250</v>
+        <v>2750</v>
       </c>
       <c r="H13" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="3">
@@ -10772,73 +10772,73 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="20"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="20"/>
+      <c r="C24" s="22"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="20"/>
+      <c r="C25" s="22"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10856,25 +10856,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="20"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -10896,154 +10896,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="26"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="26"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11150,6 +11150,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="J5:N5"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F23:N24"/>
+    <mergeCell ref="F26:N26"/>
     <mergeCell ref="B33:N33"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="B35:N35"/>
@@ -11158,17 +11169,6 @@
     <mergeCell ref="B30:N30"/>
     <mergeCell ref="B31:N31"/>
     <mergeCell ref="B32:N32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F23:N24"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="J5:N5"/>
-    <mergeCell ref="B22:N22"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11348,23 +11348,23 @@
       </c>
       <c r="F5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.96</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I5" s="7">
         <f>F5*H5</f>
-        <v>960</v>
+        <v>1008.0000000000001</v>
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11372,23 +11372,23 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>3460</v>
+        <v>1508</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11435,23 +11435,23 @@
       </c>
       <c r="F6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.92999999999999994</v>
+        <v>0.54</v>
       </c>
       <c r="I6" s="7">
         <f>F6*H6</f>
-        <v>1627.5</v>
+        <v>1296</v>
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11459,23 +11459,23 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>4127.5</v>
+        <v>1796</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.84000000000000008</v>
+        <v>0.62</v>
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1260.0000000000002</v>
+        <v>1240</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11522,23 +11522,23 @@
       </c>
       <c r="F7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I7" s="7">
         <f>F7*H7</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11546,23 +11546,23 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>4750</v>
+        <v>2060</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P7" s="8">
         <f>M7*O7</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q7" s="8">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -11609,23 +11609,23 @@
       </c>
       <c r="F8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="7">
         <f>F8*H8</f>
-        <v>2827.5</v>
+        <v>1800</v>
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11633,23 +11633,23 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>5327.5</v>
+        <v>2300</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>1900</v>
+        <v>1620</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11696,23 +11696,23 @@
       </c>
       <c r="F9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="I9" s="7">
         <f>F9*H9</f>
-        <v>3360</v>
+        <v>2016</v>
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11720,23 +11720,23 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>5860</v>
+        <v>2516</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>2160</v>
+        <v>1750</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11924,23 +11924,23 @@
       </c>
       <c r="C15" s="14">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D15" s="14">
         <f t="shared" si="1"/>
-        <v>87.5</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="2"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="3"/>
-        <v>162.5</v>
+        <v>180</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="4"/>
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -11965,23 +11965,23 @@
       </c>
       <c r="C16" s="14">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="D16" s="14">
         <f t="shared" si="1"/>
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="4"/>
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -12006,23 +12006,23 @@
       </c>
       <c r="C17" s="14">
         <f t="shared" si="0"/>
-        <v>148.80000000000001</v>
+        <v>270</v>
       </c>
       <c r="D17" s="14">
         <f t="shared" si="1"/>
-        <v>258.82499999999999</v>
+        <v>360</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="2"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="F17" s="14">
         <f t="shared" si="3"/>
-        <v>474.82499999999999</v>
+        <v>540</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="4"/>
-        <v>580.79999999999995</v>
+        <v>630</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12047,23 +12047,23 @@
       </c>
       <c r="C18" s="14">
         <f t="shared" si="0"/>
-        <v>196.8</v>
+        <v>360</v>
       </c>
       <c r="D18" s="14">
         <f t="shared" si="1"/>
-        <v>340.20000000000005</v>
+        <v>480</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="2"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F18" s="14">
         <f t="shared" si="3"/>
-        <v>616.20000000000005</v>
+        <v>720</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="4"/>
-        <v>748.80000000000007</v>
+        <v>840</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -12088,23 +12088,23 @@
       </c>
       <c r="C19" s="14">
         <f t="shared" si="0"/>
-        <v>244.8</v>
+        <v>450</v>
       </c>
       <c r="D19" s="14">
         <f t="shared" si="1"/>
-        <v>421.57500000000005</v>
+        <v>600</v>
       </c>
       <c r="E19" s="14">
         <f t="shared" si="2"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="F19" s="14">
         <f t="shared" si="3"/>
-        <v>757.57500000000005</v>
+        <v>900</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="4"/>
-        <v>916.8</v>
+        <v>1050</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -12129,23 +12129,23 @@
       </c>
       <c r="C20" s="14">
         <f t="shared" si="0"/>
-        <v>292.79999999999995</v>
+        <v>540</v>
       </c>
       <c r="D20" s="14">
         <f t="shared" si="1"/>
-        <v>502.95</v>
+        <v>720</v>
       </c>
       <c r="E20" s="14">
         <f t="shared" si="2"/>
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="3"/>
-        <v>898.95</v>
+        <v>1080</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="4"/>
-        <v>1084.8</v>
+        <v>1260</v>
       </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -12170,23 +12170,23 @@
       </c>
       <c r="C21" s="14">
         <f t="shared" si="0"/>
-        <v>340.79999999999995</v>
+        <v>630</v>
       </c>
       <c r="D21" s="14">
         <f t="shared" si="1"/>
-        <v>584.32500000000005</v>
+        <v>840</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="2"/>
-        <v>817.5</v>
+        <v>1050</v>
       </c>
       <c r="F21" s="14">
         <f t="shared" si="3"/>
-        <v>1040.3249999999998</v>
+        <v>1260</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="4"/>
-        <v>1252.8</v>
+        <v>1470</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -12211,23 +12211,23 @@
       </c>
       <c r="C22" s="14">
         <f t="shared" si="0"/>
-        <v>388.8</v>
+        <v>680.40000000000009</v>
       </c>
       <c r="D22" s="14">
         <f t="shared" si="1"/>
-        <v>665.7</v>
+        <v>904.80000000000007</v>
       </c>
       <c r="E22" s="14">
         <f t="shared" si="2"/>
-        <v>930.00000000000011</v>
+        <v>1128</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" si="3"/>
-        <v>1181.7</v>
+        <v>1350</v>
       </c>
       <c r="G22" s="14">
         <f t="shared" si="4"/>
-        <v>1420.8000000000002</v>
+        <v>1570.8000000000002</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -12252,23 +12252,23 @@
       </c>
       <c r="C23" s="14">
         <f t="shared" si="0"/>
-        <v>436.8</v>
+        <v>730.80000000000007</v>
       </c>
       <c r="D23" s="14">
         <f t="shared" si="1"/>
-        <v>747.07500000000005</v>
+        <v>969.6</v>
       </c>
       <c r="E23" s="14">
         <f t="shared" si="2"/>
-        <v>1042.5</v>
+        <v>1206</v>
       </c>
       <c r="F23" s="14">
         <f t="shared" si="3"/>
-        <v>1323.075</v>
+        <v>1440</v>
       </c>
       <c r="G23" s="14">
         <f t="shared" si="4"/>
-        <v>1588.8</v>
+        <v>1671.6000000000001</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -12293,23 +12293,23 @@
       </c>
       <c r="C24" s="14">
         <f t="shared" si="0"/>
-        <v>484.8</v>
+        <v>781.2</v>
       </c>
       <c r="D24" s="14">
         <f t="shared" si="1"/>
-        <v>828.45</v>
+        <v>1034.4000000000001</v>
       </c>
       <c r="E24" s="14">
         <f t="shared" si="2"/>
-        <v>1155</v>
+        <v>1284</v>
       </c>
       <c r="F24" s="14">
         <f t="shared" si="3"/>
-        <v>1464.45</v>
+        <v>1530</v>
       </c>
       <c r="G24" s="14">
         <f t="shared" si="4"/>
-        <v>1756.8</v>
+        <v>1772.4</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -12334,23 +12334,23 @@
       </c>
       <c r="C25" s="14">
         <f t="shared" si="0"/>
-        <v>532.80000000000007</v>
+        <v>831.60000000000014</v>
       </c>
       <c r="D25" s="14">
         <f t="shared" si="1"/>
-        <v>909.82500000000005</v>
+        <v>1099.2</v>
       </c>
       <c r="E25" s="14">
         <f t="shared" si="2"/>
-        <v>1267.5</v>
+        <v>1362</v>
       </c>
       <c r="F25" s="14">
         <f t="shared" si="3"/>
-        <v>1605.825</v>
+        <v>1620</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="4"/>
-        <v>1924.8000000000002</v>
+        <v>1873.2000000000003</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -12375,23 +12375,23 @@
       </c>
       <c r="C26" s="14">
         <f t="shared" si="0"/>
-        <v>580.79999999999995</v>
+        <v>882</v>
       </c>
       <c r="D26" s="14">
         <f t="shared" si="1"/>
-        <v>991.19999999999993</v>
+        <v>1164</v>
       </c>
       <c r="E26" s="14">
         <f t="shared" si="2"/>
-        <v>1380</v>
+        <v>1440</v>
       </c>
       <c r="F26" s="14">
         <f t="shared" si="3"/>
-        <v>1747.2</v>
+        <v>1710</v>
       </c>
       <c r="G26" s="14">
         <f t="shared" si="4"/>
-        <v>2092.8000000000002</v>
+        <v>1974</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -12416,23 +12416,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>753.80000000000007</v>
+        <v>957.40000000000009</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1197.5750000000003</v>
+        <v>1253.8000000000002</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1617.5</v>
+        <v>1543</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>2013.5750000000003</v>
+        <v>1825</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2385.8000000000002</v>
+        <v>2099.8000000000002</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12457,23 +12457,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>926.8</v>
+        <v>1032.8</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1403.9499999999998</v>
+        <v>1343.6</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1855</v>
+        <v>1646</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>2279.9499999999998</v>
+        <v>1940</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2678.8</v>
+        <v>2225.6</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12498,23 +12498,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>1099.8</v>
+        <v>1108.2</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1610.325</v>
+        <v>1433.4</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>2092.5</v>
+        <v>1749</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2546.3249999999998</v>
+        <v>2055</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>2971.8</v>
+        <v>2351.4</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12539,23 +12539,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1272.8000000000002</v>
+        <v>1183.6000000000001</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1816.7000000000003</v>
+        <v>1523.2</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>2330</v>
+        <v>1852</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2812.7</v>
+        <v>2170</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>3264.8</v>
+        <v>2477.2000000000003</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12580,23 +12580,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1445.8</v>
+        <v>1259</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>2023.075</v>
+        <v>1613</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>2567.5</v>
+        <v>1955</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>3079.0749999999998</v>
+        <v>2285</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>3557.7999999999997</v>
+        <v>2603</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12621,23 +12621,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1618.8000000000002</v>
+        <v>1334.4</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>2229.4500000000003</v>
+        <v>1702.8000000000002</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2805</v>
+        <v>2058</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>3345.4500000000003</v>
+        <v>2400</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>3850.8</v>
+        <v>2728.8</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12662,23 +12662,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1791.8</v>
+        <v>1409.8000000000002</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>2435.8249999999998</v>
+        <v>1792.6</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>3042.5</v>
+        <v>2161</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>3611.8249999999998</v>
+        <v>2515</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>4143.7999999999993</v>
+        <v>2854.6</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12703,23 +12703,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1964.8</v>
+        <v>1485.2</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>2642.2</v>
+        <v>1882.4</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>3280</v>
+        <v>2264</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>3878.2</v>
+        <v>2630</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>4436.8</v>
+        <v>2980.4</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>3250</v>
+        <v>2750</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
@@ -13148,7 +13148,7 @@
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>4750</v>
+        <v>4250</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>3250</v>
+        <v>2750</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>6250</v>
+        <v>5750</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
@@ -14044,11 +14044,11 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1400</v>
+        <v>1390</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1397.5</v>
+        <v>1392.5</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
@@ -14084,23 +14084,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1562.5</v>
+        <v>1527.5</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1597.5</v>
+        <v>1567.5</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1617.5</v>
+        <v>1592.5</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1622.5</v>
+        <v>1602.5</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1612.5</v>
+        <v>1597.5</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14124,23 +14124,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1725</v>
+        <v>1665</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1797.5</v>
+        <v>1742.5</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1855</v>
+        <v>1805</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1897.5</v>
+        <v>1852.5</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1924.9999999999998</v>
+        <v>1885</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14164,23 +14164,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1887.5</v>
+        <v>1802.5</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1997.5</v>
+        <v>1917.5</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>2092.5</v>
+        <v>2017.5</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>2172.5</v>
+        <v>2102.5</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>2237.5</v>
+        <v>2172.5</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14204,23 +14204,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>2050</v>
+        <v>1940</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>2197.5</v>
+        <v>2092.5</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>2330</v>
+        <v>2230</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>2447.5</v>
+        <v>2352.5</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>2550</v>
+        <v>2460</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14244,23 +14244,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>2212.5</v>
+        <v>2077.5</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>2397.5</v>
+        <v>2267.5</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>2567.5</v>
+        <v>2442.5</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2722.5</v>
+        <v>2602.5</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2862.5</v>
+        <v>2747.5</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14284,23 +14284,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>2375</v>
+        <v>2215</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>2597.5</v>
+        <v>2442.5</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2805</v>
+        <v>2655</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2997.5</v>
+        <v>2852.5</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>3175</v>
+        <v>3035</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14324,23 +14324,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>2537.5</v>
+        <v>2352.5</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2797.5</v>
+        <v>2617.5</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>3042.5</v>
+        <v>2867.5</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>3272.5</v>
+        <v>3102.5</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>3487.5</v>
+        <v>3322.5</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14364,23 +14364,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2700</v>
+        <v>2490</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2997.5</v>
+        <v>2792.5</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>3280</v>
+        <v>3080</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>3547.5</v>
+        <v>3352.5</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>3800</v>
+        <v>3610</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14691,19 +14691,19 @@
       </c>
       <c r="F85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.56000000000000005</v>
+        <v>0.96</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>1008.0000000000001</v>
+        <v>960</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
@@ -14711,27 +14711,27 @@
       </c>
       <c r="K85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1508</v>
+        <v>1460</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="O85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>990</v>
+        <v>880</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -14777,47 +14777,47 @@
       </c>
       <c r="F86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>2400</v>
+        <v>1750</v>
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.54</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>1296</v>
+        <v>1627.5</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>500</v>
+        <v>1250</v>
       </c>
       <c r="K86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>1796</v>
+        <v>2877.5</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.22500000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="O86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.62</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>1240</v>
+        <v>1260.0000000000002</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -14863,23 +14863,23 @@
       </c>
       <c r="F87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.52</v>
+        <v>0.9</v>
       </c>
       <c r="I87" s="8">
         <f>F87*H87</f>
-        <v>1560</v>
+        <v>2250</v>
       </c>
       <c r="J87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -14887,23 +14887,23 @@
       </c>
       <c r="L87" s="8">
         <f>I87+J87</f>
-        <v>2060</v>
+        <v>4250</v>
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="O87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.57999999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -14949,47 +14949,47 @@
       </c>
       <c r="F88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>3600</v>
+        <v>3250</v>
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.5</v>
+        <v>0.87</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>1800</v>
+        <v>2827.5</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>500</v>
+        <v>2750</v>
       </c>
       <c r="K88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>2300</v>
+        <v>5577.5</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.27500000000000002</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="O88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>1620</v>
+        <v>1900</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -15035,47 +15035,47 @@
       </c>
       <c r="F89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.48</v>
+        <v>0.84</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>2016</v>
+        <v>3360</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="K89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>2516</v>
+        <v>6860</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="O89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>1750</v>
+        <v>2160</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -15257,23 +15257,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -15297,23 +15297,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -15337,23 +15337,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>450</v>
+        <v>375</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -15377,23 +15377,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -15417,23 +15417,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>349.5</v>
+        <v>247.6</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>481</v>
+        <v>375</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>625</v>
+        <v>500</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>750</v>
+        <v>625</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>875</v>
+        <v>750</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -15457,23 +15457,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>399</v>
+        <v>291.59999999999997</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>543</v>
+        <v>439.2</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>697.5</v>
+        <v>591.99999999999989</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>865.5</v>
+        <v>750</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>1050</v>
+        <v>900</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -15497,23 +15497,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>448.5</v>
+        <v>335.59999999999997</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>605</v>
+        <v>502.2</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>770</v>
+        <v>671.99999999999989</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>946.5</v>
+        <v>848</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1137.5</v>
+        <v>1033.1999999999998</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -15537,23 +15537,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>498</v>
+        <v>379.6</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>667</v>
+        <v>565.20000000000005</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>842.5</v>
+        <v>752</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>1027.5</v>
+        <v>943</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>1225</v>
+        <v>1141.2</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -15577,23 +15577,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>547.5</v>
+        <v>423.6</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>729</v>
+        <v>628.20000000000005</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>915</v>
+        <v>832</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1108.5</v>
+        <v>1038</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>1312.5</v>
+        <v>1249.2</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -15617,23 +15617,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>597</v>
+        <v>467.6</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>791</v>
+        <v>691.2</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>987.5</v>
+        <v>912</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>1189.5</v>
+        <v>1133</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>1400</v>
+        <v>1357.2</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -15657,23 +15657,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>646.5</v>
+        <v>511.60000000000008</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>853</v>
+        <v>754.2</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>1060</v>
+        <v>992</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>1270.5000000000002</v>
+        <v>1228</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>1487.5</v>
+        <v>1465.2</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -15697,23 +15697,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>696</v>
+        <v>555.6</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>915</v>
+        <v>817.2</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>1132.5</v>
+        <v>1072</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>1351.5</v>
+        <v>1323</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>1575</v>
+        <v>1573.1999999999998</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -15737,23 +15737,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>745.5</v>
+        <v>599.6</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>977</v>
+        <v>880.2</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>1205</v>
+        <v>1152</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>1432.5</v>
+        <v>1418</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>1662.5</v>
+        <v>1681.2</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -15777,23 +15777,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>795</v>
+        <v>643.59999999999991</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>1039</v>
+        <v>943.2</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>1277.5</v>
+        <v>1232</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>1513.5</v>
+        <v>1513</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>1750</v>
+        <v>1789.1999999999998</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -15817,23 +15817,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>844.5</v>
+        <v>687.6</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>1101</v>
+        <v>1006.2000000000002</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>1350</v>
+        <v>1312</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>1594.5</v>
+        <v>1608</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>1837.5</v>
+        <v>1897.1999999999998</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -15857,23 +15857,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>894.00000000000011</v>
+        <v>731.60000000000014</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>1163</v>
+        <v>1069.2000000000003</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>1422.5</v>
+        <v>1392</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>1675.5</v>
+        <v>1703</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>1925</v>
+        <v>2005.2</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -15897,23 +15897,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>943.49999999999989</v>
+        <v>775.6</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>1225</v>
+        <v>1132.2</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>1495</v>
+        <v>1472</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>1756.5</v>
+        <v>1798</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>2012.5</v>
+        <v>2113.1999999999998</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -15937,23 +15937,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>993</v>
+        <v>819.6</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>1287</v>
+        <v>1195.2000000000003</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>1567.5</v>
+        <v>1552</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>1837.5</v>
+        <v>1893</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>2100</v>
+        <v>2221.1999999999998</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -15977,23 +15977,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>1042.5</v>
+        <v>863.6</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>1349</v>
+        <v>1258.2</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>1918.5</v>
+        <v>1988</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>2187.5</v>
+        <v>2329.1999999999998</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -16017,23 +16017,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>1092</v>
+        <v>907.6</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>1411</v>
+        <v>1321.2000000000003</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>1712.5</v>
+        <v>1712</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>1999.5</v>
+        <v>2083</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>2275</v>
+        <v>2437.1999999999998</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>1960</v>
+        <v>1460</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1750</v>
+        <v>1250</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>3377.5</v>
+        <v>2877.5</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="K127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>4750</v>
+        <v>4250</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>3250</v>
+        <v>2750</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>6077.5</v>
+        <v>5577.5</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>7360</v>
+        <v>6860</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
@@ -17545,11 +17545,11 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>600.79999999999995</v>
+        <v>590.79999999999995</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>1008.6999999999999</v>
+        <v>1003.6999999999999</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
@@ -17600,23 +17600,23 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>698.8</v>
+        <v>663.8</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1177.575</v>
+        <v>1147.575</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>1617.5</v>
+        <v>1592.5</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>2018.5750000000003</v>
+        <v>1998.575</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>2380.8000000000002</v>
+        <v>2365.8000000000002</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
@@ -17655,23 +17655,23 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>796.8</v>
+        <v>736.8</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>1346.4499999999998</v>
+        <v>1291.4499999999998</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>1855</v>
+        <v>1805</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>2322.4499999999998</v>
+        <v>2277.4499999999998</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>2748.8</v>
+        <v>2708.8</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
@@ -17710,23 +17710,23 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>894.8</v>
+        <v>809.8</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>1515.325</v>
+        <v>1435.325</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>2092.5</v>
+        <v>2017.5</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>2626.3249999999998</v>
+        <v>2556.3249999999998</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>3116.8</v>
+        <v>3051.8</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
@@ -17765,23 +17765,23 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>992.80000000000018</v>
+        <v>882.80000000000007</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>1684.2000000000003</v>
+        <v>1579.2000000000003</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>2330</v>
+        <v>2230</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>2930.2</v>
+        <v>2835.2</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>3484.8</v>
+        <v>3394.8</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
@@ -17820,23 +17820,23 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>1090.8</v>
+        <v>955.8</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>1853.075</v>
+        <v>1723.075</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>2567.5</v>
+        <v>2442.5</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>3234.0749999999998</v>
+        <v>3114.0749999999998</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>3852.7999999999997</v>
+        <v>3737.7999999999997</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
@@ -17875,23 +17875,23 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1188.8000000000002</v>
+        <v>1028.8000000000002</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>2021.9500000000003</v>
+        <v>1866.95</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>2805</v>
+        <v>2655</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>3537.9500000000003</v>
+        <v>3392.9500000000003</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>4220.8</v>
+        <v>4080.8</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
@@ -17930,23 +17930,23 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>1286.8</v>
+        <v>1101.8</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>2190.8249999999998</v>
+        <v>2010.825</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>3042.5</v>
+        <v>2867.5</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>3841.8249999999998</v>
+        <v>3671.8249999999998</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>4588.7999999999993</v>
+        <v>4423.7999999999993</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
@@ -17985,23 +17985,23 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>1384.8</v>
+        <v>1174.8</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>2359.6999999999998</v>
+        <v>2154.6999999999998</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>3280</v>
+        <v>3080</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>4145.7</v>
+        <v>3950.7</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>4956.8</v>
+        <v>4766.8</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="J165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="K165">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="L165">
         <f>I165+J165</f>
-        <v>4750</v>
+        <v>4250</v>
       </c>
       <c r="M165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>
